--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,36 +527,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>No more MH-CET exams outside Maharashtra: Chandrakant Patil</t>
+          <t>Patil slams mismanagement by institutes, urges fee reforms for girls’ education</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/mh-cet-exams-maharashtra-chandrakant-patil-10050751/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Political Jibe: Chandrakant Patil Says Sanjay Raut Has 'Political Jaundice'</t>
+          <t>No more MH-CET exams outside Maharashtra: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mh-cet-exams-maharashtra-chandrakant-patil-10050751/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chandrakant Patil urges PMC to build Sudhir Phadke Memorial in Kothrud</t>
+          <t>Political Jibe: Chandrakant Patil Says Sanjay Raut Has 'Political Jaundice'</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
         </is>
       </c>
     </row>
@@ -575,12 +575,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Patil slams mismanagement by institutes, urges fee reforms for girls’ education</t>
+          <t>Chandrakant Patil urges PMC to build Sudhir Phadke Memorial in Kothrud</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
         </is>
       </c>
     </row>
@@ -695,12 +695,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
+          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
+          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
         </is>
       </c>
     </row>
@@ -719,48 +719,48 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
+          <t>May become minister in future, either joining Congress or any other party, says Vishal Patil weeks after</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>May become minister in future, either joining Congress or any other party, says Vishal Patil weeks after</t>
+          <t>1,000 new personnel to join Pune Police force: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1,000 new personnel to join Pune Police force: Chandrakant Patil</t>
+          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
+          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
         </is>
       </c>
     </row>
@@ -803,4944 +803,4944 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>People of different backgrounds are bound to disagree in coalition govt: Chandrakant Patil</t>
+          <t>Patil tells officials to expedite land acquisition for roads in Kothrud</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Patil tells officials to expedite land acquisition for roads in Kothrud</t>
+          <t>Grateful minister urges edu trust to go autonomous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grateful minister urges edu trust to go autonomous</t>
+          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
+          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Maharashtra minister's ‘golden’ moment’ remark sparks buzz of Uddhav Thackeray-BJP patch-up</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharashtra minister's ‘golden’ moment’ remark sparks buzz of Uddhav Thackeray-BJP patch-up</t>
+          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
+          <t>RSS holds two-day brainstorming session with BJP, allied outfits</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Schools in Sangli district free of tobacco, says Chandrakant Patil</t>
+          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/schools-in-sangli-district-free-of-tobacco-says-chandrakant-patil/articleshow/120074515.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RSS holds two-day brainstorming session with BJP, allied outfits</t>
+          <t>DH Evening Brief: BSF Jawan Returns from Pakistan; MP HC Orders FIR Against Minister</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
+          <t>State’s tech edu minister reviews fee waiver for women students</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DH Evening Brief: BSF Jawan Returns from Pakistan; MP HC Orders FIR Against Minister</t>
+          <t>Retirement Age of College Principals Raised to 65: Announces Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
+          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>State’s tech edu minister reviews fee waiver for women students</t>
+          <t>DPDC meeting on Thursday</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Retirement Age of College Principals Raised to 65: Announces Minister Chandrakant Patil</t>
+          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DPDC meeting on Thursday</t>
+          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
+          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
+          <t>Pune News: Chandrakant Patil Issues Ultimatum to Pune Municipal Corporation Over Solid Waste Management Project</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
+          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pune News: Chandrakant Patil Issues Ultimatum to Pune Municipal Corporation Over Solid Waste Management Project</t>
+          <t>Three-Week Monsoon Session of Maharashtra Assembly to Begin on Monday</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
+          <t>https://www.deccanchronicle.com/nation/three-week-monsoon-session-of-maharashtra-assembly-to-begin-on-monday-1887745</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
+          <t>Pune: Chandrakant Patil reviews Bajirao Peshwa Memorial Work on Parvati Hill</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
+          <t>https://punemirror.com/politics/pune-chandrakant-patil-reviews-bajirao-peshwa-memorial-work-on-parvati-hill/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil reviews Bajirao Peshwa Memorial Work on Parvati Hill</t>
+          <t>Patil silent on Bavdhan garbage plant issue in PMC meeting</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://punemirror.com/politics/pune-chandrakant-patil-reviews-bajirao-peshwa-memorial-work-on-parvati-hill/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Three-Week Monsoon Session of Maharashtra Assembly to Begin on Monday</t>
+          <t>Maharashtra: cabinet sub-committee on Maratha quota reconstituted; Vikhe Patil new head</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/three-week-monsoon-session-of-maharashtra-assembly-to-begin-on-monday-1887745</t>
+          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wonder if some forces are working to destabilise Maharashtra: Minister amid Shaktipeeth stir</t>
+          <t>Work on the Triad of Inspection, Action, and Execution for a Traffic-Free Kothrud: Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra:-minister-amid-shaktipeeth-stir/2826353</t>
+          <t>https://punemirror.com/city/civic/work-on-the-triad-of-inspection-action-and-execution-for-a-traffic-free-kothrud-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Patil silent on Bavdhan garbage plant issue in PMC meeting</t>
+          <t>Rift in Maharashtra Congress over ‘little known face’ at helm, Prithviraj Chavan ‘surprised’</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
+          <t>https://indianexpress.com/article/political-pulse/rift-in-maharashtra-congress-over-little-known-face-at-helm-prithviraj-chavan-surprised-9838116/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Maharashtra: cabinet sub-committee on Maratha quota reconstituted; Vikhe Patil new head</t>
+          <t>State adds fourth CAP round for engineering admissions to curb costly pvt options | Mumbai news</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Work on the Triad of Inspection, Action, and Execution for a Traffic-Free Kothrud: Minister Chandrakant Patil</t>
+          <t>Mandrem Police Arrest Man for Brutally Assaulting Mother in Pernem</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/work-on-the-triad-of-inspection-action-and-execution-for-a-traffic-free-kothrud-minister-chandrakant-patil/</t>
+          <t>https://www.heraldgoa.in/goa/goa/mandrem-police-arrest-man-for-brutally-assaulting-mother-in-pernem/423993</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Rift in Maharashtra Congress over ‘little known face’ at helm, Prithviraj Chavan ‘surprised’</t>
+          <t>State may halt admissions to pharmacy colleges flouting norms</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/rift-in-maharashtra-congress-over-little-known-face-at-helm-prithviraj-chavan-surprised-9838116/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>State adds fourth CAP round for engineering admissions to curb costly pvt options | Mumbai news</t>
+          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mandrem Police Arrest Man for Brutally Assaulting Mother in Pernem</t>
+          <t>Pune civic body acts against unauthorised stalls on FC Road</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/goa/goa/mandrem-police-arrest-man-for-brutally-assaulting-mother-in-pernem/423993</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>State may halt admissions to pharmacy colleges flouting norms</t>
+          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
+          <t>BMC to restart withdrawn services by tanker association with police help</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pune civic body acts against unauthorised stalls on FC Road</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
+          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
+          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BMC to restart withdrawn services by tanker association with police help</t>
+          <t>Islampur to be renamed Ishwarpur</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
+          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
+          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
+          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Islampur to be renamed Ishwarpur</t>
+          <t>C R Patil takes charge as Jal Shakti minister</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://www.ptinews.com/story/national/c-r-patil-takes-charge-as-jal-shakti-minister/1575205</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
+          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra cabinet sub-committee on Maratha quota reconstituted Vikhe Patil new head</t>
+          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/22/bes35-mh-maratha-committee.html</t>
+          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
+          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
+          <t>Police bust chain-snatching gang; two held, minor detained</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
+          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
+          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
+          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
+          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
+          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
+          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
+          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
+          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
+          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
+          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Maharashtra State CET Cell Launches visionary initiative ‘CET-ATAL’ Module for Mock Tests</t>
+          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://indiatechnologynews.in/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
+          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
+          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
+          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
+          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Maharashtra: Samajwadi Party’s Abu Azmi suspended from Assembly session for remark about Aurangzeb</t>
+          <t>BJP district rural unit president elected in Kalaburagi</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1079939/maharashtra-samajwadi-partys-abu-azmi-suspended-from-assembly-session-for-remark-about-aurangzeb</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
+          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
+          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
+          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
+          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
+          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BJP district rural unit president elected in Kalaburagi</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces Quantum Computing Training For Over 500 Professors To Boost</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-quantum-computing-training-for-over-500-professors-to-boost-tech-education-under-nep-2020</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
+          <t>Universities Should Implement ‘Carry On’ Scheme For Student Welfare, Says Higher &amp; Technical Education</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
+          <t>https://www.freepressjournal.in/education/universities-should-implement-carry-on-scheme-for-student-welfare-says-higher-technical-education-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
+          <t>Maharashtra Politics: Chandrakant Patil Dismisses Buzz Over NCP Merger, Calls It Pure Speculation</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-chandrakant-patil-dismisses-buzz-over-ncp-merger-calls-it-pure-speculation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>शाश्वत कृषी संजीवनीचे पुस्तकाचे प्रकाशन: चंद्रकांत पाटील यांच्या हस्ते अनावरण, नैसर्गिक शेतीचे महत्त्व पटवू...</t>
+          <t>Pune News: Chandrakant Patil Urges Citizens To Stay Vigilant</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-natural-farming-book-release-135379530.html</t>
+          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces Quantum Computing Training For Over 500 Professors To Boost</t>
+          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-quantum-computing-training-for-over-500-professors-to-boost-tech-education-under-nep-2020</t>
+          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Universities Should Implement ‘Carry On’ Scheme For Student Welfare, Says Higher &amp; Technical Education</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/universities-should-implement-carry-on-scheme-for-student-welfare-says-higher-technical-education-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Chandrakant Patil Dismisses Buzz Over NCP Merger, Calls It Pure Speculation</t>
+          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-chandrakant-patil-dismisses-buzz-over-ncp-merger-calls-it-pure-speculation</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pune News: Chandrakant Patil Urges Citizens To Stay Vigilant</t>
+          <t>Chandrakant Patil Reveals Details Of Vidhan Bhavan Meetings On Pune Municipal Corporation Budget</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
+          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
+          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
+          <t>Ensure Safety Measures For Pune Hills: Higher And Technical Education Minister Chandrakant Patil’s Directives</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Reveals Details Of Vidhan Bhavan Meetings On Pune Municipal Corporation Budget</t>
+          <t>Pune: Chandrakant Patil Warns PMC, Shut Down Sus Waste Project Or Face Protest</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Maratha Quota Controversy: Manoj Jarange's Protest Sparks Government Appeal</t>
+          <t>Pune: Chandrakant Patil Demands Swift Action On City’s Missing Road Link Projects</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/law-order/3601499-maratha-quota-controversy-manoj-jaranges-protest-sparks-government-appeal</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
+          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Demands Swift Action On City’s Missing Road Link Projects</t>
+          <t>No Ajit Pawar vs Chandrakant Patil In Pune: PMC Polls Likely To Be Held Under Leadership Of Muralidhar Mohol</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
+          <t>https://www.freepressjournal.in/pune/no-ajit-pawar-vs-chandrakant-patil-in-pune-pmc-polls-likely-to-be-held-under-leadership-of-muralidhar-mohol</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
+          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
+          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
+          <t>Buldhana Shock: Doctor Dies After Setting Himself on Fire, Motive Still a Mystery</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.lokmattimes.com/maharashtra/buldhana-shock-doctor-dies-after-setting-himself-on-fire-motive-still-a-mystery-a525/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Buldhana Shock: Doctor Dies After Setting Himself on Fire, Motive Still a Mystery</t>
+          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/buldhana-shock-doctor-dies-after-setting-himself-on-fire-motive-still-a-mystery-a525/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
+          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
+          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
+          <t>Pune: Chandrakant Patil Flags PMC Misgovernance Amid Delayed Elections; High-Level Meeting with Ajit Pawar Likely</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
+          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Intensifies Efforts for Girls' Fee Waiver, Plans Surprise Visits to 100 Colleges</t>
+          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-intensifies-efforts-for-girls-fee-waiver-plans-surprise-visits-to-100-colleges/</t>
+          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Flags PMC Misgovernance Amid Delayed Elections; High-Level Meeting with Ajit Pawar Likely</t>
+          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
+          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
+          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
+          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
+          <t>Pune: Chandrakant Patil Promises Full Support for Women Empowerment and Girls’ Education in Mulshi Taluka</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
+          <t>https://www.punekarnews.in/pune-chandrakant-patil-promises-full-support-for-women-empowerment-and-girls-education-in-mulshi-taluka/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
+          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
+          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
+          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
+          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Promises Full Support for Women Empowerment and Girls’ Education in Mulshi Taluka</t>
+          <t>NCTE Cancels Recognition Of 16 B.Ed. Colleges In Maharashtra: Minister Chandrakant Patil (Video)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-promises-full-support-for-women-empowerment-and-girls-education-in-mulshi-taluka/</t>
+          <t>https://www.freepressjournal.in/education/ncte-cancels-recognition-of-16-bed-colleges-in-maharashtra-minister-chandrakant-patil-video</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
+          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
+          <t>Delay In Pune's Equal Water Supply Scheme Sparks Public Discontent; MLA Chandrakant Patil Criticizes PMC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
+          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NCTE Cancels Recognition Of 16 B.Ed. Colleges In Maharashtra: Minister Chandrakant Patil (Video)</t>
+          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/ncte-cancels-recognition-of-16-bed-colleges-in-maharashtra-minister-chandrakant-patil-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
+          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Delay In Pune's Equal Water Supply Scheme Sparks Public Discontent; MLA Chandrakant Patil Criticizes PMC</t>
+          <t>Wonder if some forces are working to destabilise Maharashtra: Minister amid Shaktipeeth stir</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
+          <t>https://www.newsdrum.in/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra-minister-amid-shaktipeeth-stir-9664386</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
+          <t>'To Prevent Malpractices': Maharashtra Minister Says CET Exam Not To Be Held Outside State</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
+          <t>https://www.thedailyjagran.com/maharashtra/to-prevent-malpractices-maharashtra-minister-says-cet-exam-not-to-be-held-outside-state-10243139</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
+          <t>Maharashtra Assembly Monsoon Session: Opposition Raises Alarm Over Poor Living Conditions At Mumbai</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-assembly-monsoon-session-opposition-raises-alarm-over-poor-living-conditions-at-mumbai-universitys-cama-girls-hostel-govt-denies-lapses</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Wonder if some forces are working to destabilise Maharashtra: Minister amid Shaktipeeth stir</t>
+          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra-minister-amid-shaktipeeth-stir-9664386</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>“Society is Responsible for Keeping Every Person Alive” – CM Devendra Fadnavis at Guinness World Record Event in Pune</t>
+          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>'To Prevent Malpractices': Maharashtra Minister Says CET Exam Not To Be Held Outside State</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/to-prevent-malpractices-maharashtra-minister-says-cet-exam-not-to-be-held-outside-state-10243139</t>
+          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Maharashtra Assembly Monsoon Session: Opposition Raises Alarm Over Poor Living Conditions At Mumbai</t>
+          <t>CET Exams to Be Held Only Within Maharashtra</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-assembly-monsoon-session-opposition-raises-alarm-over-poor-living-conditions-at-mumbai-universitys-cama-girls-hostel-govt-denies-lapses</t>
+          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
+          <t>“Society is Responsible for Keeping Every Person Alive” – CM Devendra Fadnavis at Guinness World Record Event in Pune</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
+          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Maharashtra: Over 1,600 EWS Students Granted Special Exemption For Certificate Submission</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-over-1600-ews-students-granted-special-exemption-for-certificate-submission</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
+          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CET Exams to Be Held Only Within Maharashtra</t>
+          <t>CAP: Maharashtra to Introduce Four Rounds in Centralised Engineering Admissions; Stricter Seat Allotment Rules Planned</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://www.punekarnews.in/cap-maharashtra-to-introduce-four-rounds-in-centralised-engineering-admissions-stricter-seat-allotment-rules-planned/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 1,600 EWS Students Granted Special Exemption For Certificate Submission</t>
+          <t>VIDEO I Attention Punekars! Two Municipal Corporations In Pune Soon With PMC Bifurcation—Read Details Here</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-over-1600-ews-students-granted-special-exemption-for-certificate-submission</t>
+          <t>https://www.freepressjournal.in/pune/video-i-attention-punekars-two-municipal-corporations-in-pune-soon-with-pmc-bifurcationread-details-here</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
+          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
+          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CAP: Maharashtra to Introduce Four Rounds in Centralised Engineering Admissions; Stricter Seat Allotment Rules Planned</t>
+          <t>Mr. Sunjjoy Chaudhri Leads Team Veer Santaji at Khasdar Celebrity Cricket League 2025, Celebrating Pune’s Grand Festival with Support from Mr. Murlidhar Mohol and Mr. Chandrakant Patil</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cap-maharashtra-to-introduce-four-rounds-in-centralised-engineering-admissions-stricter-seat-allotment-rules-planned/</t>
+          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VIDEO I Attention Punekars! Two Municipal Corporations In Pune Soon With PMC Bifurcation—Read Details Here</t>
+          <t>Pune: Defence Minister Rajnath Singh Likely to Inaugurate Peshwa Memorial at Parvati Hill</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/video-i-attention-punekars-two-municipal-corporations-in-pune-soon-with-pmc-bifurcationread-details-here</t>
+          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
+          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mr. Sunjjoy Chaudhri Leads Team Veer Santaji at Khasdar Celebrity Cricket League 2025, Celebrating Pune’s Grand Festival with Support from Mr. Murlidhar Mohol and Mr. Chandrakant Patil</t>
+          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
+          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Pune: Defence Minister Rajnath Singh Likely to Inaugurate Peshwa Memorial at Parvati Hill</t>
+          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
+          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
+          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
+          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
+          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
+          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा</t>
+          <t>सांगलीचे अपक्ष खासदार विशाल पाटील यांना चंद्रकांत पाटील यांच्याकडून खुली ऑफर</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://www.jaimaharashtranews.com/politics/chandrakant-patil-makes-an-open-offer-to-sangli-independent-mp-vishal-patil-to-join-bjp/34589</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील म्हणतात… करोनाची लस घेतल्याचे साईड इफेक्ट…</t>
+          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/chandrakant-patil-statement-regarding-the-tribute-to-ramdas-ambatkar-corona-vaccine-mnb-82-amy-95-5081710/</t>
+          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
+          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांना हवंय देवेंद्र फडणवीसांचं पद? थेट म्हणाले, सर्व मंत्रिपदं भूषवली आता फक्त…</t>
+          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-i-am-senior-minister-only-home-minister-department-is-remain-1389806.html</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>सांगलीचे अपक्ष खासदार विशाल पाटील यांना चंद्रकांत पाटील यांच्याकडून खुली ऑफर</t>
+          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/chandrakant-patil-makes-an-open-offer-to-sangli-independent-mp-vishal-patil-to-join-bjp/34589</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
+          <t>चंद्रकांत पाटलांना हवंय देवेंद्र फडणवीसांचं पद? थेट म्हणाले, सर्व मंत्रिपदं भूषवली आता फक्त…</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-i-am-senior-minister-only-home-minister-department-is-remain-1389806.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>Chandrakant patil: एकनाथ शिंदेकडे 75 नगरसेवक गेलेत, आता मुंबई महापालिकेसाठी राज ठाकरे राजकीय</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
+          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>विशाल पाटील कसे विजयी झाले हे जाहीरपणे सांगू शकत नाही : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-cannot-reveal-how-vishal-patil-won-dc95</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Chandrakant patil: एकनाथ शिंदेकडे 75 नगरसेवक गेलेत, आता मुंबई महापालिकेसाठी राज ठाकरे राजकीय</t>
+          <t>उच्च व तंत्रशिक्षण मंत्र्यांच्या घरातील कपाटांमध्ये…; स्वतः चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
+          <t>https://www.loksatta.com/pune/akshardhara-book-gallery-maruti-chitampally-literature-gallery-inaugurated-chandrakant-patil-pune-print-news-ssb-93-5260696/</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
+          <t>केंद्रीय मंत्री रक्षा खडसे यांच्या मुलीची छेड, शिंदे सेनेचे आमदार चंद्रकांत पाटील यांनी मौन सोडले,...</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
+          <t>मग युती कधी? उद्धव ठाकरेंसमोर मिलिंद नार्वेकरांची गुगली, मी सुद्धा या सुवर्णक्षणाची</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>विशाल पाटील कसे विजयी झाले हे जाहीरपणे सांगू शकत नाही : चंद्रकांत पाटील</t>
+          <t>आंदोलनाचा प्रत्येकाला अधिकार, मात्र मार्ग सनदशीर नसल्यास कारवाई; चंद्रकांत पाटील यांचा इशारा…</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-cannot-reveal-how-vishal-patil-won-dc95</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-warns-against-illegal-protests-ocd-94-5326788/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>केंद्रीय मंत्री रक्षा खडसे यांच्या मुलीची छेड, शिंदे सेनेचे आमदार चंद्रकांत पाटील यांनी मौन सोडले,...</t>
+          <t>Chandrakant Patil Shiv Sena On Raksha Khadse Daughter | शिवसेना आमदार चंद्रकांत पाटील यांच्या कार्यकर्त्यांकडून छेडछाड? पाटील स्पष्टच बोलले..</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
+          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>मग युती कधी? उद्धव ठाकरेंसमोर मिलिंद नार्वेकरांची गुगली, मी सुद्धा या सुवर्णक्षणाची</t>
+          <t>Chandrakant Patil: “… तर मुख्यमंत्री धनंजय मुंडेंना राजीनामा द्यायला सांगतील”, चंद्रकांत पाटील यांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-chandrakant-patil-reaction-on-dhananjay-munde-ministerial-post-says-cm-will-take-decision-on-resignation-kvg-85-4850775/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>उच्च व तंत्रशिक्षण मंत्र्यांच्या घरातील कपाटांमध्ये…; स्वतः चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>पत्रकारांच्या मुला-मुलींच्या करिअर अन् कुटुंबाच्या आरोग्यासाठी मोठं पाऊल</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/akshardhara-book-gallery-maruti-chitampally-literature-gallery-inaugurated-chandrakant-patil-pune-print-news-ssb-93-5260696/</t>
+          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Shiv Sena On Raksha Khadse Daughter | शिवसेना आमदार चंद्रकांत पाटील यांच्या कार्यकर्त्यांकडून छेडछाड? पाटील स्पष्टच बोलले..</t>
+          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
+          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>आंदोलनाचा प्रत्येकाला अधिकार, मात्र मार्ग सनदशीर नसल्यास कारवाई; चंद्रकांत पाटील यांचा इशारा…</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-warns-against-illegal-protests-ocd-94-5326788/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>पत्रकारांच्या मुला-मुलींच्या करिअर अन् कुटुंबाच्या आरोग्यासाठी मोठं पाऊल</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
+          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: “… तर मुख्यमंत्री धनंजय मुंडेंना राजीनामा द्यायला सांगतील”, चंद्रकांत पाटील यांचं मोठं विधान</t>
+          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-chandrakant-patil-reaction-on-dhananjay-munde-ministerial-post-says-cm-will-take-decision-on-resignation-kvg-85-4850775/</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
+          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>नाविन्यपूर्ण उपक्रमांसाठी जिल्हा परिषदेच्या पाठीशी राहू – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170695/</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
+          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
+          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
+          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
+          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
+          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
+          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
+          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
+          <t>https://mahasamvad.in/172941/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
+          <t>सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
+          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
+          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
+          <t>https://mahasamvad.in/174837/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
+          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
+          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172941/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ चंद्रकांत पाटील</t>
+          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
+          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
+          <t>कानडवाडी येथील १० एम.व्ही.ए. पॉवर ट्रान्सफॉर्मरचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
+          <t>https://mahasamvad.in/175996/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
+          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174837/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
+          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
+          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>कानडवाडी येथील १० एम.व्ही.ए. पॉवर ट्रान्सफॉर्मरचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
+          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175996/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
+          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
+          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
+          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
+          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
+          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
+          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
+          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
+          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
+          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
+          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
+          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
+          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>राज्यात दोन हजार नवीन ग्रंथालये : उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/two-thousand-new-libraries-in-maharashtra-announces-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
+          <t>हात जोडतो, नसते वाद काढू नका!वाघ्या कुत्र्याच्या समाधीवरून चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-appeal-over-tomb-of-tiger-dog-controversy-zws-70-4983085/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
+          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
+          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
+          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
+          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>समडोळी रोड घनकचरा प्रकल्प येथील बायो-मिथनायझेन प्रकल्पाचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175942/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>हात जोडतो, नसते वाद काढू नका!वाघ्या कुत्र्याच्या समाधीवरून चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-appeal-over-tomb-of-tiger-dog-controversy-zws-70-4983085/</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
+          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
+          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
+          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
+          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
+          <t>क्वांटम संगणन उपक्रमाच्या माध्यमातून प्राध्यापकांना प्रशिक्षण – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://www.mahasamvad.in/169422/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
+          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
+          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
+          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटील म्हणतात, भारतीय जनता पार्टीच्या नेत्यांनी धंगेकरांना घेण्याचा निर्णय केला असता तर…</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
+          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>क्वांटम संगणन उपक्रमाच्या माध्यमातून प्राध्यापकांना प्रशिक्षण – मंत्री चंद्रकांत पाटील</t>
+          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
+          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
+          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
+          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील म्हणतात, भारतीय जनता पार्टीच्या नेत्यांनी धंगेकरांना घेण्याचा निर्णय केला असता तर…</t>
+          <t>पुण्यात वारकऱ्यांसाठी ‘फिरता दवाखाना’; मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
+          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
+          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
+          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
+          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
+          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
+          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
+          <t>सीमाप्रश्नी चंद्रकांत पाटील, शंभूराज देसाई पुन्हा समन्वयकमंत्री</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-shambhuraj-desai-reappointed-border-issue-coordination-ministers</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>पुण्यात वारकऱ्यांसाठी ‘फिरता दवाखाना’; मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : शिक्षकांनी गुरूंचे स्थान उंचावले पाहिजे, चंद्रकांत पाटील यांचे मत; विकसित भारताबाबत परिसंवाद</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-emphasizes-role-of-education-in-building-developed-india-by-2047-amp17</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
+          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
+          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
+          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>सीमाप्रश्नी चंद्रकांत पाटील, शंभूराज देसाई पुन्हा समन्वयकमंत्री</t>
+          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-shambhuraj-desai-reappointed-border-issue-coordination-ministers</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
+          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>मुक्ताईनगरमध्ये आंदोलन तीव्र; शिंदे गटाचे आमदार चंद्रकांत पाटील, शेतकरी पोलिसांच्या ताब्यात</t>
+          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/jalgaon/protests-intensify-in-muktainagar-shinde-group-mla-chandrakant-patil-and-farmers-in-police-custody-a-a747/</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
+          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
+          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>सांगली महापालिकेत महायुतीचाच झेंडा फडकणार, ६५ जागा जिंकू; पालकमंत्री चंद्रकांत पाटील यांचा विश्वास</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/the-flag-of-the-mahayuti-will-fly-in-the-municipal-corporation-we-will-win-65-seats-guardian-minister-chandrakant-patil-is-confident-a-a746/</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
+          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
+          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शिक्षकांनी गुरूंचे स्थान उंचावले पाहिजे, चंद्रकांत पाटील यांचे मत; विकसित भारताबाबत परिसंवाद</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-emphasizes-role-of-education-in-building-developed-india-by-2047-amp17</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
+          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
+          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
+          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>'महाराष्ट्र एज्युकेशन अँड कॉर्पोरेट आयकॉन्स 2025' सन्मान सोहळा: उद्योग आणि शिक्षण संस्थांमधील परस्पर समन्वय...</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/education-industry-collaboration-essential-skilled-workforce-chandrakant-patil-135447177.html</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
+          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटलांकडून अपक्ष खासदाराला खुली ऑफर: म्हणाले - विशाल पाटील सोबत आल्यास सांगलीच्या विकासाला गती मि...</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-134651805.html</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
+          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
+          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
+          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>'महाराष्ट्र एज्युकेशन अँड कॉर्पोरेट आयकॉन्स 2025' सन्मान सोहळा: उद्योग आणि शिक्षण संस्थांमधील परस्पर समन्वय...</t>
+          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/education-industry-collaboration-essential-skilled-workforce-chandrakant-patil-135447177.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
+          <t>उच्च व तंत्र शिक्षण विभागातील प्रलंबित प्रकरणे वेळेत निकाली काढा – मंत्री चंद्रकांत (दादा) पाटील</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
+          <t>https://mahasamvad.in/154565/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
+          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांकडून अपक्ष खासदाराला खुली ऑफर: म्हणाले - विशाल पाटील सोबत आल्यास सांगलीच्या विकासाला गती मि...</t>
+          <t>मुंबईकडे कूच नको, कागद-पेन घ्या अन् चर्चेला या: शांततेने मागण्या मांडल्या तर सरकार ऐकेल, चंद्रकांत पाटलांचा...</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-134651805.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/manoj-jarange-protest-warning-chandrakant-patil-135741950.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
+          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
+          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
+          <t>शाश्वत कृषी संजीवनीचे पुस्तकाचे प्रकाशन: चंद्रकांत पाटील यांच्या हस्ते अनावरण, नैसर्गिक शेतीचे महत्त्व पटवू...</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-natural-farming-book-release-135379530.html</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
+          <t>आम्ही काही सोन्याचा चमचा घेऊन जन्माला आलोय असं नाही… अजित पवार यांचा चंद्रकांतदादांना टोला</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
+          <t>https://www.tv9marathi.com/maharashtra/ajit-pawars-attack-on-chandrakant-patil-in-islampur-1471041.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
+          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
+          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>मुंबईकडे कूच नको, कागद-पेन घ्या अन् चर्चेला या: शांततेने मागण्या मांडल्या तर सरकार ऐकेल, चंद्रकांत पाटलांचा...</t>
+          <t>Jayshree Patil : जयश्री पाटलांना भाजपचे रिटर्न गिफ्ट! प्रवेशाच्या आधीच चंद्रकांत पाटलांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/manoj-jarange-protest-warning-chandrakant-patil-135741950.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jayshree-patil-joins-bjp-and-appointed-to-sangli-district-planning-committee-by-chandrakant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
+          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
+          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
+          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
+          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
+          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>आम्ही काही सोन्याचा चमचा घेऊन जन्माला आलोय असं नाही… अजित पवार यांचा चंद्रकांतदादांना टोला</t>
+          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ajit-pawars-attack-on-chandrakant-patil-in-islampur-1471041.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>अशी दादागिरी चालणार नाही, चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, बाधित म्हणाले तुम्हाला टाहो फोडून</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-and-farmers-came-face-to-face-over-shaktipith-highway/903727</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : फडणवीस यांचा आदेश येऊ द्या... जयंत पाटील यांना भाजपमध्ये आणण्यासाठी मी स्वतः जाईल!</t>
+          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jayant-patil-bjp-entry-speculation-after-chandrakant-patils-statement-as11</t>
+          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Jayshree Patil : जयश्री पाटलांना भाजपचे रिटर्न गिफ्ट! प्रवेशाच्या आधीच चंद्रकांत पाटलांची मोठी घोषणा</t>
+          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jayshree-patil-joins-bjp-and-appointed-to-sangli-district-planning-committee-by-chandrakant-patil-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
+          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
+          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
+          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
+          <t>कोल्हापुरातील शिवाजी विद्यापीठाचे उपकेंद्र खानापुरात, मंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
+          <t>https://www.lokmat.com/sangli/shivaji-university-sub-centre-to-be-set-up-in-khanapur-announced-by-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
+          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
+          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
+          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
+          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>अशी दादागिरी चालणार नाही, चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, बाधित म्हणाले तुम्हाला टाहो फोडून</t>
+          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-and-farmers-came-face-to-face-over-shaktipith-highway/903727</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
+          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
+          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
+          <t>Chandrakant Patil : जन्मभूमीतच दादांचा करिष्मा ओसरला, भाजपचे पदाधिकारी शोधण्याची वेळ</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/no-bjp-celebration-for-minister-chandrakant-patil-birthday-this-year-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
+          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
+          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
+          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
+          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : जन्मभूमीतच दादांचा करिष्मा ओसरला, भाजपचे पदाधिकारी शोधण्याची वेळ</t>
+          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/no-bjp-celebration-for-minister-chandrakant-patil-birthday-this-year-as11-rg93</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: डिसेंबरपर्यंत अनुकंपा तत्त्वावरील सर्व भरती करणार; उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची ग्वाही</t>
+          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/amravati-university-completes-compassionate-appointment-by-december-says-minister-chandrakant-patil-vsb99</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Chandrakant Patil : झेडपी अध्यक्ष अन् महापालिकेत महापौर भाजपचाच; स्थानिकच्या निवडणुकांसाठी चंद्रकांत पाटलांनी सांगितली व्यूहरचना</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-local-elections-bjp-mahayuti-strategy-chandrakant-patil-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
+          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
+          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
+          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
+          <t>Chandrakant Patil : शक्तिपीठ बाधित शेतकऱ्यांना भरपाई मिळणार? काय म्हणाले चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
+          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : झेडपी अध्यक्ष अन् महापालिकेत महापौर भाजपचाच; स्थानिकच्या निवडणुकांसाठी चंद्रकांत पाटलांनी सांगितली व्यूहरचना</t>
+          <t>Chandrakant Patil : मुंबई तोडण्याची ताकद कोणात नाही, चंद्रकांत पाटलांचा ठाकरेंवर निशाणा</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-local-elections-bjp-mahayuti-strategy-chandrakant-patil-jap93-rg93</t>
+          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
+          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
+          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
+          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यास शासन सकारात्मक; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-library-grant-increase-40-percent-chandrakant-patil-assurance</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शक्तिपीठ बाधित शेतकऱ्यांना भरपाई मिळणार? काय म्हणाले चंद्रकांत पाटील</t>
+          <t>Agriculture Crisis: कृषी पदवीधरांनी शेतीकडे पाठ फिरविणे चिंतेचे : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
+          <t>https://agrowon.esakal.com/agro-special/concern-over-agriculture-graduates-turning-their-backs-on-farming-chandrakant-patil-rat16</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
+          <t>Chandrakant Patil: 'अमित शहांना भेटण्यासाठी आधी लोक माझ्याकडे पाहायचे, पण आता मलाही...'; चंद्रकांतदादांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-says-he-now-needs-to-coordinate-with-murlidhar-mohol-to-reach-amit-shah-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मुंबई तोडण्याची ताकद कोणात नाही, चंद्रकांत पाटलांचा ठाकरेंवर निशाणा</t>
+          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
+          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
+          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : चंद्रकांतदादांची 'ऑफर' अन् विशाल पाटलांकडून भाजपला सुखावणारं 'बंपर' उत्तर; खासदार पाटील म्हणाले?</t>
+          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-offered-mp-vishal-patil-to-join-bjp-bam92</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
+          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यास शासन सकारात्मक; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांचे आश्वासन</t>
+          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-library-grant-increase-40-percent-chandrakant-patil-assurance</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Agriculture Crisis: कृषी पदवीधरांनी शेतीकडे पाठ फिरविणे चिंतेचे : चंद्रकांत पाटील</t>
+          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/concern-over-agriculture-graduates-turning-their-backs-on-farming-chandrakant-patil-rat16</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: 'अमित शहांना भेटण्यासाठी आधी लोक माझ्याकडे पाहायचे, पण आता मलाही...'; चंद्रकांतदादांचं मोठं विधान</t>
+          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-says-he-now-needs-to-coordinate-with-murlidhar-mohol-to-reach-amit-shah-dk88-sm89</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
+          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>गोगावलेंची पूजा जनतेच्या कल्याणासाठी, अघोरी पूजेच्या आरोपांच्या वादात चंद्रकांत पाटलांची उडी</t>
+          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-supports-bharat-gogawale-after-allegations-of-aghori-puja/916805</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
+          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
+          <t>Chandrakant Patil : राज ठाकरे चांगले नेते पण जरा समजून घेतलं पाहिजे आणि… हिंदी सक्तीवरून...</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
+          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
+          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
+          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
+          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
+          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
+          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
+          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
+          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>छत्रपती शिवाजी महाराज यांच्या पुण्यतिथी कार्यक्रम तयारीचा उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
+          <t>Mohite Patil : भाजपच्या निमंत्रण पत्रिकेतून मोहिते पाटलांना डावलले; विमान कंपनीच्या पत्रिकेत मात्र सर्वांची नावे</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ranjitsinh-mohite-patils-name-omitted-from-bjps-invitation-letter-for-solapur-air-service-vd83</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
+          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
+          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
+          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>MHT CET 2025: एमएचटी-सीईटी परीक्षेत त्रुटी; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची कबुली</t>
+          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-exam-21-incorrect-questions-in-math-exam-paper-minister-chandrakant-patils-admission/articleshow/122223140.cms</t>
+          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
+          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
+          <t>Sanjay Raut : “सत्तेसाठी अमित शाह यांचे पाय चाटणार नाही, उद्धव ठाकरे…”, संजय राऊत यांचं चंद्रकांत पाटील यांना उत्तर</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-strong-answer-to-chandrkant-patil-over-his-statement-over-uddhav-thackeray-also-criticized-amit-shah-scj-81-5018633/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
+          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Mohite Patil : भाजपच्या निमंत्रण पत्रिकेतून मोहिते पाटलांना डावलले; विमान कंपनीच्या पत्रिकेत मात्र सर्वांची नावे</t>
+          <t>मराठा आरक्षण उपसमितीच्या अध्यक्षपदी राधाकृष्ण विखे-पाटील</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ranjitsinh-mohite-patils-name-omitted-from-bjps-invitation-letter-for-solapur-air-service-vd83</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/radhakrishna-vikhe-patil-appointed-maratha-reservation-subcommittee-chairman</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
+          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
+          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
+          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
+          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
+          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
+          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
+          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
+          <t>‘बी.फार्म’ आणि ‘डी.फार्म’ अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
+          <t>https://mahasamvad.in/173736/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Sanjay Raut : “सत्तेसाठी अमित शाह यांचे पाय चाटणार नाही, उद्धव ठाकरे…”, संजय राऊत यांचं चंद्रकांत पाटील यांना उत्तर</t>
+          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-strong-answer-to-chandrkant-patil-over-his-statement-over-uddhav-thackeray-also-criticized-amit-shah-scj-81-5018633/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
+          <t>मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
+          <t>https://mahasamvad.in/169668/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>पोलीस दलातील १६ अधिकारी, कर्मचाऱ्यांना प्रत्येकी २५ हजाराचे बक्षीस</t>
+          <t>‘कमवा व शिका’ योजनेतील विद्यार्थिनींना अधिकच्या अडीच हजार निधीसाठी प्रयत्न</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169297/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shivaji-universitys-east-west-campus-subway-inauguration</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
+          <t>जयश्री पाटलांच्या भाजप प्रवेशावर शिक्कामोर्तब; फडणवीसांच्या उपस्थितीत हाती घेणार कमळ</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
+          <t>राज्यातील प्राचार्यांसाठी आनंदाची बातमी ! निवृत्तीचे वय 62 वरून लवकरच होणार 65 वर; उच्च शिक्षणमंत्र्यांचे महत्त्वपूर्ण संकेत</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
+          <t>https://www.navarashtra.com/maharashtra/retirement-age-of-principals-may-be-raised-from-62-to-65-says-minister-chandrakant-patil-941276.html</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
+          <t>Vishal Patil : ‘आमचं काय व्हायचं ते होऊ दे, तुरुंगात जायचीही तयारी; पण...’; भाजप प्रवेशाबाबत विशाल पाटलांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
+          <t>https://www.navarashtra.com/maharashtra/mp-vishal-patil-big-staatment-on-bjp-joining-chandrakant-patilo-offer-911751.html</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
+          <t>BJP Pune Meeting : मेधा कुलकर्णी उठून गेल्या, चंद्रकांतदादा-मोहळांकडून महिला आघाडीच्या आंदोलनाचं समर्थन; भाजप बैठकीत नेमकं काय घडलं?</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt?page=2</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
+          <t>CET Exam | एकसमान अभ्यासक्रमांसाठी एकच सीईटी</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
+          <t>https://pudhari.news/maharashtra/solapur/single-cet-for-uniform-curriculum-sk95</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
+          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>‘बी.फार्म’ आणि ‘डी.फार्म’ अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
+          <t>सांगली जिल्ह्याच्या विकासासाठी ५४५ कोटींचा आराखडा - पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173736/</t>
+          <t>https://www.lokmat.com/sangli/rs-545-crore-plan-for-the-development-of-sangli-district-says-guardian-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
+          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
+          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>जयश्री पाटलांच्या भाजप प्रवेशावर शिक्कामोर्तब; फडणवीसांच्या उपस्थितीत हाती घेणार कमळ</t>
+          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>‘कमवा व शिका’ योजनेतील विद्यार्थिनींना अधिकच्या अडीच हजार निधीसाठी प्रयत्न</t>
+          <t>Shaktipeeth Highway: शक्तिपीठ महामार्गाला विरोध, शेतकऱ्यांनी ताकद दाखवली, मंत्री चंद्रकांत पाटलांना घेरलं</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shivaji-universitys-east-west-campus-subway-inauguration</t>
+          <t>https://saamtv.esakal.com/maharashtra/clash-between-minister-chandrakant-patil-and-protesters-over-shaktipith-highway-sangli-latest-news-bdk97</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा</t>
+          <t>पुण्यात सामाजिक कार्याचा गौरव, पत्रकारांच्या पाल्ल्यांसाठी 'प्रतिबिंब प्रतिष्ठान'</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169668/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>राज्यातील प्राचार्यांसाठी आनंदाची बातमी ! निवृत्तीचे वय 62 वरून लवकरच होणार 65 वर; उच्च शिक्षणमंत्र्यांचे महत्त्वपूर्ण संकेत</t>
+          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/retirement-age-of-principals-may-be-raised-from-62-to-65-says-minister-chandrakant-patil-941276.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Vishal Patil : ‘आमचं काय व्हायचं ते होऊ दे, तुरुंगात जायचीही तयारी; पण...’; भाजप प्रवेशाबाबत विशाल पाटलांचं मोठं विधान</t>
+          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mp-vishal-patil-big-staatment-on-bjp-joining-chandrakant-patilo-offer-911751.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BJP Pune Meeting : मेधा कुलकर्णी उठून गेल्या, चंद्रकांतदादा-मोहळांकडून महिला आघाडीच्या आंदोलनाचं समर्थन; भाजप बैठकीत नेमकं काय घडलं?</t>
+          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
+          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
+          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
+          <t>https://mahasamvad.in/163883/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>CET Exam | एकसमान अभ्यासक्रमांसाठी एकच सीईटी</t>
+          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/single-cet-for-uniform-curriculum-sk95</t>
+          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ajit Pawar-Jayant Patil At Sangli : सांगलीत अजितदादा-जयंत पाटील एकत्र; विकास कामांचे उद्घाटन करणार</t>
+          <t>जयश्री पाटील भाजपसोबत जाणे अनैसर्गिक युती : विशाल पाटील</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/ajitdada-jayant-patil-together-in-sangli-will-inaugurate-development-works</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-joining-bjp-an-unnatural-alliance-says-vishal-patil-dc95</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
+          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
+          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
+          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
+          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
+          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
+          <t>मोठी बातमी, मराठा आरक्षण उपसमितीचं अध्यक्षपद राधाकृष्ण विखे पाटील यांच्याकडे,</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
+          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
+          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
+          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
+          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
+          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
+          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>मोठी बातमी, मराठा आरक्षण उपसमितीचं अध्यक्षपद राधाकृष्ण विखे पाटील यांच्याकडे,</t>
+          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
+          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
+          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
+          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
+          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
+          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
+          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>जयश्री पाटील भाजपसोबत जाणे अनैसर्गिक युती : विशाल पाटील</t>
+          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-joining-bjp-an-unnatural-alliance-says-vishal-patil-dc95</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
+          <t>Chandrakant Patil: पालकमंत्र्यांनी साधला पूरग्रस्त कुटुंबांशी संवाद, मदत करण्याचे अश्वासन</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
+          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
+          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
+          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
+          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
+          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
+          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
+          <t>Sharad Lad | ‘पदवीधर’साठी भाजपकडून शरद लाड?</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
+          <t>https://pudhari.news/maharashtra/sangali/will-bjp-nominate-sharad-lad-for-graduate-constituency-sk95</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
+          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
+          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
+          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
+          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
+          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
+          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
+          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: पालकमंत्र्यांनी साधला पूरग्रस्त कुटुंबांशी संवाद, मदत करण्याचे अश्वासन</t>
+          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Gopichand Padalkar : मंत्री झाले आता महायुतीचा आमदारही गोत्यात? देवालाही सोडलं नाही, 34 एकर जमीन लाटल्याचा आरोप</t>
+          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-mla-gopichand-padalkar-accused-of-grabbing-aundh-temple-land-by-activist-ram-khade-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
+          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
+          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
+          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
+          <t>Sangli Politics: मलाही मंत्री व्हायचंय, भविष्यात काँग्रेससोबत राहीन असे नाही; विशाल पाटलांच्या विधानाने खळबळ</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
+          <t>https://www.lokmat.com/sangli/i-will-join-some-other-party-in-the-future-mp-vishal-patil-statement-creates-a-stir-a-a468-c746/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Sharad Lad | ‘पदवीधर’साठी भाजपकडून शरद लाड?</t>
+          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/will-bjp-nominate-sharad-lad-for-graduate-constituency-sk95</t>
+          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
+          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
+          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
+          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
+          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
+          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
+          <t>Devendra Fadnavis | सांगलीतील मोठे घराणे यायचे होते ते आले : मुख्यमंत्री फडणवीस</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-prominent-family-joins-bjp-says-cm-fadnavis-sk95</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
+          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Electronic Cigarette : सांगलीत ई-सिगरेटचा धूर, नशाबाजाराविरोधात कारवाईचा धडाका सुरूच</t>
+          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/police-seize-e-cigarette-stock-in-anti-drug-operation-in-sangli-as11</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Gopichand Padalkar Politics : जिल्हा नियोजन बैठकीत पडळकर-आयुक्त गांधी यांच्यात खडाजंगी? नेमकं कारणं काय?</t>
+          <t>जळगावात महामार्गाचे काम रोखले; शेतकऱ्यांसह शिंदे गटाचे आमदार पोलिसांच्या ताब्यात</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-mla-gopichand-padalkar-vs-sangli-commissioner-gandhi-over-action-on-street-vendors-in-planning-meeting-as11</t>
+          <t>https://www.loksatta.com/nashik/thackeray-group-mlas-including-farmers-taken-into-police-custody-for-blocking-highway-work-in-jalgaon-amy-95-5246634/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
+          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Sangli : परदेशी गुंतवणुकीत महाराष्ट्र देशात प्रथम</t>
+          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/maharashtra-tops-india-in-foreign-investment-says-chandrakant-patil-dc95</t>
+          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
+          <t>Jalgaon News : शेतकऱ्यांसह सत्ताधारी आमदारांचे जलसमाधी आंदोलन</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-news-water-immersion-protest-by-farmers-and-ruling-mlas-ar84</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
+          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
+          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
+          <t>सांगली : जिल्हा विकास योजनांचा 745 कोटींचा आराखडा</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-district-development-plan-745-crore-budget</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
+          <t>Maharashtra Education News | अभियांत्रिकीच्या प्रवेशात आता तीनऐवजी चार ‘कॅप’ फेर्‍या</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-engineering-admission-four-cap-rounds-rule-change-sp96</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
+          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
+          <t>शेत जमिनीचे भूसंपादन करताना शेतकऱ्यांवर अन्याय होणार नाही, याची प्रशासनाने दक्षता घ्यावी - महसूल मंत्री चंद्रशेखर बावनकुळे</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
+          <t>https://mahasamvad.in/171768/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
+          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
+          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
+          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | सांगलीतील मोठे घराणे यायचे होते ते आले : मुख्यमंत्री फडणवीस</t>
+          <t>राज्यात 5,500 प्राध्यापकांची भरती: चंद्रकांत पाटील यांची घोषणा; प्राचार्य फोरम अधिवेशन उद्घाटन</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-prominent-family-joins-bjp-says-cm-fadnavis-sk95</t>
+          <t>https://eduvarta.com/Chandrakant-Patil-announces-recruitment-of-5500-professors-in-the-state</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Annasaheb Dange | माजी मंत्री अण्णासाहेब डांगे यांचा लवकरच भाजपमध्ये प्रवेश</t>
+          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/former-minister-annasaheb-dange-to-join-bjp-soon-sk95</t>
+          <t>https://eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>सासरच्या लोकांसह धर्मगुरूकडून धर्मांतरणासाठी दबाव, छळाला कंटाळून सात महिन्याच्या गर्भवतीची आत्महत्या</t>
+          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
+          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
+          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
+          <t>संजयकाकांसाठी भाजपचे दरवाजे बंद; चंद्रकांत पाटील म्हणाले, आम्ही दुसऱ्या पाटलांमागे</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
+          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
+          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
+          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | वसंतदादा स्मारकाचे काम पूर्ण करणार : देवेंद्र फडणवीस</t>
+          <t>कला पदविका अभ्यासक्रमांसाठी प्रवेश घेण्याचे मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/devendra-fadnavis-to-complete-vasantdada-memorial-sk95</t>
+          <t>https://eduvarta.com/Minister-Chandrakant-Patil--appeal-to-take-admission-in-Arts-Diploma-courses</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
+          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Sharad Lad : शरद लाडही भाजपच्या वाटेवर?</t>
+          <t>Chandrakant Patil</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sharad-lad-on-way-to-join-bjp-sk95</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
+          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>‘मिरज सिव्हिल’मधील दोषींवर कारवाई होईल</t>
+          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/action-against-culprits-in-miraj-hospital-baby-theft-case-ab96</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>34 एकर शेती 100 एकर कशी झाली?: शिंदे गटाच्या नेत्याचा एकनाथ खडसेंना सवाल? खडसेंचाही 120 एकर असल्याचा खोचक ट...</t>
+          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/eknath-shinde-shiv-sena-leader-criticized-eknath-khadse-land-scam-jalgaon-135186839.html</t>
+          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Farmer Loan Waiver : कर्जमाफीसाठी निवडणुकीची वाट पाहताय?; सतेज पाटलांची सरकारवर टिका</t>
+          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/waiting-for-elections-to-waive-farm-loans-satej-patil-slams-maharashtra-govt</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
+          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>सांगली : जिल्हा विकास योजनांचा 745 कोटींचा आराखडा</t>
+          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-district-development-plan-745-crore-budget</t>
+          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
+          <t>Jayshree Patil : सांगलीत कॉँग्रेसला धक्का : वसंतदादा पाटील यांच्या नातसून जयश्री पाटील भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
+          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Maharashtra Education News | अभियांत्रिकीच्या प्रवेशात आता तीनऐवजी चार ‘कॅप’ फेर्‍या</t>
+          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-engineering-admission-four-cap-rounds-rule-change-sp96</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
+          <t>जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
+          <t>https://ratnagirikhabardar.com/news/68678/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
+          <t>दख्खन जत्रेतून स्वयंसहाय्यता बचत गटाच्या महिलांना आर्थिकदृष्ट्या स्वावलंबी होण्यास प्रोत्साहन - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
+          <t>https://www.athawadavishesh.com/34215/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>शेत जमिनीचे भूसंपादन करताना शेतकऱ्यांवर अन्याय होणार नाही, याची प्रशासनाने दक्षता घ्यावी - महसूल मंत्री चंद्रशेखर बावनकुळे</t>
+          <t>अजित पवार म्हणाले, ठीक आहे तो रोहित बघतो घरी गेल्यावर</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://www.marathiebatmya.com/political/ajit-pawar-said-will-see-rohit-pawar-at-home/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Chandrakant Patil On Sanjay Raut | चंद्रकांत पाटलांची संजय राऊतांवर जोरदार टीका</t>
+          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/chandrakant-patil-on-sanjay-raut-chandrakant-patal-s-strong-criticism-of-sanjay-raut-1057460.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकरांनी औंध देवस्थानाची 34 एकर जमीन लाटली कागदपत्रे दाखवत राम खाडेंचा</t>
+          <t>Satara News : आणखी १७ शिक्षकांची दिव्यांग प्रमाणपत्रे अयोग्य; आठ टप्प्यांमध्ये ३७९ जणांची तपासणी</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
+          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
+          <t>Manoj Jarange Patil : मनोज जरांगे पाटील आंदोलनाआधीच सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
+          <t>https://puneprahar.com/2025/08/manoj-jarange-patil-governments-big/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
+          <t>State to conduct second CET, colleges worried about delay in academic year</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>आम्हीही चांदीचा चमचा घेऊन जन्माला आलो नाही', अजित पवारांची चंद्रकांत पाटील यांच्यावर टीका</t>
+          <t>Mahayuti parties battling each other during poaching spree</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/editor-letters/ajit-pawar-criticizes-chandrakant-patil-125081700011_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
@@ -5759,1596 +5759,1416 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>Powerloom body appeals to shun trade with Turkiye &amp; Azerbaijan</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/powerloom-body-appeals-to-shun-trade-with-turkiye-azerbaijan/articleshow/121218402.cms</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Police bust chain-snatching gang; two held, minor detained</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Abu Azmi writes letter to Maharashtra Speaker Rahul Narwekar to revoke his suspension</t>
+          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
+          <t>Jab Baat Desh Ki Ho: Posters Hailing Operation Sindoor Put Up In Kothrud, Resident Urges To Stop Defacing</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://www.freepressjournal.in/pune/jab-baat-desh-ki-ho-posters-hailing-operation-sindoor-put-up-in-kothrud-resident-urges-to-stop-defacing-city</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
+          <t>Good News For Punekars! Both Maharashtra Assembly And Council Deputy Chiefs Now From Pune As Anna Bansode</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
+          <t>https://www.freepressjournal.in/pune/good-news-for-punekars-both-maharashtra-assembly-and-council-deputy-chiefs-now-from-pune-as-anna-bansode-joins-neelam-gorhe</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
+          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
+          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
+          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Sushma Andhare यांच्यामुळे ठाकरेंच्या शिवसेनेत नाराजी? अंधारे बैठकीला येताच चंद्रकांत मोकाटेंचा काढता पाय</t>
+          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/is-sushma-andhare-causing-discontent-in-thackerays-shiv-sena</t>
+          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>रोहित, बघतो तुला घरी गेल्यावर….! काका – पुतणे आणि टोमणे….</t>
+          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
+          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>अजित पवार, चंद्रकांत पाटलांमध्ये जुगलबंदी; सोन्याच्या चमच्यावरुन टोलेबाजी</t>
+          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/chandrakant-patil-ajit-pawar-on-born-with-golden-spoon/933026</t>
+          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
+          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>माजी मुख्यमंत्री वसंतदादा पाटलांची नातसून भाजपमध्ये जाणार: सांगलीत कॉंग्रेसला मोठा धक्का, मुख्यमंत्री देवें...</t>
+          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/kolhapur/news/jayashree-patil-joins-bjp-sangli-congress-setback-135246996.html</t>
+          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>सांगलीत काँग्रेसला मोठा धक्का! खासदार विशाल पाटलांच्या कट्टर समर्थकांचा भाजपात प्रवेश</t>
+          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/big-blow-to-congress-vishal-patil-loyalists-in-sangli-former-mayor-joins-bjp-nck90</t>
+          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>कोथरूडमध्ये उभारणार सुधीर फडके यांचे स्मारक: गदिमांच्या स्मारकाजवळ बाबूजींच्या स्मारकासाठी मंत्री चंद्रकांत...</t>
+          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/kothrud-sudhir-phadke-memorial-proposal-135505418.html</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: मी मंत्री कसा झालो, मलाही कळालं नाही, मुरलीधर मोहोळ यांच्या विधानाने राजकीय वर्तुळात चर्चा|VIDEO</t>
+          <t>पदविका प्रवेशाला १ लाखांहून अधिक विद्यार्थ्यांचा प्रवेश; प्रवेशाला १४ ऑगस्टवरून ४ सप्टेंबरपर्यंत मुदतवाढ</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/murli-mohol-unexpected-union-minister-appointment-pune-mp-bjp-leaders-reactions-om0906</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-diploma-admission-see-surge-chandrakant-patil-announce-deadline-extension-mumbai-print-news-rds-00-5299696/</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
+          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
+          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
+          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
+          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>राज्यात 5,500 प्राध्यापकांची भरती: चंद्रकांत पाटील यांची घोषणा; प्राचार्य फोरम अधिवेशन उद्घाटन</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chandrakant-Patil-announces-recruitment-of-5500-professors-in-the-state</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray : उद्धव ठाकरेंच्या मनात चाललंय तरी काय ? चंद्रकांत पाटील यांची घेतली भेट</t>
+          <t>Double Voting Allegations | Rohini Khadse वर Chandrakant Patil यांचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/uddhav-thackeray-and-bjp-leader-chandrakant-patil-meeting-at-a-wedding-article-117713206</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
+          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
+          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>संजयकाकांसाठी भाजपचे दरवाजे बंद; चंद्रकांत पाटील म्हणाले, आम्ही दुसऱ्या पाटलांमागे</t>
+          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
+          <t>Sharad Lad : शरद लाडही भाजपच्या वाटेवर?</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://pudhari.news/maharashtra/sangali/sharad-lad-on-way-to-join-bjp-sk95</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>कला पदविका अभ्यासक्रमांसाठी प्रवेश घेण्याचे मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Sushma Andhare यांच्यामुळे ठाकरेंच्या शिवसेनेत नाराजी? अंधारे बैठकीला येताच चंद्रकांत मोकाटेंचा काढता पाय</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Minister-Chandrakant-Patil--appeal-to-take-admission-in-Arts-Diploma-courses</t>
+          <t>https://www.lokshahi.com/news/is-sushma-andhare-causing-discontent-in-thackerays-shiv-sena</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
+          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
+          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Chandrakant Patil</t>
+          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
+          <t>गोपीचंद पडळकरांनी औंध देवस्थानाची 34 एकर जमीन लाटली कागदपत्रे दाखवत राम खाडेंचा</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
+          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
+          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
+          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Jayshree Patil : सांगलीत कॉँग्रेसला धक्का : वसंतदादा पाटील यांच्या नातसून जयश्री पाटील भाजपच्या वाटेवर</t>
+          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
+          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
+          <t>‘पुण्यात ११०१ हून अधिक’ दाम्पत्यांकडून सामूहिक रुद्रपूजन</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
+          <t>Abu Azmi writes letter to Maharashtra Speaker Rahul Narwekar to revoke his suspension</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
+          <t>Maharashtra News Updates: “ती महिला स्वत:हून पुड्या काढून देत होती”, प्रांजल खेवलकरांच्या वकिलाचा दावा; सगळंच संशयास्पद असल्याचा युक्तिवाद</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Pharmacy courses: राज्य सरकारने फार्मसी महाविद्यालये का थांबवली? विद्यार्थ्यांचा ओढा कमी होण्याचे कारण काय?</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
+          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>‘चंद्रकांतदादांना अजून पुणेकर कोल्हापूरचेच समजतात’, अजित पवारांनी डिवचले</t>
+          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/punekars-still-consider-chandrakant-dada-to-be-from-kolhapur-ajit-pawar-harsh-comment/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
+          <t>संजय गांधी राष्ट्रीय उद्यानातील अतिक्रमकांचे पुनर्वसन लवकरच पूर्ण होणार – वनमंत्री गणेश नाईक</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://mahasamvad.in/158932/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
+          <t>केसरीचे आधारवड हरपले, केसरीभाऊ पाटील यांचे निधन</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://www.etvbharat.com/mr/!state/kesari-father-in-law-has-been-lost-kesaribhau-patil-passes-away-maharashtra-news-mhs25021502516</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही : चंद्रकांत पाटील</t>
+          <t>5 New Police Stations: शहरात होणार नवीन पाच पोलिस ठाणी; मुख्यमंत्र्यांकडून घोषणा</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/68678/</t>
+          <t>https://pudhari.news/maharashtra/pune/cm-announces-five-new-police-stations-in-the-city-sb97</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Satara News : आणखी १७ शिक्षकांची दिव्यांग प्रमाणपत्रे अयोग्य; आठ टप्प्यांमध्ये ३७९ जणांची तपासणी</t>
+          <t>Sangli News | कवठेमहांकाळ येथे जिल्हा व अतिरिक्त सत्रन्यायालयास उच्च न्यायालयाची मंजुरी</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-news-high-court-approval-for-district-additional-sessions-judge-kavathemahanaghat-sk95</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Creative Foundation Pune | Chandrakant Patil-Sandeep Khardekar</t>
+          <t>Pune Sinhagad Road flyover: सिंहगड रोड उड्डाणपुलावरून आजपासून वाहतूक सुसाट; अजित पवार यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://policenama.com/creative-foundation-pune-creative-foundation-and-mukul-madhav-foundation-donate-useful-items-to-various-organizations-chandrakant-patil/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-sinhagad-road-flyover-inauguration-by-ajit-pawar-sb97</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>दख्खन जत्रेतून स्वयंसहाय्यता बचत गटाच्या महिलांना आर्थिकदृष्ट्या स्वावलंबी होण्यास प्रोत्साहन - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Sangli : ग्रंथालय वाढीव अनुदानात आमचा हिस्सा किती?</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://pudhari.news/maharashtra/sangali/40-percent-hike-in-library-grants-in-maharashtra-dc95</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Sangli Politics : काँग्रेसला खिंडार; पृथ्वीराज पाटील शेकडो समर्थकांसह भाजपात!</t>
+          <t>Yoga Day: भक्ती आणि योगाच्या माध्यमातून आरोग्यदायी समाज निर्मितीसाठी प्रयत्न करूया; देवेंद्र फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
+          <t>https://pudhari.news/maharashtra/pune/let-us-strive-to-create-a-healthy-society-through-bhakti-and-yoga-devendra-fadnavis-appeal-sb97</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>‘पुण्यात ११०१ हून अधिक’ दाम्पत्यांकडून सामूहिक रुद्रपूजन</t>
+          <t>सरकार शब्द फिरवणार नाही, योग्यवेळी कर्जमाफीचा निर्णय घेणार - मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
+          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Manoj Jarange Patil : मनोज जरांगे पाटील आंदोलनाआधीच सरकारचा मोठा निर्णय</t>
+          <t>Devendra Fadnavis : विद्यापीठे, महाविद्यालयांतील रिक्त पदांची भरती होणार, अभियांत्रिकी संस्थांमध्येही पदभरतीस मान्यता, मुख्यमंत्री फडणवीसांचा निर्णय</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/08/manoj-jarange-patil-governments-big/</t>
+          <t>https://www.loksatta.com/maharashtra/recruitment-for-vacant-posts-in-public-universities-and-colleges-100-percent-recruitment-in-engineering-institutes-approved-devendra-fadnavis-decision-gkt-96-5213795/</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
+          <t>Malin Village: दुर्घटनेनंतरही माळीविासीयांना घरांसाठी अडीच वर्षांची प्रतीक्षा; गावकर्‍यांनी अडीच वर्षे काढली पत्राशेडमध्ये</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
+          <t>https://pudhari.news/maharashtra/pune/malin-survivors-homeless-after-2-years-sb97</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Maharashtra News Updates: “ती महिला स्वत:हून पुड्या काढून देत होती”, प्रांजल खेवलकरांच्या वकिलाचा दावा; सगळंच संशयास्पद असल्याचा युक्तिवाद</t>
+          <t>10th Exam Result 2025: ... तर दहावीचा निकाल ठेवला जाणार राखीव; नाशिक विभागातील ६६८ शाळांचे काम अद्याप बाकी</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Pharmacy courses: राज्य सरकारने फार्मसी महाविद्यालये का थांबवली? विद्यार्थ्यांचा ओढा कमी होण्याचे कारण काय?</t>
+          <t>NEET PG Counselling 2024: मेडिकल कौन्सिल कमिटीकडून 'कट ऑफ पर्सेटाइल'मध्ये घट; ५ पसेंटाइल असणारे 'नीट पीजी'साठी पात्र</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
+          <t>MAH CET 2025: बीबीए, बीसीए सीईटीसाठी चार दिवसांत नोंदणी सुरू; उच्च व तंत्रशिक्षण विभागाच्या आदेशानंतर सीईटी कक्षाची तयारी</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
+          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>5 New Police Stations: शहरात होणार नवीन पाच पोलिस ठाणी; मुख्यमंत्र्यांकडून घोषणा</t>
+          <t>Polytechnic | अभियांत्रिकी पदविका प्रवेश अर्ज नोंदणीसाठी आणखी मुदतवाढ, नवीन वेळापत्रक जाहीर - मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/cm-announces-five-new-police-stations-in-the-city-sb97</t>
+          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Sangli News | कवठेमहांकाळ येथे जिल्हा व अतिरिक्त सत्रन्यायालयास उच्च न्यायालयाची मंजुरी</t>
+          <t>घडामोडींना वेग! मनोज जरांगे पाटलांच्या मुंबईतील आंदोलनाचा धसका; फडणवीस सरकारचा 'हा' सर्वात मोठा निर्णय</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-news-high-court-approval-for-district-additional-sessions-judge-kavathemahanaghat-sk95</t>
+          <t>https://mangalwedhatimes.in/maratha-reservation-activist-manoj-jarange-patil-launched-a-major-movement-to-get-reservation-for-maratha-community-decision-of-fadnavis-government/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Pune Sinhagad Road flyover: सिंहगड रोड उड्डाणपुलावरून आजपासून वाहतूक सुसाट; अजित पवार यांच्या हस्ते उद्घाटन</t>
+          <t>Laxman Jagtap: लोकनेते लक्ष्मण जगताप हा प्रेरणादायी अध्याय: उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-sinhagad-road-flyover-inauguration-by-ajit-pawar-sb97</t>
+          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Sangli : ग्रंथालय वाढीव अनुदानात आमचा हिस्सा किती?</t>
+          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/40-percent-hike-in-library-grants-in-maharashtra-dc95</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Yoga Day: भक्ती आणि योगाच्या माध्यमातून आरोग्यदायी समाज निर्मितीसाठी प्रयत्न करूया; देवेंद्र फडणवीस यांचे आवाहन</t>
+          <t>MKCL - Devendra Fadnavis | MKCL's Silver Jubilee Foundation Day</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/let-us-strive-to-create-a-healthy-society-through-bhakti-and-yoga-devendra-fadnavis-appeal-sb97</t>
+          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>सरकार शब्द फिरवणार नाही, योग्यवेळी कर्जमाफीचा निर्णय घेणार - मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
+          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : विद्यापीठे, महाविद्यालयांतील रिक्त पदांची भरती होणार, अभियांत्रिकी संस्थांमध्येही पदभरतीस मान्यता, मुख्यमंत्री फडणवीसांचा निर्णय</t>
+          <t>Pune | हडपसरला नवीन मेट्रो मार्गिका, मुख्य शहराशी कनेक्टिव्हिटी मिळणार असल्याने प्रवास होणार वेगवान...</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/recruitment-for-vacant-posts-in-public-universities-and-colleges-100-percent-recruitment-in-engineering-institutes-approved-devendra-fadnavis-decision-gkt-96-5213795/</t>
+          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Malin Village: दुर्घटनेनंतरही माळीविासीयांना घरांसाठी अडीच वर्षांची प्रतीक्षा; गावकर्‍यांनी अडीच वर्षे काढली पत्राशेडमध्ये</t>
+          <t>राज्यातील ग्रंथालयांसाठी फडणवीस सरकारचा ऐतिहासिक निर्णय : अनुदानात ४०% वाढ</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/malin-survivors-homeless-after-2-years-sb97</t>
+          <t>https://ratnagirikhabardar.com/news/65971/</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Jalgaon Accident: भीषण! एसटी बसचा ब्रेक फेल; नवविवाहित तरुणासह आणखी एकाचा चिरडून मृत्यू, CCTV फुटेज समोर</t>
+          <t>ABP Majha Headlines : 11:00AM : 14 April 2024 : Maharashtra News : एबीपी माझा हेडलाईन्स</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/jalgaon-news/st-bus-brakes-fail-in-chopda-taluka-newlywed-youth-died-in-accident-cctv-footage/articleshow/121291227.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-100-headlines-14-april-2025-marathi-headlines-maharashtra-chandrakant-patil-on-sanjay-raut-1354271</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>10th Exam Result 2025: ... तर दहावीचा निकाल ठेवला जाणार राखीव; नाशिक विभागातील ६६८ शाळांचे काम अद्याप बाकी</t>
+          <t>Sanjay Raut Vs Chandrakant Patil | Special Report | फुले चित्रपटावरुन राऊत-पाटलामध्ये जुंपली</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
+          <t>https://lokmat.news18.com/videos/video/sanjay-raut-vs-chandrakant-patil-special-report-raut-patla-clash-over-phule-movie-1038823.html</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>NEET PG Counselling 2024: मेडिकल कौन्सिल कमिटीकडून 'कट ऑफ पर्सेटाइल'मध्ये घट; ५ पसेंटाइल असणारे 'नीट पीजी'साठी पात्र</t>
+          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>MAH CET 2025: बीबीए, बीसीए सीईटीसाठी चार दिवसांत नोंदणी सुरू; उच्च व तंत्रशिक्षण विभागाच्या आदेशानंतर सीईटी कक्षाची तयारी</t>
+          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
+          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Thane News: ठाणे महापालिका क्षेत्रातील विद्यार्थ्यांचे भवितव्य संकटात! ६८ अनधिकृत शाळांविरोधात FIR</t>
+          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
+          <t>Maharashtra CET Admission 2025: विद्यार्थ्यांसाठी दिलासादायक बातमी! BE/BTech आणि MBA प्रवेशासाठी मुदतवाढ जाहीर</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>घडामोडींना वेग! मनोज जरांगे पाटलांच्या मुंबईतील आंदोलनाचा धसका; फडणवीस सरकारचा 'हा' सर्वात मोठा निर्णय</t>
+          <t>भयंकर शेवट! दिरानेच केला भावजय व तिच्या मित्राचा खून; 'या' कारणांमुळे घडले मंगळवेढ्यातील दुहेरी हत्याकांड</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/maratha-reservation-activist-manoj-jarange-patil-launched-a-major-movement-to-get-reservation-for-maratha-community-decision-of-fadnavis-government/</t>
+          <t>https://mangalwedhatimes.in/seven-people-murder-woman-a-man-over-a-farming-dispute-incident-in-gunjegaon-two-are-undergoing-treatment-in-a-private-hospital-three-are-in-custody/</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>पुण्याला मिळणार ५ नवीन पोलीस स्टेशन अन् १०० अतिरिक्त पोलीस बळ</t>
+          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/city/pune/big-announcement-for-pune-police-will-get-5-new-police-stations-and-1000-additional-police-force/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
+          <t>Maharashtra cites poor standards, proposes no new pharmacy colleges for 5 years | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-cites-poor-standards-proposes-no-new-pharmacy-colleges-for-5-years-101750656728006.html</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>MKCL - Devendra Fadnavis | MKCL's Silver Jubilee Foundation Day</t>
+          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
+          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
+          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Pune | हडपसरला नवीन मेट्रो मार्गिका, मुख्य शहराशी कनेक्टिव्हिटी मिळणार असल्याने प्रवास होणार वेगवान...</t>
+          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>राज्यातील ग्रंथालयांसाठी फडणवीस सरकारचा ऐतिहासिक निर्णय : अनुदानात ४०% वाढ</t>
+          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/65971/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Sanjay Raut Vs Chandrakant Patil | Special Report | फुले चित्रपटावरुन राऊत-पाटलामध्ये जुंपली</t>
+          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/sanjay-raut-vs-chandrakant-patil-special-report-raut-patla-clash-over-phule-movie-1038823.html</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
+          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>सर्वात मोठी बातमी, राधाकृष्ण विखे पाटील मराठा उपसमितीचे अध्यक्ष, 12 सदस्यांमध्ये कुणाकुणाला जबाबदारी?</t>
+          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-appoint-radhakrishna-vikhe-patil-as-new-president-of-maratha-reservation-sub-committee/articleshow/123457847.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Maharashtra CET Admission 2025: विद्यार्थ्यांसाठी दिलासादायक बातमी! BE/BTech आणि MBA प्रवेशासाठी मुदतवाढ जाहीर</t>
+          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Sangli News : सांगली जिल्ह्याला अवकाळीने झोडपले; वादळी वाऱ्यासह पावसाची हजेरी, रब्बीला पिकाला फटका</t>
+          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/sangli-news-unseasonal-rain-in-miraj-tasgaon-hits-rabi-winter-crops/articleshow/119493800.cms</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>भयंकर शेवट! दिरानेच केला भावजय व तिच्या मित्राचा खून; 'या' कारणांमुळे घडले मंगळवेढ्यातील दुहेरी हत्याकांड</t>
+          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/seven-people-murder-woman-a-man-over-a-farming-dispute-incident-in-gunjegaon-two-are-undergoing-treatment-in-a-private-hospital-three-are-in-custody/</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>State to conduct second CET, colleges worried about delay in academic year</t>
+          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
+          <t>Jayant Patil Emotional: ‘एकत्र यायला हवं…’,जयंत पाटलांची भावनिक साद; पत्राने चर्चेला उधाण</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Sinhgad Institute Staff Suffer as Salary Crisis Deepens</t>
+          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://punemirror.com/education/sinhgad-institute-staff-suffer-as-salary-crisis-deepens/</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
+          <t>Union Minister says daughter harassed in Maharashtra, Devendra Fadnavis reacts</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
+          <t>https://www.indiatoday.in/india/story/union-minister-raksha-khadse-daughter-molested-in-maharashtra-devendra-fadnavis-reacts-2687760-2025-03-02</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
+          <t>What AI means for today’s classrooms</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://www.deccanherald.com/dhie/science/2025/07/16/what-ai-means-for-todays-classrooms</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
+          <t>‘Dead bodies, debris’: Eyewitness recalls hearing ‘massive sound’ during Air India plane crash | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
+          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
+          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
+          <t>Aftermath of baby kidnap: Sangli guardian minister Chandrakant Patil announces enhanced security measures</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>Samiti, residents demand removal of unauthorised arch in Kalaburagi</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://www.thehindu.com/news/national/karnataka/samiti-residents-demand-removal-of-unauthorised-arch-in-kalaburagi/article69147129.ece</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
+          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
+          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
+          <t>'If anything happens to me...':Abu Azmi responds after suspension over Aurangzeb remarks</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
+          <t>https://english.mathrubhumi.com/news/india/abu-azmi-suspended-maharashtra-assembly-aurangzeb-42dc0e0b</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
+          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Jayant Patil Emotional: ‘एकत्र यायला हवं…’,जयंत पाटलांची भावनिक साद; पत्राने चर्चेला उधाण</t>
+          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
+          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
+          <t>Millennium National School shines at Invitational Taekwondo Inter-School Competition</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
+          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>मोठी बातमी! MHT-CET 2025 पीसीएम गटाची फेर परीक्षा; 'या' दिवशी होणार पेपर, सीईटी सेलची माहिती</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
+          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
+          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
+          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Ahilyadevi Holkar’s legacy must be known to youth: CM</t>
+          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
+          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
+          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
+          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
+          <t>Sanjay Raut claims 'some in BJP' want alliance with Uddhav Sena, Fadnavis retorts</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
+          <t>BJP MLC first to record statement in CM’s SIT probe</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
+          <t>BJP leaders conduct back-to-back separate review meetings at PMC; Oppn questions lack of results</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163883/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>भविष्यात मराठी शाळा बंद पडण्याची भीती; काय आहे कारण? घ्या जाणून</t>
+          <t>BJP leader's statement on Raj Thackeray, 'Like one who predicts...'?</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/marathi-bhasha-gaurav-din-2025-marathi-schools-on-the-verge-of-shut-down-in-future-in-maharashtra-know-the-reason-maharashtra-news-mhs25022606375</t>
+          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>मोठी बातमी! MHT-CET 2025 पीसीएम गटाची फेर परीक्षा; 'या' दिवशी होणार पेपर, सीईटी सेलची माहिती</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>Mahayuti parties battling each other during poaching spree</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>Sanjay Raut claims 'some in BJP' want alliance with Uddhav Sena, Fadnavis retorts</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>BJP MLC first to record statement in CM’s SIT probe</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>BJP leaders conduct back-to-back separate review meetings at PMC; Oppn questions lack of results</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
-        </is>
-      </c>
-      <c r="B573" t="inlineStr">
-        <is>
           <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>पृथ्वीराज पाटील यांचा भाजप प्रवेश टाळला</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>Jayashree Patil - जयश्री पाटील यांचा आज भाजपमध्ये प्रवेश!</t>
-        </is>
-      </c>
-      <c r="B575" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/jayashree-patil-joins-bjp-maharashtra-politics-political-entry-news-msr87</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>काँग्रेसचे पृथ्वीराज पाटील यांचा भाजप प्रवेश निश्चित</t>
-        </is>
-      </c>
-      <c r="B576" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/sangali/congress-prithviraj-patil-to-join-bjp-dc95</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>Sangli: वसंतदादा पाटील यांच्या नातसून जयश्रीताई पाटील भाजपमध्ये, अजितदादांना शह</t>
-        </is>
-      </c>
-      <c r="B577" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/sangli/former-chief-minister-vasantdada-patil-granddaughter-jayashreetai-patil-will-join-bjp-a-a746/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B562"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,84 +563,84 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Outright Kunbi status to will not stand legal test: Chandrakant Patil</t>
+          <t>Sangli guardian minister Chandrakant Patil calls upon former BJP MP Sanjaykaka Patil, urges him to return</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chandrakant Patil urges PMC to build Sudhir Phadke Memorial in Kothrud</t>
+          <t>Higher education minister Chandrakant Patil’s surprise visit to a city college</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
+          <t>https://www.thebridgechronicle.com/education/higher-education-minister-chandrakant-patil-surprise-visit-garware-college-free-education-girls</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>India has a roadmap ready for AI application: Chandrakant Patil</t>
+          <t>Chandrakant Patil urges PMC to build Sudhir Phadke Memorial in Kothrud</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/india-ai-roadmap-maharashtra-minister-chandrakant-patil-9925307/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-pmc-to-build-sudhir-phadke-memorial-in-kothrud-101753209522556.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BJP mantri’s remark sparks buzz of patch-up with Shiv Sena UBT</t>
+          <t>India has a roadmap ready for AI application: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
+          <t>https://indianexpress.com/article/cities/pune/india-ai-roadmap-maharashtra-minister-chandrakant-patil-9925307/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chandrakant Patil urges universities to speed up professor recruitment</t>
+          <t>Movie ‘Phule’ depicts discrimination of bygone era, no need to oppose it: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-universities-to-speed-up-professor-recruitment-101750100033990.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chandrakant Patil discusses safety, security of 17 hills in Pune with forest department</t>
+          <t>Chandrakant Patil urges universities to speed up professor recruitment</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/chandrakant-patil-safety-security-hills-pune-forest-department-9777078/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/chandrakant-patil-urges-universities-to-speed-up-professor-recruitment-101750100033990.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sangli guardian minister Chandrakant Patil calls upon former BJP MP Sanjaykaka Patil, urges him to return</t>
+          <t>Chandrakant Patil discusses safety, security of 17 hills in Pune with forest department</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
+          <t>https://indianexpress.com/article/cities/pune/chandrakant-patil-safety-security-hills-pune-forest-department-9777078/</t>
         </is>
       </c>
     </row>
@@ -671,1248 +671,1248 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Movie ‘Phule’ depicts discrimination of bygone era, no need to oppose it: Chandrakant Patil</t>
+          <t>1,000 new personnel to join Pune Police force: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Higher education minister Chandrakant Patil’s surprise visit to a city college</t>
+          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/education/higher-education-minister-chandrakant-patil-surprise-visit-garware-college-free-education-girls</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
+          <t>Maharashtra Minister asks Jarange to hold talks with Govt ahead of protests</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-asks-jarange-to-hold-talks-with-govt-ahead-of-protests/article69969205.ece</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Maharashtra Minister asks Jarange to hold talks with Govt ahead of protests</t>
+          <t>May become minister in future, either joining Congress or any other party, says Vishal Patil weeks after</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-asks-jarange-to-hold-talks-with-govt-ahead-of-protests/article69969205.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>May become minister in future, either joining Congress or any other party, says Vishal Patil weeks after</t>
+          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/may-become-minister-in-future-either-joining-congress-or-any-other-party-says-vishal-patil-weeks-after-chandrakant-patils-offer-to-join-bjp/articleshow/120171254.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1,000 new personnel to join Pune Police force: Chandrakant Patil</t>
+          <t>MVA under a cloud, Sanjay Raut says many in BJP keen on aligning with Sena (UBT), feeling ‘mutual’</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
+          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
+          <t>Vishal Patil turns down BJP minister’s offer to join alliance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
+          <t>100 per cent fee waiver for EWS girls: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MVA under a cloud, Sanjay Raut says many in BJP keen on aligning with Sena (UBT), feeling ‘mutual’</t>
+          <t>Outright Kunbi status to will not stand legal test: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vishal Patil turns down BJP minister’s offer to join alliance</t>
+          <t>People of different backgrounds are bound to disagree in coalition govt: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-of-different-backgrounds-are-bound-to-disagree-in-coalition-govt-chandrakant-patil-23519840</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>100 per cent fee waiver for EWS girls: Chandrakant Patil</t>
+          <t>Patil tells officials to expedite land acquisition for roads in Kothrud</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Patil tells officials to expedite land acquisition for roads in Kothrud</t>
+          <t>Grateful minister urges edu trust to go autonomous</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-tells-officials-to-expedite-land-acquisition-for-roads-in-kothrud-101745865957490.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Grateful minister urges edu trust to go autonomous</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
+          <t>Maharashtra minister's ‘golden’ moment’ remark sparks buzz of Uddhav Thackeray-BJP patch-up</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Maharashtra minister's ‘golden’ moment’ remark sparks buzz of Uddhav Thackeray-BJP patch-up</t>
+          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-ministers-golden-moment-remark-sparks-buzz-of-uddhav-thackeray-bjp-patch-up/articleshow/117769125.cms</t>
+          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
+          <t>Aftermath of baby kidnap: Sangli guardian minister Chandrakant Patil announces enhanced security measures</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RSS holds two-day brainstorming session with BJP, allied outfits</t>
+          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
+          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DH Evening Brief: BSF Jawan Returns from Pakistan; MP HC Orders FIR Against Minister</t>
+          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>State’s tech edu minister reviews fee waiver for women students</t>
+          <t>If some leader leaves, not necessarily people join him: Vishwajeet Kadam</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Retirement Age of College Principals Raised to 65: Announces Minister Chandrakant Patil</t>
+          <t>RSS holds two-day brainstorming session with BJP, allied outfits</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DPDC meeting on Thursday</t>
+          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
+          <t>DH Evening Brief: BSF Jawan Returns from Pakistan; MP HC Orders FIR Against Minister</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.deccanherald.com/india/dh-evening-brief-bsf-jawan-returns-from-pak-custody-fir-ordered-against-mp-minister-for-remarks-against-col-sofia-qureshi-3540442</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
+          <t>State’s tech edu minister reviews fee waiver for women students</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
+          <t>Retirement Age of College Principals Raised to 65: Announces Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
+          <t>https://thelivenagpur.com/2025/07/27/retirement-age-of-college-principals-raised-to-65-announces-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pune News: Chandrakant Patil Issues Ultimatum to Pune Municipal Corporation Over Solid Waste Management Project</t>
+          <t>DPDC meeting on Thursday</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
+          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Three-Week Monsoon Session of Maharashtra Assembly to Begin on Monday</t>
+          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/three-week-monsoon-session-of-maharashtra-assembly-to-begin-on-monday-1887745</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil reviews Bajirao Peshwa Memorial Work on Parvati Hill</t>
+          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://punemirror.com/politics/pune-chandrakant-patil-reviews-bajirao-peshwa-memorial-work-on-parvati-hill/</t>
+          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Patil silent on Bavdhan garbage plant issue in PMC meeting</t>
+          <t>No CET outside Maharashtra: Minister</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-cet-outside-maharashtra-minister-101749151005604.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Maharashtra: cabinet sub-committee on Maratha quota reconstituted; Vikhe Patil new head</t>
+          <t>State to conduct second CET, colleges worried about delay in academic year</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Work on the Triad of Inspection, Action, and Execution for a Traffic-Free Kothrud: Minister Chandrakant Patil</t>
+          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/work-on-the-triad-of-inspection-action-and-execution-for-a-traffic-free-kothrud-minister-chandrakant-patil/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rift in Maharashtra Congress over ‘little known face’ at helm, Prithviraj Chavan ‘surprised’</t>
+          <t>Mahayuti parties battling each other during poaching spree</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/rift-in-maharashtra-congress-over-little-known-face-at-helm-prithviraj-chavan-surprised-9838116/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>State adds fourth CAP round for engineering admissions to curb costly pvt options | Mumbai news</t>
+          <t>Pune News: Chandrakant Patil Issues Ultimatum to Pune Municipal Corporation Over Solid Waste Management Project</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
+          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mandrem Police Arrest Man for Brutally Assaulting Mother in Pernem</t>
+          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.heraldgoa.in/goa/goa/mandrem-police-arrest-man-for-brutally-assaulting-mother-in-pernem/423993</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>State may halt admissions to pharmacy colleges flouting norms</t>
+          <t>Pune: Chandrakant Patil reviews Bajirao Peshwa Memorial Work on Parvati Hill</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://punemirror.com/politics/pune-chandrakant-patil-reviews-bajirao-peshwa-memorial-work-on-parvati-hill/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
+          <t>Maharashtra deputy chief minister Ajit Pawar vows swift action to restore OBC quota</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/maharashtra-deputy-chief-minister-ajit-pawar-vows-swift-action-to-restore-obc-quota/articleshow/120525973.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pune civic body acts against unauthorised stalls on FC Road</t>
+          <t>Patil silent on Bavdhan garbage plant issue in PMC meeting</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/pune-civic-body-acts-against-unauthorised-stalls-on-fc-road-101749148183563.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-silent-on-bavdhan-garbage-plant-issue-in-pmc-meeting-101745953467654.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
+          <t>Maharashtra: cabinet sub-committee on Maratha quota reconstituted; Vikhe Patil new head</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
+          <t>https://www.ptinews.com/story/national/maharashtra:-cabinet-sub-committee-on-maratha-quota-reconstituted;-vikhe-patil-new-head/2847184</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BMC to restart withdrawn services by tanker association with police help</t>
+          <t>Work on the Triad of Inspection, Action, and Execution for a Traffic-Free Kothrud: Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
+          <t>https://punemirror.com/city/civic/work-on-the-triad-of-inspection-action-and-execution-for-a-traffic-free-kothrud-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
+          <t>Rift in Maharashtra Congress over ‘little known face’ at helm, Prithviraj Chavan ‘surprised’</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
+          <t>https://indianexpress.com/article/political-pulse/rift-in-maharashtra-congress-over-little-known-face-at-helm-prithviraj-chavan-surprised-9838116/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
+          <t>State adds fourth CAP round for engineering admissions to curb costly pvt options | Mumbai news</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-adds-fourth-cap-round-for-engineering-admissions-to-curb-costly-pvt-options-101749150825079.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Islampur to be renamed Ishwarpur</t>
+          <t>Mandrem Police Arrest Man for Brutally Assaulting Mother in Pernem</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://www.heraldgoa.in/goa/goa/mandrem-police-arrest-man-for-brutally-assaulting-mother-in-pernem/423993</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
+          <t>Samiti, residents demand removal of unauthorised arch in Kalaburagi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
+          <t>https://www.thehindu.com/news/national/karnataka/samiti-residents-demand-removal-of-unauthorised-arch-in-kalaburagi/article69147129.ece</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
+          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C R Patil takes charge as Jal Shakti minister</t>
+          <t>State committed to opposing Almatti height rise, says minister Vikhe Patil</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/c-r-patil-takes-charge-as-jal-shakti-minister/1575205</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Protesters oppose name expansion proposal of Shivaji University in Kolhapur</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
+          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
+          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Police bust chain-snatching gang; two held, minor detained</t>
+          <t>Islampur to be renamed Ishwarpur</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
+          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
+          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
+          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
+          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
+          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
+          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
+          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
+          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
+          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
+          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
+          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
+          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
+          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
+          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
+          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BJP district rural unit president elected in Kalaburagi</t>
+          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
+          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
+          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
+          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
+          <t>Maharashtra: Samajwadi Party’s Abu Azmi suspended from Assembly session for remark about Aurangzeb</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
+          <t>https://scroll.in/latest/1079939/maharashtra-samajwadi-partys-abu-azmi-suspended-from-assembly-session-for-remark-about-aurangzeb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
+          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
+          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces Quantum Computing Training For Over 500 Professors To Boost</t>
+          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-quantum-computing-training-for-over-500-professors-to-boost-tech-education-under-nep-2020</t>
+          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Universities Should Implement ‘Carry On’ Scheme For Student Welfare, Says Higher &amp; Technical Education</t>
+          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/universities-should-implement-carry-on-scheme-for-student-welfare-says-higher-technical-education-minister-chandrakant-patil</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Chandrakant Patil Dismisses Buzz Over NCP Merger, Calls It Pure Speculation</t>
+          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-chandrakant-patil-dismisses-buzz-over-ncp-merger-calls-it-pure-speculation</t>
+          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pune News: Chandrakant Patil Urges Citizens To Stay Vigilant</t>
+          <t>BJP district rural unit president elected in Kalaburagi</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
+          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
+          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
+          <t>Maharashtra State CET Cell launches CET-ATAL module for mock tests</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
+          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
+          <t>BJP leader's statement on Raj Thackeray, 'Like one who predicts...'?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Reveals Details Of Vidhan Bhavan Meetings On Pune Municipal Corporation Budget</t>
+          <t>शाश्वत कृषी संजीवनीचे पुस्तकाचे प्रकाशन: चंद्रकांत पाटील यांच्या हस्ते अनावरण, नैसर्गिक शेतीचे महत्त्व पटवू...</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-natural-farming-book-release-135379530.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces Quantum Computing Training For Over 500 Professors To Boost</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-quantum-computing-training-for-over-500-professors-to-boost-tech-education-under-nep-2020</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
+          <t>Universities Should Implement ‘Carry On’ Scheme For Student Welfare, Says Higher &amp; Technical Education</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/education/universities-should-implement-carry-on-scheme-for-student-welfare-says-higher-technical-education-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ensure Safety Measures For Pune Hills: Higher And Technical Education Minister Chandrakant Patil’s Directives</t>
+          <t>Maharashtra Politics: Chandrakant Patil Dismisses Buzz Over NCP Merger, Calls It Pure Speculation</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-chandrakant-patil-dismisses-buzz-over-ncp-merger-calls-it-pure-speculation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Warns PMC, Shut Down Sus Waste Project Or Face Protest</t>
+          <t>Pune News: Chandrakant Patil Urges Citizens To Stay Vigilant</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
+          <t>https://www.mypunepulse.com/pune-news-chandrakant-patil-urges-citizens-to-stay-vigilant/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Demands Swift Action On City’s Missing Road Link Projects</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
+          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
+          <t>Chandrakant Patil Reveals Details Of Vidhan Bhavan Meetings On Pune Municipal Corporation Budget</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
+          <t>https://www.mypunepulse.com/chandrakant-patil-reveals-details-of-vidhan-bhavan-meetings-on-pune-municipal-corporation-budget/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>No Ajit Pawar vs Chandrakant Patil In Pune: PMC Polls Likely To Be Held Under Leadership Of Muralidhar Mohol</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/no-ajit-pawar-vs-chandrakant-patil-in-pune-pmc-polls-likely-to-be-held-under-leadership-of-muralidhar-mohol</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
+          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
+          <t>Ensure Safety Measures For Pune Hills: Higher And Technical Education Minister Chandrakant Patil’s Directives</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Buldhana Shock: Doctor Dies After Setting Himself on Fire, Motive Still a Mystery</t>
+          <t>Pune: Chandrakant Patil Warns PMC, Shut Down Sus Waste Project Or Face Protest</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/buldhana-shock-doctor-dies-after-setting-himself-on-fire-motive-still-a-mystery-a525/</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
+          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
+          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
+          <t>Pune: Chandrakant Patil Demands Swift Action On City’s Missing Road Link Projects</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-demands-swift-action-on-citys-missing-road-link-projects/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
+          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Flags PMC Misgovernance Amid Delayed Elections; High-Level Meeting with Ajit Pawar Likely</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
+          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
+          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
+          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
+          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
+          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
+          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Promises Full Support for Women Empowerment and Girls’ Education in Mulshi Taluka</t>
+          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-promises-full-support-for-women-empowerment-and-girls-education-in-mulshi-taluka/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
+          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
+          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
+          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NCTE Cancels Recognition Of 16 B.Ed. Colleges In Maharashtra: Minister Chandrakant Patil (Video)</t>
+          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/ncte-cancels-recognition-of-16-bed-colleges-in-maharashtra-minister-chandrakant-patil-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
+          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
+          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Delay In Pune's Equal Water Supply Scheme Sparks Public Discontent; MLA Chandrakant Patil Criticizes PMC</t>
+          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
+          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
+          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
+          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Wonder if some forces are working to destabilise Maharashtra: Minister amid Shaktipeeth stir</t>
+          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra-minister-amid-shaktipeeth-stir-9664386</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
@@ -1943,120 +1943,120 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
+          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
+          <t>CET Exams to Be Held Only Within Maharashtra</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
+          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CET Exams to Be Held Only Within Maharashtra</t>
+          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>“Society is Responsible for Keeping Every Person Alive” – CM Devendra Fadnavis at Guinness World Record Event in Pune</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/society-is-responsible-for-keeping-every-person-alive-cm-devendra-fadnavis-at-guinness-world-record-event-in-pune/</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 1,600 EWS Students Granted Special Exemption For Certificate Submission</t>
+          <t>Pune: Union Minister Muralidhar Mohol Supports MLA Hemant Rasanes Hoarding-Free Kasba Initiative</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-over-1600-ews-students-granted-special-exemption-for-certificate-submission</t>
+          <t>https://www.freepressjournal.in/pune/pune-union-minister-muralidhar-mohol-supports-mla-hemant-rasanes-hoarding-free-kasba-initiative</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
+          <t>From Pan Tapri Owner to Maharashtra Assembly Deputy Speaker: Pimpri MLA Anna Bansode Wins Unopposed</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
+          <t>https://www.freepressjournal.in/pune/from-pan-tapri-owner-to-maharashtra-assembly-deputy-speaker-pimpri-mla-anna-bansode-wins-unopposed</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAP: Maharashtra to Introduce Four Rounds in Centralised Engineering Admissions; Stricter Seat Allotment Rules Planned</t>
+          <t>VIDEO I Attention Punekars! Two Municipal Corporations In Pune Soon With PMC Bifurcation—Read Details Here</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/cap-maharashtra-to-introduce-four-rounds-in-centralised-engineering-admissions-stricter-seat-allotment-rules-planned/</t>
+          <t>https://www.freepressjournal.in/pune/video-i-attention-punekars-two-municipal-corporations-in-pune-soon-with-pmc-bifurcationread-details-here</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>VIDEO I Attention Punekars! Two Municipal Corporations In Pune Soon With PMC Bifurcation—Read Details Here</t>
+          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/video-i-attention-punekars-two-municipal-corporations-in-pune-soon-with-pmc-bifurcationread-details-here</t>
+          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
+          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
@@ -2075,144 +2075,144 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pune: Defence Minister Rajnath Singh Likely to Inaugurate Peshwa Memorial at Parvati Hill</t>
+          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
+          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
+          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
+          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा</t>
+          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
+          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
+          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
+          <t>सांगलीचे अपक्ष खासदार विशाल पाटील यांना चंद्रकांत पाटील यांच्याकडून खुली ऑफर</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
+          <t>https://www.jaimaharashtranews.com/politics/chandrakant-patil-makes-an-open-offer-to-sangli-independent-mp-vishal-patil-to-join-bjp/34589</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>सांगलीचे अपक्ष खासदार विशाल पाटील यांना चंद्रकांत पाटील यांच्याकडून खुली ऑफर</t>
+          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/chandrakant-patil-makes-an-open-offer-to-sangli-independent-mp-vishal-patil-to-join-bjp/34589</t>
+          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
+          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
+          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2315,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: “… तर मुख्यमंत्री धनंजय मुंडेंना राजीनामा द्यायला सांगतील”, चंद्रकांत पाटील यांचं मोठं विधान</t>
+          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-chandrakant-patil-reaction-on-dhananjay-munde-ministerial-post-says-cm-will-take-decision-on-resignation-kvg-85-4850775/</t>
+          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
         </is>
       </c>
     </row>
@@ -2339,168 +2339,168 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
+          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
+          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
+          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
+          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
+          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
+          <t>खासदार विशाल पाटलांना भाजपकडून ऑफर, चंद्रकांत पाटील म्हणाले, "एक चांगला माणूस यावा, यासाठी..."</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://www.lokmat.com/sangli/chandrakant-patil-has-offered-sangli-congress-mp-vishal-patil-to-join-the-bjp-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>शिक्षक गिरीश फोंडे यांचे निलंबन रद्द करणार, मंत्री चंद्रकांत पाटील यांच्याकडून आश्वासन</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://www.lokmat.com/sangli/teacher-girish-fondes-suspension-will-be-revoked-assurance-from-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
+          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
+          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
+          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
+          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
+          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
+          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172941/</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
@@ -2519,300 +2519,300 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
+          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
+          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
+          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174837/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
+          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
+          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>कानडवाडी येथील १० एम.व्ही.ए. पॉवर ट्रान्सफॉर्मरचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
+          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175996/</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
+          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
+          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
+          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
+          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
+          <t>https://mahasamvad.in/172941/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
+          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
+          <t>जिल्हा नियोजनची कामे मुदतीत न करणाऱ्या ठेकेदारांवर कारवाई, पालकमंत्री चंद्रकांत पाटील यांचा इशारा</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
+          <t>https://www.lokmat.com/sangli/action-will-be-taken-against-contractors-who-do-not-complete-district-planning-works-within-the-deadline-guardian-minister-chandrakant-patil-warns-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
+          <t>जिल्हा नियोजनसाठी ६३२ कोटींचा निधी मंजूर, सांगलीचे पालकमंत्री चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
+          <t>https://www.lokmat.com/sangli/fund-of-rs-632-crores-approved-for-district-planning-sangli-guardian-minister-chandrakant-patil-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
+          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
+          <t>https://mahasamvad.in/174837/</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>राज्यात दोन हजार नवीन ग्रंथालये : उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/two-thousand-new-libraries-in-maharashtra-announces-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
+          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
+          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
+          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>राज्यात दोन हजार नवीन ग्रंथालये : उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/two-thousand-new-libraries-in-maharashtra-announces-minister-chandrakant-patil-ap84</t>
+          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
+          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
+          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
         </is>
       </c>
     </row>
@@ -2831,624 +2831,624 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
+          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
+          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>खानापूरला शिवाजी विद्यापीठाचे उपकेंद्र; चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
+          <t>https://www.loksatta.com/maharashtra/shivaji-university-s-sub-centre-in-khanapur-says-chandrakant-patil-zws-70-4960985/</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
+          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
+          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
+          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
+          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
+          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
+          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
+          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>क्वांटम संगणन उपक्रमाच्या माध्यमातून प्राध्यापकांना प्रशिक्षण – मंत्री चंद्रकांत पाटील</t>
+          <t>मंत्री चंद्रकांत पाटील यांची ‘दिलखुलास’ मध्ये २४ ते २६ तर ‘जय महाराष्ट्र’मध्ये २५ मार्चला मुलाखत</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://mahasamvad.in/160007/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
+          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
+          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील म्हणतात, भारतीय जनता पार्टीच्या नेत्यांनी धंगेकरांना घेण्याचा निर्णय केला असता तर…</t>
+          <t>क्वांटम संगणन उपक्रमाच्या माध्यमातून प्राध्यापकांना प्रशिक्षण – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
+          <t>https://www.mahasamvad.in/169422/</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
+          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
+          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
+          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
+          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
+          <t>चंद्रकांत पाटील म्हणतात, भारतीय जनता पार्टीच्या नेत्यांनी धंगेकरांना घेण्याचा निर्णय केला असता तर…</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>पुण्यात वारकऱ्यांसाठी ‘फिरता दवाखाना’; मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
+          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
+          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
+          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
+          <t>पुण्यात वारकऱ्यांसाठी ‘फिरता दवाखाना’; मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
+          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
+          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
+          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
+          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
+          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>सीमाप्रश्नी चंद्रकांत पाटील, शंभूराज देसाई पुन्हा समन्वयकमंत्री</t>
+          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-shambhuraj-desai-reappointed-border-issue-coordination-ministers</t>
+          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
+          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
+          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
+          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
+          <t>राष्ट्रवादीचे अस्तित्व केवळ पवार कुटुंबापुरतेच मर्यादित, मंत्री चंद्रकांत पाटील यांचे टीकास्त्र</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://www.lokmat.com/sangli/ncp-existence-is-limited-to-the-pawar-family-only-minister-chandrakant-patils-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शिक्षकांनी गुरूंचे स्थान उंचावले पाहिजे, चंद्रकांत पाटील यांचे मत; विकसित भारताबाबत परिसंवाद</t>
+          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-emphasizes-role-of-education-in-building-developed-india-by-2047-amp17</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
+          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
+          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
+          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
+          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
+          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>छत्रपती संभाजी महाराज स्मृतीस्थळ विकासाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://mahasamvad.in/173013/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
+          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
+          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>'महाराष्ट्र एज्युकेशन अँड कॉर्पोरेट आयकॉन्स 2025' सन्मान सोहळा: उद्योग आणि शिक्षण संस्थांमधील परस्पर समन्वय...</t>
+          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/education-industry-collaboration-essential-skilled-workforce-chandrakant-patil-135447177.html</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
+          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
@@ -3467,84 +3467,84 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
+          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
+          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
+          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
+          <t>अमली पदार्थ विरोधी टास्क फोर्सने कायद्याचा धाक निर्माण करावा – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-says-anti-drug-task-force-should-create-fear-of-law-mrj-95-4882600/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>उच्च व तंत्र शिक्षण विभागातील प्रलंबित प्रकरणे वेळेत निकाली काढा – मंत्री चंद्रकांत (दादा) पाटील</t>
+          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/154565/</t>
+          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
+          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/eps-employees-pension-%E0%A4%88%E0%A4%AA-%E0%A4%8F%E0%A4%B8-%E0%A4%95%E0%A4%B0%E0%A5%8D%E0%A4%AE%E0%A4%9A-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%B5%E0%A5%87%E0%A4%A4%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%B8-%E0%A4%A0-%E0%A4%AA-%E0%A4%A0%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%B5-%E0%A4%95%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1La4cI</t>
+          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
+          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
@@ -3563,24 +3563,24 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
+          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
+          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>शाश्वत कृषी संजीवनीचे पुस्तकाचे प्रकाशन: चंद्रकांत पाटील यांच्या हस्ते अनावरण, नैसर्गिक शेतीचे महत्त्व पटवू...</t>
+          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-natural-farming-book-release-135379530.html</t>
+          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
         </is>
       </c>
     </row>
@@ -3599,12 +3599,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
+          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
         </is>
       </c>
     </row>
@@ -3623,204 +3623,204 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
+          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
+          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
+          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
+          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
+          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
+          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>अशी दादागिरी चालणार नाही, चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, बाधित म्हणाले तुम्हाला टाहो फोडून</t>
+          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-and-farmers-came-face-to-face-over-shaktipith-highway/903727</t>
+          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
+          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
+          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
+          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>कोल्हापुरातील शिवाजी विद्यापीठाचे उपकेंद्र खानापुरात, मंत्री चंद्रकांत पाटील यांची घोषणा</t>
+          <t>नवनियुक्त आयुक्तांची भेट घेत चंद्रकांत पाटलांनी वाचला पुण्यातील अडचणींचा पाढा</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/shivaji-university-sub-centre-to-be-set-up-in-khanapur-announced-by-minister-chandrakant-patil-a-a746/</t>
+          <t>https://www.lokmat.com/pune/pune-news-chandrakant-patil-while-meeting-the-newly-appointed-commissioners-read-out-the-problems-in-pune-a-a1014-c1008/</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
+          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
+          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
+          <t>कोल्हापुरातील शिवाजी विद्यापीठाचे उपकेंद्र खानापुरात, मंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
+          <t>https://www.lokmat.com/sangli/shivaji-university-sub-centre-to-be-set-up-in-khanapur-announced-by-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
+          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
+          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
+          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
+          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
@@ -3839,84 +3839,84 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
+          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
+          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
+          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
         </is>
       </c>
     </row>
@@ -3935,72 +3935,72 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
+          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
+          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
+          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
+          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शक्तिपीठ बाधित शेतकऱ्यांना भरपाई मिळणार? काय म्हणाले चंद्रकांत पाटील</t>
+          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrkant-patil-will-the-farmers-affected-by-shaktipeeth-get-compensation-what-did-chandrakant-patil-say/912426/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
+          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
         </is>
       </c>
     </row>
@@ -4019,24 +4019,24 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
+          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
+          <t>Ranjitsinh Mohite Patil : पालकमंत्र्यांची एन्ट्री होताच रणजितसिंह मोहिते पाटलांनी विद्यापीठाच्या कार्यक्रमातून काढता पाय घेतला!</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/as-soon-as-guardian-minister-jaykumar-gore-entered-ranjitsinh-mohite-patil-walked-out-of-the-program-vd83</t>
         </is>
       </c>
     </row>
@@ -4067,12 +4067,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
         </is>
       </c>
     </row>
@@ -4091,300 +4091,300 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
+          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
+          <t>उद्या शंभर एकर जागा देतो, कोल्हापुरातील आयटी पार्क प्रश्नावर मंत्री चंद्रकांत पाटलांचे मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
+          <t>https://www.lokmat.com/kolhapur/tomorrow-i-will-give-100-acres-of-land-minister-chandrakant-patil-big-statement-on-the-it-park-issue-in-kolhapur-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
+          <t>गोगावलेंची पूजा जनतेच्या कल्याणासाठी, अघोरी पूजेच्या आरोपांच्या वादात चंद्रकांत पाटलांची उडी</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-supports-bharat-gogawale-after-allegations-of-aghori-puja/916805</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
+          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
+          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
+          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
+          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
+          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
+          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
+          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राज ठाकरे चांगले नेते पण जरा समजून घेतलं पाहिजे आणि… हिंदी सक्तीवरून...</t>
+          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
+          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
+          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
+          <t>Chandrakant Patil : राज ठाकरे चांगले नेते पण जरा समजून घेतलं पाहिजे आणि… हिंदी सक्तीवरून...</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
+          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
+          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
+          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
+          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
+          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>छत्रपती शिवाजी महाराज यांच्या पुण्यतिथी कार्यक्रम तयारीचा उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160732/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mohite Patil : भाजपच्या निमंत्रण पत्रिकेतून मोहिते पाटलांना डावलले; विमान कंपनीच्या पत्रिकेत मात्र सर्वांची नावे</t>
+          <t>छत्रपती शिवाजी महाराज यांच्या पुण्यतिथी कार्यक्रम तयारीचा उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ranjitsinh-mohite-patils-name-omitted-from-bjps-invitation-letter-for-solapur-air-service-vd83</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
+          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
+          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
+          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
+          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
+          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
+          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
+          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
+          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
+          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
         </is>
       </c>
     </row>
@@ -4403,144 +4403,144 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
+          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
+          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>मराठा आरक्षण उपसमितीच्या अध्यक्षपदी राधाकृष्ण विखे-पाटील</t>
+          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/radhakrishna-vikhe-patil-appointed-maratha-reservation-subcommittee-chairman</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
+          <t>मराठा आरक्षण उपसमितीच्या अध्यक्षपदी राधाकृष्ण विखे-पाटील</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/radhakrishna-vikhe-patil-appointed-maratha-reservation-subcommittee-chairman</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
+          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
+          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
+          <t>तिघे वेगवेगळ्या पार्श्वभूमीतील, खडखड होणारच; चंद्रकांत पाटलांनी नाराजीचा चेंडू भिरकावला</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
+          <t>https://www.lokmat.com/pune/three-from-different-backgrounds-there-will-be-a-clash-chandrakant-patil-spoke-about-the-displeasure-of-the-mahayuti-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>‘बी.फार्म’ आणि ‘डी.फार्म’ अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
+          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173736/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
+          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा</t>
+          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169668/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>‘कमवा व शिका’ योजनेतील विद्यार्थिनींना अधिकच्या अडीच हजार निधीसाठी प्रयत्न</t>
+          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/shivaji-universitys-east-west-campus-subway-inauguration</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
         </is>
       </c>
     </row>
@@ -4619,144 +4619,144 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
+          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
+          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>सांगली जिल्ह्याच्या विकासासाठी ५४५ कोटींचा आराखडा - पालकमंत्री पाटील</t>
+          <t>पुण्यातील टेकड्यांबाबत मोठा निर्णय, आता 17 टेकड्यांवर अशी होणार उपाययोजना</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/rs-545-crore-plan-for-the-development-of-sangli-district-says-guardian-minister-chandrakant-patil-a-a746/</t>
+          <t>https://www.tv9marathi.com/maharashtra/pune/mhatoba-tekdi-pune-chandrakant-patil-will-install-cctv-1333776.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>सांगली जिल्ह्याच्या विकासासाठी ५४५ कोटींचा आराखडा - पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://www.lokmat.com/sangli/rs-545-crore-plan-for-the-development-of-sangli-district-says-guardian-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
+          <t>Shaktipeeth Highway: शक्तिपीठ महामार्गाला विरोध, शेतकऱ्यांनी ताकद दाखवली, मंत्री चंद्रकांत पाटलांना घेरलं</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
+          <t>https://saamtv.esakal.com/maharashtra/clash-between-minister-chandrakant-patil-and-protesters-over-shaktipith-highway-sangli-latest-news-bdk97</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
+          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Shaktipeeth Highway: शक्तिपीठ महामार्गाला विरोध, शेतकऱ्यांनी ताकद दाखवली, मंत्री चंद्रकांत पाटलांना घेरलं</t>
+          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/clash-between-minister-chandrakant-patil-and-protesters-over-shaktipith-highway-sangli-latest-news-bdk97</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>पुण्यात सामाजिक कार्याचा गौरव, पत्रकारांच्या पाल्ल्यांसाठी 'प्रतिबिंब प्रतिष्ठान'</t>
+          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
+          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
+          <t>पुण्यात सामाजिक कार्याचा गौरव, पत्रकारांच्या पाल्ल्यांसाठी 'प्रतिबिंब प्रतिष्ठान'</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
+          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
+          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
+          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
+          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163883/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
@@ -4775,60 +4775,60 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
+          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
+          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
+          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
+          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
+          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
+          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
+          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
         </is>
       </c>
     </row>
@@ -4847,120 +4847,120 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
+          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
+          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
+          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
+          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
+          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
+          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
+          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
+          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
+          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
+          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
+          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
+          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
         </is>
       </c>
     </row>
@@ -4979,1368 +4979,1368 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
+          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
+          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
+          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
+          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
+          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
+          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
+          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Sharad Lad | ‘पदवीधर’साठी भाजपकडून शरद लाड?</t>
+          <t>Sushma Andhare यांच्यामुळे ठाकरेंच्या शिवसेनेत नाराजी? अंधारे बैठकीला येताच चंद्रकांत मोकाटेंचा काढता पाय</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/will-bjp-nominate-sharad-lad-for-graduate-constituency-sk95</t>
+          <t>https://www.lokshahi.com/news/is-sushma-andhare-causing-discontent-in-thackerays-shiv-sena</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
+          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
+          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
+          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
+          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
+          <t>विधि सीईटीत १०० पर्सेंटाईलचे चार विद्यार्थी चौकशीच्या फेऱ्यात; गैरप्रकाराचा संशय</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
+          <t>https://www.lokmat.com/national/four-students-with-100-percentile-in-law-cet-under-investigation-as-suspicion-of-malpractices-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
+          <t>भाजपमध्ये आणखी एका नेत्याचा प्रवेश; सांगलीच्या खानापूरमध्ये आता पक्षाची वाढणार ताकद</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
+          <t>https://www.navarashtra.com/politics/vaibhav-patil-joins-bjp-with-presence-of-chandrakant-patil-895969.html</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
+          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
+          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
+          <t>Sangli : परदेशी गुंतवणुकीत महाराष्ट्र देशात प्रथम</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
+          <t>https://pudhari.news/maharashtra/sangali/maharashtra-tops-india-in-foreign-investment-says-chandrakant-patil-dc95</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
+          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Sangli Politics: मलाही मंत्री व्हायचंय, भविष्यात काँग्रेससोबत राहीन असे नाही; विशाल पाटलांच्या विधानाने खळबळ</t>
+          <t>Gopichand Padalkar Politics : जिल्हा नियोजन बैठकीत पडळकर-आयुक्त गांधी यांच्यात खडाजंगी? नेमकं कारणं काय?</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/i-will-join-some-other-party-in-the-future-mp-vishal-patil-statement-creates-a-stir-a-a468-c746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-mla-gopichand-padalkar-vs-sangli-commissioner-gandhi-over-action-on-street-vendors-in-planning-meeting-as11</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
+          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
+          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
+          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
+          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis | सांगलीतील मोठे घराणे यायचे होते ते आले : मुख्यमंत्री फडणवीस</t>
+          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-prominent-family-joins-bjp-says-cm-fadnavis-sk95</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
+          <t>पदविका प्रवेशाला १ लाखांहून अधिक विद्यार्थ्यांचा प्रवेश; प्रवेशाला १४ ऑगस्टवरून ४ सप्टेंबरपर्यंत मुदतवाढ</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-diploma-admission-see-surge-chandrakant-patil-announce-deadline-extension-mumbai-print-news-rds-00-5299696/</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>कोरोना काळात बंद झालेला पुलोत्सव पुन्हा सुरू होणार; चंद्रकांत पाटलांची माहिती</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://www.lokmat.com/pune/bridge-festival-which-was-closed-during-corona-period-will-resume-information-from-chandrakant-patil-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>जळगावात महामार्गाचे काम रोखले; शेतकऱ्यांसह शिंदे गटाचे आमदार पोलिसांच्या ताब्यात</t>
+          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/thackeray-group-mlas-including-farmers-taken-into-police-custody-for-blocking-highway-work-in-jalgaon-amy-95-5246634/</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
+          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
+          <t>जळगावात महामार्गाचे काम रोखले; शेतकऱ्यांसह शिंदे गटाचे आमदार पोलिसांच्या ताब्यात</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
+          <t>https://www.loksatta.com/nashik/thackeray-group-mlas-including-farmers-taken-into-police-custody-for-blocking-highway-work-in-jalgaon-amy-95-5246634/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Jalgaon News : शेतकऱ्यांसह सत्ताधारी आमदारांचे जलसमाधी आंदोलन</t>
+          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-news-water-immersion-protest-by-farmers-and-ruling-mlas-ar84</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
+          <t>सांगलीत काँग्रेसला मोठा धक्का; जयश्रीताईंना पालकमंत्री भेटले, भाजप प्रवेशाचे ठरले</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
+          <t>https://www.lokmat.com/sangli/congress-rebel-jayashreetai-patil-from-sangli-will-join-bjp-a-a468-c746/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
+          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
+          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>सांगली : जिल्हा विकास योजनांचा 745 कोटींचा आराखडा</t>
+          <t>सासरच्या लोकांसह धर्मगुरूकडून धर्मांतरणासाठी दबाव, छळाला कंटाळून सात महिन्याच्या गर्भवतीची आत्महत्या</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-district-development-plan-745-crore-budget</t>
+          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Maharashtra Education News | अभियांत्रिकीच्या प्रवेशात आता तीनऐवजी चार ‘कॅप’ फेर्‍या</t>
+          <t>रोहित, बघतो तुला घरी गेल्यावर….! काका – पुतणे आणि टोमणे….</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-engineering-admission-four-cap-rounds-rule-change-sp96</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
+          <t>संजय राऊत अन् त्यांचा पक्षच 'पनवती'; राऊतांची 'पनवती' टीका भाजप नेत्याच्या जिव्हारी, प्रत्युत्तर देत म्हणाले...</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-leader-chandrakant-patil-has-responded-to-sanjay-raut-criticism-of-panvati-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>शेत जमिनीचे भूसंपादन करताना शेतकऱ्यांवर अन्याय होणार नाही, याची प्रशासनाने दक्षता घ्यावी - महसूल मंत्री चंद्रशेखर बावनकुळे</t>
+          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171768/</t>
+          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
+          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
+          <t>Farmer Loan Waiver : कर्जमाफीसाठी निवडणुकीची वाट पाहताय?; सतेज पाटलांची सरकारवर टिका</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://agrowon.esakal.com/agro-special/waiting-for-elections-to-waive-farm-loans-satej-patil-slams-maharashtra-govt</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>राज्यात 5,500 प्राध्यापकांची भरती: चंद्रकांत पाटील यांची घोषणा; प्राचार्य फोरम अधिवेशन उद्घाटन</t>
+          <t>Sanjay Shirsat PA controversy : सामाजिक न्याय मंत्र्यांचा 'पीए' बांधकाम कामगार? चंद्रकांतदादांचा चौकशीला नकार घंटा का?</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chandrakant-Patil-announces-recruitment-of-5500-professors-in-the-state</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivsena-minister-sanjay-shirsat-pa-name-household-items-list-sangli-bjp-minister-chandrakant-patil-ignores-inquiry-pp82-as11</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
+          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
+          <t>Kolhapur Politics : जिंकणाऱ्या पैलवानांवरच खेळणार डाव...'स्थानिक'ची कुस्ती जिंकण्यासाठी 'महायुती'चा प्लॅन ठरला!</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-election-bjp-ncp-shiv-sena-chandrakant-patil-hasan-mushrif-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>संजयकाकांसाठी भाजपचे दरवाजे बंद; चंद्रकांत पाटील म्हणाले, आम्ही दुसऱ्या पाटलांमागे</t>
+          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
+          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
+          <t>राज्यात उच्च शिक्षण क्षेत्रात भव्य भरती; प्राध्यापक व कर्मचाऱ्यांसाठी ८४०० पदांवर नियुक्तीची संधी</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
+          <t>https://www.nagpurtoday.in/grand-recruitment-in-higher-education-sector-in-the-state-appointment-notice-for-8400-posts-for-professors-and-employees/07251413</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>कला पदविका अभ्यासक्रमांसाठी प्रवेश घेण्याचे मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Minister-Chandrakant-Patil--appeal-to-take-admission-in-Arts-Diploma-courses</t>
+          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Chandrakant Patil</t>
+          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
+          <t>Maharashtra Politics: मी मंत्री कसा झालो, मलाही कळालं नाही, मुरलीधर मोहोळ यांच्या विधानाने राजकीय वर्तुळात चर्चा|VIDEO</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
+          <t>https://saamtv.esakal.com/video/murli-mohol-unexpected-union-minister-appointment-pune-mp-bjp-leaders-reactions-om0906</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सांगलीत काँग्रेसला मोठा धक्का! खासदार विशाल पाटलांच्या कट्टर समर्थकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://saamtv.esakal.com/video/big-blow-to-congress-vishal-patil-loyalists-in-sangli-former-mayor-joins-bjp-nck90</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
+          <t>बीफार्म आणि डीफार्म अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
+          <t>https://www.loksatta.com/mumbai/bpharm-dpharm-institutes-must-complete-norms-in-one-month-or-face-admission-ban-ocd-94-5266306/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
+          <t>Maharashtra Polytechnic admissions 2025: पॉलीटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/dte-maharashtra-polytechnic-admissions-2025-deadline-extended-for-applications-until-june-26/articleshow/121889185.cms</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
+          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
+          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
+          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
+          <t>Maharashtra forms new body to ensure effective implementation of NEP 2020 in higher education</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-forms-new-body-to-ensure-effective-implementation-of-nep-2020-in-higher-education-9964171/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Jayshree Patil : सांगलीत कॉँग्रेसला धक्का : वसंतदादा पाटील यांच्या नातसून जयश्री पाटील भाजपच्या वाटेवर</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://news24pune.com/congress-suffers-setback-in-sangli-vasantdada-patils-granddaughter-jayashree-patil-joins-bjp/</t>
+          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
+          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही : चंद्रकांत पाटील</t>
+          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/68678/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>दख्खन जत्रेतून स्वयंसहाय्यता बचत गटाच्या महिलांना आर्थिकदृष्ट्या स्वावलंबी होण्यास प्रोत्साहन - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>No Ajit Pawar vs Chandrakant Patil In Pune: PMC Polls Likely To Be Held Under Leadership Of Muralidhar Mohol</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://www.freepressjournal.in/pune/no-ajit-pawar-vs-chandrakant-patil-in-pune-pmc-polls-likely-to-be-held-under-leadership-of-muralidhar-mohol</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>अजित पवार म्हणाले, ठीक आहे तो रोहित बघतो घरी गेल्यावर</t>
+          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ajit-pawar-said-will-see-rohit-pawar-at-home/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
+          <t>Maharashtra: Over 1,600 EWS Students Granted Special Exemption For Certificate Submission</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-over-1600-ews-students-granted-special-exemption-for-certificate-submission</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Satara News : आणखी १७ शिक्षकांची दिव्यांग प्रमाणपत्रे अयोग्य; आठ टप्प्यांमध्ये ३७९ जणांची तपासणी</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Manoj Jarange Patil : मनोज जरांगे पाटील आंदोलनाआधीच सरकारचा मोठा निर्णय</t>
+          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/08/manoj-jarange-patil-governments-big/</t>
+          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
+          <t>Carry On Yojana: कॅरी ऑन योजना दुर्दैवी..' चंद्रकांत पाटलांच्या निर्णयाला ABVP चा विरोध</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>State to conduct second CET, colleges worried about delay in academic year</t>
+          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-to-conduct-second-cet-colleges-worried-about-delay-in-academic-year-101749409146794.html</t>
+          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Mahayuti parties battling each other during poaching spree</t>
+          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Maharashtra forms new body to ensure effective implementation of NEP 2020 in higher education</t>
+          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-forms-new-body-to-ensure-effective-implementation-of-nep-2020-in-higher-education-9964171/</t>
+          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Powerloom body appeals to shun trade with Turkiye &amp; Azerbaijan</t>
+          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/powerloom-body-appeals-to-shun-trade-with-turkiye-azerbaijan/articleshow/121218402.cms</t>
+          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
+          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Jab Baat Desh Ki Ho: Posters Hailing Operation Sindoor Put Up In Kothrud, Resident Urges To Stop Defacing</t>
+          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jab-baat-desh-ki-ho-posters-hailing-operation-sindoor-put-up-in-kothrud-resident-urges-to-stop-defacing-city</t>
+          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Good News For Punekars! Both Maharashtra Assembly And Council Deputy Chiefs Now From Pune As Anna Bansode</t>
+          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/good-news-for-punekars-both-maharashtra-assembly-and-council-deputy-chiefs-now-from-pune-as-anna-bansode-joins-neelam-gorhe</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
+          <t>Sangli Politics: मलाही मंत्री व्हायचंय, भविष्यात काँग्रेससोबत राहीन असे नाही; विशाल पाटलांच्या विधानाने खळबळ</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
+          <t>https://www.lokmat.com/sangli/i-will-join-some-other-party-in-the-future-mp-vishal-patil-statement-creates-a-stir-a-a468-c746/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Double Voting Allegations | Rohini Khadse वर Chandrakant Patil यांचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
+          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
+          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
+          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
+          <t>सांगलीत 'कमळ' सुसाट, काँग्रेसला गळती? भाजप दुसरा मोठा धक्का देण्याच्या तयारीत, आमदाराच्या वक्तव्याने खळबळ</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sudhir-gadgils-statement-fuels-bjp-congress-tensions-as-defection-rumors-gain-momentum-over-prithviraj-patils-bjp-entry-in-sangli-as11</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
+          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
+          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
+          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
+          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
+          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
+          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
+          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
+          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
+          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
+          <t>https://eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>पदविका प्रवेशाला १ लाखांहून अधिक विद्यार्थ्यांचा प्रवेश; प्रवेशाला १४ ऑगस्टवरून ४ सप्टेंबरपर्यंत मुदतवाढ</t>
+          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-diploma-admission-see-surge-chandrakant-patil-announce-deadline-extension-mumbai-print-news-rds-00-5299696/</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
+          <t>संजयकाकांसाठी भाजपचे दरवाजे बंद; चंद्रकांत पाटील म्हणाले, आम्ही दुसऱ्या पाटलांमागे</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
+          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
+          <t>कला पदविका अभ्यासक्रमांसाठी प्रवेश घेण्याचे मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
+          <t>https://eduvarta.com/Minister-Chandrakant-Patil--appeal-to-take-admission-in-Arts-Diploma-courses</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
+          <t>Chandrakant Patil</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
+          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
+          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
+          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Double Voting Allegations | Rohini Khadse वर Chandrakant Patil यांचा गंभीर आरोप</t>
+          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
+          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
+          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
+          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Sharad Lad : शरद लाडही भाजपच्या वाटेवर?</t>
+          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sharad-lad-on-way-to-join-bjp-sk95</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Sushma Andhare यांच्यामुळे ठाकरेंच्या शिवसेनेत नाराजी? अंधारे बैठकीला येताच चंद्रकांत मोकाटेंचा काढता पाय</t>
+          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/is-sushma-andhare-causing-discontent-in-thackerays-shiv-sena</t>
+          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
+          <t>Polytechnic | अभियांत्रिकी पदविका प्रवेश अर्ज नोंदणीसाठी आणखी मुदतवाढ, नवीन वेळापत्रक जाहीर - मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
+          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
+          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकरांनी औंध देवस्थानाची 34 एकर जमीन लाटली कागदपत्रे दाखवत राम खाडेंचा</t>
+          <t>जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/gopichand-padalkar-embezzled-34-acres-of-land-of-oundh-devasthan-ram-khade-makes-serious-allegations-by-showing-documents-1350057</t>
+          <t>https://ratnagirikhabardar.com/news/68678/</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>Satara News : आणखी १७ शिक्षकांची दिव्यांग प्रमाणपत्रे अयोग्य; आठ टप्प्यांमध्ये ३७९ जणांची तपासणी</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
+          <t>दख्खन जत्रेतून स्वयंसहाय्यता बचत गटाच्या महिलांना आर्थिकदृष्ट्या स्वावलंबी होण्यास प्रोत्साहन - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
+          <t>https://www.athawadavishesh.com/34215/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
+          <t>Sangli Politics : काँग्रेसला खिंडार; पृथ्वीराज पाटील शेकडो समर्थकांसह भाजपात!</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
+          <t>Police bust chain-snatching gang; two held, minor detained</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
+          <t>Pune: Chandrakant Patil Flags PMC Misgovernance Amid Delayed Elections; High-Level Meeting with Ajit Pawar Likely</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>‘पुण्यात ११०१ हून अधिक’ दाम्पत्यांकडून सामूहिक रुद्रपूजन</t>
+          <t>Delay In Pune's Equal Water Supply Scheme Sparks Public Discontent; MLA Chandrakant Patil Criticizes PMC</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/more-than-1101-couples-perform-collective-rudra-puja-in-pune-97635/</t>
+          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Abu Azmi writes letter to Maharashtra Speaker Rahul Narwekar to revoke his suspension</t>
+          <t>आता प्राचार्यांची सेवानिवृत्ती ६५ व्या वर्षी हाेणार : ना. चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
+          <t>https://www.lokmat.com/amravati/now-principals-will-retire-at-the-age-of-65-announcement-by-n-chandrakant-patil-a-a782-c1000/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Maharashtra News Updates: “ती महिला स्वत:हून पुड्या काढून देत होती”, प्रांजल खेवलकरांच्या वकिलाचा दावा; सगळंच संशयास्पद असल्याचा युक्तिवाद</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Pharmacy courses: राज्य सरकारने फार्मसी महाविद्यालये का थांबवली? विद्यार्थ्यांचा ओढा कमी होण्याचे कारण काय?</t>
+          <t>Maharashtra News Updates: “ती महिला स्वत:हून पुड्या काढून देत होती”, प्रांजल खेवलकरांच्या वकिलाचा दावा; सगळंच संशयास्पद असल्याचा युक्तिवाद</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
+          <t>Pharmacy courses: राज्य सरकारने फार्मसी महाविद्यालये का थांबवली? विद्यार्थ्यांचा ओढा कमी होण्याचे कारण काय?</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>संजय गांधी राष्ट्रीय उद्यानातील अतिक्रमकांचे पुनर्वसन लवकरच पूर्ण होणार – वनमंत्री गणेश नाईक</t>
+          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158932/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>केसरीचे आधारवड हरपले, केसरीभाऊ पाटील यांचे निधन</t>
+          <t>5 New Police Stations: शहरात होणार नवीन पाच पोलिस ठाणी; मुख्यमंत्र्यांकडून घोषणा</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/kesari-father-in-law-has-been-lost-kesaribhau-patil-passes-away-maharashtra-news-mhs25021502516</t>
+          <t>https://pudhari.news/maharashtra/pune/cm-announces-five-new-police-stations-in-the-city-sb97</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>5 New Police Stations: शहरात होणार नवीन पाच पोलिस ठाणी; मुख्यमंत्र्यांकडून घोषणा</t>
+          <t>Sangli News | कवठेमहांकाळ येथे जिल्हा व अतिरिक्त सत्रन्यायालयास उच्च न्यायालयाची मंजुरी</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/cm-announces-five-new-police-stations-in-the-city-sb97</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-news-high-court-approval-for-district-additional-sessions-judge-kavathemahanaghat-sk95</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Sangli News | कवठेमहांकाळ येथे जिल्हा व अतिरिक्त सत्रन्यायालयास उच्च न्यायालयाची मंजुरी</t>
+          <t>'वसंतदादा घराण्यात मुख्यमंत्रिपद, आमदारकी, खासदारकी...', आमच्यावरही असा अन्याय करावा; काँग्रेस नेत्याची जयश्री पाटलांवर उपरोधिक टीका</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-news-high-court-approval-for-district-additional-sessions-judge-kavathemahanaghat-sk95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prithviraj-patil-slams-jayshree-patil-bjp-entry-congress-reaction-sangli-politics-as11</t>
         </is>
       </c>
     </row>
@@ -6383,792 +6383,780 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>सरकार शब्द फिरवणार नाही, योग्यवेळी कर्जमाफीचा निर्णय घेणार - मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Malin Village: दुर्घटनेनंतरही माळीविासीयांना घरांसाठी अडीच वर्षांची प्रतीक्षा; गावकर्‍यांनी अडीच वर्षे काढली पत्राशेडमध्ये</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
+          <t>https://pudhari.news/maharashtra/pune/malin-survivors-homeless-after-2-years-sb97</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : विद्यापीठे, महाविद्यालयांतील रिक्त पदांची भरती होणार, अभियांत्रिकी संस्थांमध्येही पदभरतीस मान्यता, मुख्यमंत्री फडणवीसांचा निर्णय</t>
+          <t>सार्वजनिक विद्यापीठे, अशासकीय महाविद्यालयांमधील रिक्तपदांच्या भरतीस वेग येणार, अभियांत्रिकी संस्थांमध्ये 100 टक्के पदभरतीस मान्यता</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/recruitment-for-vacant-posts-in-public-universities-and-colleges-100-percent-recruitment-in-engineering-institutes-approved-devendra-fadnavis-decision-gkt-96-5213795/</t>
+          <t>https://www.etvbharat.com/mr/!state/public-universities-recruitment-of-vacancies-in-non-colleges-will-be-accelerated-100-percent-recruitment-in-engineering-institutions-maharashtra-news-mhs25070802041</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Malin Village: दुर्घटनेनंतरही माळीविासीयांना घरांसाठी अडीच वर्षांची प्रतीक्षा; गावकर्‍यांनी अडीच वर्षे काढली पत्राशेडमध्ये</t>
+          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/malin-survivors-homeless-after-2-years-sb97</t>
+          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
+          <t>NEET PG Counselling 2024: मेडिकल कौन्सिल कमिटीकडून 'कट ऑफ पर्सेटाइल'मध्ये घट; ५ पसेंटाइल असणारे 'नीट पीजी'साठी पात्र</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>10th Exam Result 2025: ... तर दहावीचा निकाल ठेवला जाणार राखीव; नाशिक विभागातील ६६८ शाळांचे काम अद्याप बाकी</t>
+          <t>Pune | हडपसरला नवीन मेट्रो मार्गिका, मुख्य शहराशी कनेक्टिव्हिटी मिळणार असल्याने प्रवास होणार वेगवान...</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
+          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>NEET PG Counselling 2024: मेडिकल कौन्सिल कमिटीकडून 'कट ऑफ पर्सेटाइल'मध्ये घट; ५ पसेंटाइल असणारे 'नीट पीजी'साठी पात्र</t>
+          <t>Thane News: ठाणे महापालिका क्षेत्रातील विद्यार्थ्यांचे भवितव्य संकटात! ६८ अनधिकृत शाळांविरोधात FIR</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>MAH CET 2025: बीबीए, बीसीए सीईटीसाठी चार दिवसांत नोंदणी सुरू; उच्च व तंत्रशिक्षण विभागाच्या आदेशानंतर सीईटी कक्षाची तयारी</t>
+          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/notification-regarding-the-conduction-of-additional-cet-for-bca-bba-bms-bbm-cet-2025-state-common-entrance-test-cell/articleshow/121692037.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
+          <t>Laxman Jagtap: लोकनेते लक्ष्मण जगताप हा प्रेरणादायी अध्याय: उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Polytechnic | अभियांत्रिकी पदविका प्रवेश अर्ज नोंदणीसाठी आणखी मुदतवाढ, नवीन वेळापत्रक जाहीर - मंत्री चंद्रकांत पाटील</t>
+          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>घडामोडींना वेग! मनोज जरांगे पाटलांच्या मुंबईतील आंदोलनाचा धसका; फडणवीस सरकारचा 'हा' सर्वात मोठा निर्णय</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/maratha-reservation-activist-manoj-jarange-patil-launched-a-major-movement-to-get-reservation-for-maratha-community-decision-of-fadnavis-government/</t>
+          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Laxman Jagtap: लोकनेते लक्ष्मण जगताप हा प्रेरणादायी अध्याय: उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>राज्यातील ग्रंथालयांसाठी फडणवीस सरकारचा ऐतिहासिक निर्णय : अनुदानात ४०% वाढ</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://ratnagirikhabardar.com/news/65971/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
+          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
+          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>MKCL - Devendra Fadnavis | MKCL's Silver Jubilee Foundation Day</t>
+          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
+          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
+          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Pune | हडपसरला नवीन मेट्रो मार्गिका, मुख्य शहराशी कनेक्टिव्हिटी मिळणार असल्याने प्रवास होणार वेगवान...</t>
+          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>राज्यातील ग्रंथालयांसाठी फडणवीस सरकारचा ऐतिहासिक निर्णय : अनुदानात ४०% वाढ</t>
+          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/65971/</t>
+          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>ABP Majha Headlines : 11:00AM : 14 April 2024 : Maharashtra News : एबीपी माझा हेडलाईन्स</t>
+          <t>Maharashtra CET Admission 2025: विद्यार्थ्यांसाठी दिलासादायक बातमी! BE/BTech आणि MBA प्रवेशासाठी मुदतवाढ जाहीर</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-top-100-headlines-14-april-2025-marathi-headlines-maharashtra-chandrakant-patil-on-sanjay-raut-1354271</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Sanjay Raut Vs Chandrakant Patil | Special Report | फुले चित्रपटावरुन राऊत-पाटलामध्ये जुंपली</t>
+          <t>Ramabai Ambedkar Punyatithi 2025: रमाबाई आंबेडकर यांच्या</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/sanjay-raut-vs-chandrakant-patil-special-report-raut-patla-clash-over-phule-movie-1038823.html</t>
+          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
+          <t>State may halt admissions to pharmacy colleges flouting norms</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
+          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
+          <t>Maharashtra: एनसीपी गुटों के विलय पर अटकलें तेज, भाजपा नेता बोले- हकीकत नहीं; शरद गुट से भी आई प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
+          <t>https://www.amarujala.com/india-news/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions-news-in-hindi-2025-05-14</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Maharashtra CET Admission 2025: विद्यार्थ्यांसाठी दिलासादायक बातमी! BE/BTech आणि MBA प्रवेशासाठी मुदतवाढ जाहीर</t>
+          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>भयंकर शेवट! दिरानेच केला भावजय व तिच्या मित्राचा खून; 'या' कारणांमुळे घडले मंगळवेढ्यातील दुहेरी हत्याकांड</t>
+          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/seven-people-murder-woman-a-man-over-a-farming-dispute-incident-in-gunjegaon-two-are-undergoing-treatment-in-a-private-hospital-three-are-in-custody/</t>
+          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
+          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Maharashtra cites poor standards, proposes no new pharmacy colleges for 5 years | Latest News India - Hindustan Times</t>
+          <t>Free education: मुलींना मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा, मंत्र्यांनी दिले थेट आदेश</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-cites-poor-standards-proposes-no-new-pharmacy-colleges-for-5-years-101750656728006.html</t>
+          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
+          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
+          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
+          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
+          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
+          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
+          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
+          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
+          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
+          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Jayant Patil Emotional: ‘एकत्र यायला हवं…’,जयंत पाटलांची भावनिक साद; पत्राने चर्चेला उधाण</t>
+          <t>Ahilyadevi Holkar’s legacy must be known to youth: CM</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/jayant-patil-emotional-letter-to-maharashtra-marathi/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
+          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Union Minister says daughter harassed in Maharashtra, Devendra Fadnavis reacts</t>
+          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/union-minister-raksha-khadse-daughter-molested-in-maharashtra-devendra-fadnavis-reacts-2687760-2025-03-02</t>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>What AI means for today’s classrooms</t>
+          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/dhie/science/2025/07/16/what-ai-means-for-todays-classrooms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>‘Dead bodies, debris’: Eyewitness recalls hearing ‘massive sound’ during Air India plane crash | Trending - Hindustan Times</t>
+          <t>'If anything happens to me...':Abu Azmi responds after suspension over Aurangzeb remarks</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
+          <t>https://english.mathrubhumi.com/news/india/abu-azmi-suspended-maharashtra-assembly-aurangzeb-42dc0e0b</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
+          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
+          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
+          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Aftermath of baby kidnap: Sangli guardian minister Chandrakant Patil announces enhanced security measures</t>
+          <t>Buldhana Shock: Doctor Dies After Setting Himself on Fire, Motive Still a Mystery</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/buldhana-shock-doctor-dies-after-setting-himself-on-fire-motive-still-a-mystery-a525/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Samiti, residents demand removal of unauthorised arch in Kalaburagi</t>
+          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/samiti-residents-demand-removal-of-unauthorised-arch-in-kalaburagi/article69147129.ece</t>
+          <t>https://mahasamvad.in/163883/</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
+          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
+          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>'If anything happens to me...':Abu Azmi responds after suspension over Aurangzeb remarks</t>
+          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://english.mathrubhumi.com/news/india/abu-azmi-suspended-maharashtra-assembly-aurangzeb-42dc0e0b</t>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
+          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
+          <t>BJP mantri’s remark sparks buzz of patch-up with Shiv Sena UBT</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
+          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Millennium National School shines at Invitational Taekwondo Inter-School Competition</t>
+          <t>Sanjay Raut claims 'some in BJP' want alliance with Uddhav Sena, Fadnavis retorts</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
+          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>मोठी बातमी! MHT-CET 2025 पीसीएम गटाची फेर परीक्षा; 'या' दिवशी होणार पेपर, सीईटी सेलची माहिती</t>
+          <t>BJP MLC first to record statement in CM’s SIT probe</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
+          <t>BJP leaders conduct back-to-back separate review meetings at PMC; Oppn questions lack of results</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
+          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
+          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
+          <t>पृथ्वीराज पाटील यांचा भाजप प्रवेश टाळला</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
+          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Sanjay Raut claims 'some in BJP' want alliance with Uddhav Sena, Fadnavis retorts</t>
+          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>BJP MLC first to record statement in CM’s SIT probe</t>
+          <t>Jayashree Patil - जयश्री पाटील यांचा आज भाजपमध्ये प्रवेश!</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/jayashree-patil-joins-bjp-maharashtra-politics-political-entry-news-msr87</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>BJP leaders conduct back-to-back separate review meetings at PMC; Oppn questions lack of results</t>
+          <t>काँग्रेसचे पृथ्वीराज पाटील यांचा भाजप प्रवेश निश्चित</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/congress-prithviraj-patil-to-join-bjp-dc95</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>BJP leader's statement on Raj Thackeray, 'Like one who predicts...'?</t>
+          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
+          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
+          <t>Sangli: वसंतदादा पाटील यांच्या नातसून जयश्रीताई पाटील भाजपमध्ये, अजितदादांना शह</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
+          <t>https://www.lokmat.com/sangli/former-chief-minister-vasantdada-patil-granddaughter-jayashreetai-patil-will-join-bjp-a-a746/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B561"/>
+  <dimension ref="A1:B562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,84 +503,84 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Maharashtra Minister dismisses rumours of rift in coalition, calls disagreements ‘natural’</t>
+          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-dismisses-rumours-of-rift-in-coalition-calls-disagreements-natural/article69452391.ece</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Calls Urgent Meeting on PMC Irregularities: Push for Accountability and Administrative Reform</t>
+          <t>Maharashtra Minister dismisses rumours of rift in coalition, calls disagreements ‘natural’</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/chandrakant-patil-pmc-irregularities-meeting-pune</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-dismisses-rumours-of-rift-in-coalition-calls-disagreements-natural/article69452391.ece</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Patil slams mismanagement by institutes, urges fee reforms for girls’ education</t>
+          <t>Chandrakant Patil Calls Urgent Meeting on PMC Irregularities: Push for Accountability and Administrative Reform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
+          <t>https://www.thebridgechronicle.com/news/chandrakant-patil-pmc-irregularities-meeting-pune</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>No more MH-CET exams outside Maharashtra: Chandrakant Patil</t>
+          <t>Patil slams mismanagement by institutes, urges fee reforms for girls’ education</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/mh-cet-exams-maharashtra-chandrakant-patil-10050751/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-slams-mismanagement-by-institutes-urges-fee-reforms-for-girls-education-101747081287274.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Political Jibe: Chandrakant Patil Says Sanjay Raut Has 'Political Jaundice'</t>
+          <t>No more MH-CET exams outside Maharashtra: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mh-cet-exams-maharashtra-chandrakant-patil-10050751/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sangli guardian minister Chandrakant Patil calls upon former BJP MP Sanjaykaka Patil, urges him to return</t>
+          <t>Political Jibe: Chandrakant Patil Says Sanjay Raut Has 'Political Jaundice'</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/sanjay-raut-afflicted-with-political-jaundice-i-know-the-right-medicine-chandrakant-patil-3588266</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Higher education minister Chandrakant Patil’s surprise visit to a city college</t>
+          <t>Outright Kunbi status to will not stand legal test: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/education/higher-education-minister-chandrakant-patil-surprise-visit-garware-college-free-education-girls</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
         </is>
       </c>
     </row>
@@ -611,12 +611,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Movie ‘Phule’ depicts discrimination of bygone era, no need to oppose it: Chandrakant Patil</t>
+          <t>Sangli guardian minister Chandrakant Patil calls upon former BJP MP Sanjaykaka Patil, urges him to return</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/sangli-guardian-minister-chandrakant-patil-calls-upon-former-bjp-mp-sanjaykaka-patil-urges-him-to-return-to-bjp/articleshow/119609029.cms</t>
         </is>
       </c>
     </row>
@@ -647,60 +647,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maharashtra-Karnataka border row: Govt reappoints Chandrakant Patil, Shambhuraj Desai as nodal ministers to resolve dispute</t>
+          <t>Movie ‘Phule’ depicts discrimination of bygone era, no need to oppose it: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-karnataka-border-chandrakant-patil-shambhuraj-desai-9862005/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/movie-phule-depicts-discrimination-of-bygone-era-no-need-to-oppose-it-chandrakant-patil/articleshow/120288218.cms</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>After Kulkarni’s criticism, Mohol and Chandrakant Patil come out in support of BJP workers</t>
+          <t>Maharashtra-Karnataka border row: Govt reappoints Chandrakant Patil, Shambhuraj Desai as nodal ministers to resolve dispute</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-karnataka-border-chandrakant-patil-shambhuraj-desai-9862005/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1,000 new personnel to join Pune Police force: Chandrakant Patil</t>
+          <t>After Kulkarni’s criticism, Mohol and Chandrakant Patil come out in support of BJP workers</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/1000-new-personnel-to-join-pune-police-force-chandrakant-patil-101751829456309.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/after-kulkarni-s-criticism-mohol-and-chandrakant-patil-come-out-in-support-of-bjp-workers-101744225445616.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18.06.2025: Minister for Higher and Technical Education Chandrakant Patil meets Governor to discuss on various matters pertaining to higher education</t>
+          <t>Higher education minister Chandrakant Patil’s surprise visit to a city college</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/18-06-2025-minister-for-higher-and-technical-education-chandrakant-patil-meets-governor-to-discuss-on-various-matters-pertaining-to-higher-education/</t>
+          <t>https://www.thebridgechronicle.com/education/higher-education-minister-chandrakant-patil-surprise-visit-garware-college-free-education-girls</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maharashtra Minister asks Jarange to hold talks with Govt ahead of protests</t>
+          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-asks-jarange-to-hold-talks-with-govt-ahead-of-protests/article69969205.ece</t>
+          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
         </is>
       </c>
     </row>
@@ -719,60 +719,60 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
+          <t>Maharashtra Minister asks Jarange to hold talks with Govt ahead of protests</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-minister-asks-jarange-to-hold-talks-with-govt-ahead-of-protests/article69969205.ece</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MVA under a cloud, Sanjay Raut says many in BJP keen on aligning with Sena (UBT), feeling ‘mutual’</t>
+          <t>Engineering admission process revision: Four CAP rounds instead of three, stricter admission confirmation rules: Patil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/engineering-admission-process-revision-four-cap-rounds-10050523/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vishal Patil turns down BJP minister’s offer to join alliance</t>
+          <t>100 per cent fee waiver for EWS girls: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>100 per cent fee waiver for EWS girls: Chandrakant Patil</t>
+          <t>MVA under a cloud, Sanjay Raut says many in BJP keen on aligning with Sena (UBT), feeling ‘mutual’</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/100-per-cent-fee-waiver-for-ews-girls-chandrakant-patil-101750360390574.html</t>
+          <t>https://indianexpress.com/article/political-pulse/mva-sanjay-raut-bjp-sena-ubt-9808199/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Outright Kunbi status to will not stand legal test: Chandrakant Patil</t>
+          <t>Vishal Patil turns down BJP minister’s offer to join alliance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/outright-kunbi-status-to-will-not-stand-legal-test-chandrakant-patil/articleshow/123487443.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/vishal-patil-turns-down-bjp-ministers-offer-to-join-alliance/articleshow/119084771.cms</t>
         </is>
       </c>
     </row>
@@ -803,24 +803,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grateful minister urges edu trust to go autonomous</t>
+          <t>Engg admission: Soon, four CAPs and seat confirmation by round 3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/engg-admission-soon-four-caps-and-seat-confirmation-by-round-3/articleshow/121657513.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
+          <t>Grateful minister urges edu trust to go autonomous</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/grateful-minister-urges-edu-trust-to-go-autonomous-101752002033361.html</t>
         </is>
       </c>
     </row>
@@ -839,96 +839,96 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
+          <t>Guardian Ministers: Ajit Pawar (Pune, Beed), Chandrakant Patil (Sangli), Madhuri Misal (Kolhapur)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
+          <t>https://www.thebridgechronicle.com/news/guardian-ministers-ajit-pawar-pune-beed-chandrakant-patil-sangli-madhuri-misal-kolhapur</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
+          <t>Congress Sangli city prez Prithviraj Patil to join BJP</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/congress-sangli-city-prez-prithviraj-patil-to-join-bjp/articleshow/123265799.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aftermath of baby kidnap: Sangli guardian minister Chandrakant Patil announces enhanced security measures</t>
+          <t>Open the Bridge Without Delay: Chandrakant Patil Orders PMC to Acquire Land</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
+          <t>https://www.thebridgechronicle.com/pune/open-bridge-without-delay-chandrakant-patil-orders-pmc-land-acquisition</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
+          <t>Aftermath of baby kidnap: Sangli guardian minister Chandrakant Patil announces enhanced security measures</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/aftermath-of-baby-kidnap-sangli-guardian-minister-chandrakant-patil-announces-enhanced-security-measures-at-miraj-govt-hospital/articleshow/121006495.cms</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
+          <t>If some leader leaves, not necessarily people join him: Vishwajeet Kadam</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
+          <t>Fadnavis will seek Dhananjay Munde’s resignation if he is linked to Beed sarpanch murder: BJP’s Chandrakant Patil</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/fadnavis-will-seek-dhananjay-mundes-resignation-if-he-is-linked-to-beed-sarpanch-murder-bjps-chandrakant-pati/article69146499.ece</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>If some leader leaves, not necessarily people join him: Vishwajeet Kadam</t>
+          <t>Former CM Vasantdada Patil’s granddaughter-in-law joins BJP</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/if-some-leader-leaves-not-necessarily-people-join-him-vishwajeet-kadam/articleshow/123289946.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/former-cm-vasantdada-patils-granddaughter-in-law-joins-bjp/articleshow/121893459.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>RSS holds two-day brainstorming session with BJP, allied outfits</t>
+          <t>'Saw smoke in the…': Eyewitness at Ahmedabad airport describes Air India plane crash | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/rss-holds-two-day-brainstorming-session-with-bjp-allied-outfits-3362607</t>
+          <t>https://www.hindustantimes.com/trending/saw-smoke-in-the-eyewitness-at-ahmedabad-airport-describes-air-india-crash-101749727540094.html</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>State’s tech edu minister reviews fee waiver for women students</t>
+          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
         </is>
       </c>
     </row>
@@ -983,48 +983,48 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DPDC meeting on Thursday</t>
+          <t>State’s tech edu minister reviews fee waiver for women students</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/states-tech-edu-minister-reviews-fee-waiver-for-women-students/articleshow/118310028.cms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
+          <t>DPDC meeting on Thursday</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/dpdc-meeting-on-thursday-101738176153028.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
+          <t>Sub-centre of SPPU slated to be inaugurated by May-end in Nashik’s Shivnai area; Chandrakant Patil instru</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/sub-centre-of-sppu-slated-to-be-inaugurated-by-may-end-in-nashiks-shivnai-area-chandrakant-patil-instructs-officials-to-expedite-facility/articleshow/121036464.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
+          <t>Patil asks PMC to acquire land on priority as Balewadi-Wakad bridge lies unused</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/patil-asks-pmc-to-acquire-land-on-priority-as-balewadi-wakad-bridge-lies-unused-101751741109744.html</t>
         </is>
       </c>
     </row>
@@ -1055,48 +1055,48 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
+          <t>Azmi is suspended, Yogi says send him to UP for ‘treatment’</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/azmi-is-suspended-yogi-says-send-him-to-up-for-treatment/articleshow/118742113.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mahayuti parties battling each other during poaching spree</t>
+          <t>Girls' Free Education Scheme Exists Only on Paper: Higher Education Minister to Inspect Colleges</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
+          <t>https://www.thebridgechronicle.com/news/girls-free-education-scheme-exists-only-on-paper-higher-education-minister-to-inspect-colleges</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Pune News: Chandrakant Patil Issues Ultimatum to Pune Municipal Corporation Over Solid Waste Management Project</t>
+          <t>Def min likely to inaugurate Peshwa memorial at Parvati</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://punemirror.com/pune-mirror-explore/pune-news-chandrakant-patil-issues-ultimatum-to-pune-municipal-corporation-over-solid-waste-management-project/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/def-min-likely-to-inaugurate-peshwa-memorial-at-parvati-101736539722952.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
+          <t>Mahayuti parties battling each other during poaching spree</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-parties-battling-each-other-during-poaching-spree-101751053618819.html</t>
         </is>
       </c>
     </row>
@@ -1211,336 +1211,336 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
+          <t>Ahead of Jarange stir in Mumbai, cabinet sub-committee on Maratha quota reconstituted, Vikhe Patil now ne</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ahead-of-jarange-stir-in-mumbai-cabinet-sub-committee-on-maratha-quota-reconstituted-vikhe-patil-now-new-head/articleshow/123460725.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>State committed to opposing Almatti height rise, says minister Vikhe Patil</t>
+          <t>State announces new recruitment process for university teachers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-announces-new-recruitment-process-for-university-teachers-101740684012522.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Protesters oppose name expansion proposal of Shivaji University in Kolhapur</t>
+          <t>Local Shiv Sena leader, six others arrested for harassing MoS Raksha Khadse’s daughter</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Mar/03/three-more-held-for-harassing-union-minister-khadses-daughter-friends-in-jalgaon</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
+          <t>Protesters oppose name expansion proposal of Shivaji University in Kolhapur</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/protesters-oppose-name-expansion-proposal-of-shivaji-university-in-kolhapur/articleshow/119544233.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
+          <t>State committed to opposing Almatti height rise, says minister Vikhe Patil</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/state-committed-to-opposing-almatti-height-rise-says-minister-vikhe-patil/articleshow/118652829.cms</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Islampur to be renamed Ishwarpur</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Minister</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
+          <t>https://theprint.in/india/cet-for-courses-in-maharashtra-not-to-be-held-outside-state-to-prevent-malpractices-minister/2649554/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
+          <t>State government plans to grant university status to JBIMS | Mumbai news</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/state-government-plans-to-grant-university-status-to-jbims-101743881532444.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
+          <t>Islampur to be renamed Ishwarpur</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/islampur-to-be-renamed-ishwarpur-101752864742122.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Maharashtra Introduces New Rule, Stops CET Exams at Centres Outside the State</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
+          <t>https://thelivenagpur.com/2025/06/06/maharashtra-introduces-new-rule-stops-cet-exams-at-centres-outside-the-state/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
+          <t>'Many in BJP want alliance with Uddhav Thackeray': Sena UBT's Sanjay Raut stirs speculation</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
+          <t>https://www.businesstoday.in/india/story/many-in-bjp-want-alliance-with-uddhav-thackeray-sena-ubts-sanjay-raut-stirs-speculation-462645-2025-01-30</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
+          <t>https://theprint.in/india/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt/2727471/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
+          <t>Chandrakant Patil Takes Action on Kothrud’s Road, Water, and Traffic Issues</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
+          <t>https://punemirror.com/city/civic/chandrakant-patil-takes-action-on-kothrud-s-road-water-and-traffic-issues/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
+          <t>Marathwada varsity stops PG admissions in 113 colleges after 'irregularities' come to fore</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/marathwada-varsity-stops-pg-admissions-in-113-colleges-after-irregularities-come-to-fore/122912620</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
+          <t>Education News: Over 11K Posts of Professors Vacant in State</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
+          <t>https://punemirror.com/state/education-news-over-11k-posts-of-professors-vacant-in-state/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
+          <t>Maharashtra Unveils Ambitious Higher Education Reforms</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
+          <t>https://punemirror.com/education/maharashtra-unveils-ambitious-higher-education-reforms/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
+          <t>Maharashtra appoints two ministers for border dispute case, Karnataka not serious: Experts</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
+          <t>https://www.newindianexpress.com/states/karnataka/2025/Mar/04/maharashtra-appoints-two-ministers-for-border-dispute-case-karnataka-not-serious-experts</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
+          <t>Pune Railway Station to Undergo Major Transformation; World-class facilities including four new platforms are planned</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2126625</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
+          <t>18.06.2025: Higher &amp; Tech Education Minister meets Governor</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-06-2025-higher-tech-education-minister-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
+          <t>CET for courses in Maharashtra not to be held outside state to prevent malpractices: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
+          <t>https://news.careers360.com/cet-for-courses-in-maharashtra-not-be-held-outside-state-prevent-malpractices-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Maharashtra: Samajwadi Party’s Abu Azmi suspended from Assembly session for remark about Aurangzeb</t>
+          <t>4 Toppers, 1 Centre: Patna CET Row Prompts Maharashtra To Ban Out-Of-State Exam Centres</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1079939/maharashtra-samajwadi-partys-abu-azmi-suspended-from-assembly-session-for-remark-about-aurangzeb</t>
+          <t>https://www.news18.com/education-career/4-toppers-1-centre-patna-cet-row-prompts-maharashtra-to-ban-out-of-state-exam-centres-ws-dkl-9372134.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
+          <t>Jayashree Patil Joins BJP: Major Setback for Congress in Sangli</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
+          <t>https://english.lokshahi.com/politics/jayashree-patil-to-join-bjp-today-maharashtra-politics-congress</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
+          <t>Baner-Balewadi Traffic Woes Get High-Level Attention at Key PMC Meeting</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
+          <t>https://punemirror.com/city/civic/baner-balewadi-traffic-woes-get-high-level-attention-at-key-pmc-meeting/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
+          <t>Maharashtra: Samajwadi Party’s Abu Azmi suspended from Assembly session for remark about Aurangzeb</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
+          <t>https://scroll.in/latest/1079939/maharashtra-samajwadi-partys-abu-azmi-suspended-from-assembly-session-for-remark-about-aurangzeb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
+          <t>All Maharashtra professional colleges can now charge 3x fees for management, 5x for NRI seats</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
+          <t>https://news.careers360.com/maharashtra-fee-hike-all-engineering-medical-professional-colleges-fra-charge-3x-fees-for-management-5x-nri-quota-seats</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BJP district rural unit president elected in Kalaburagi</t>
+          <t>Maharashtra may ‘stop’ CAP admission 2025 if pharmacy colleges don't meet PCI guidelines</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
+          <t>https://news.careers360.com/maharashtra-may-stop-bpharm-cap-admission-2025-if-pharmacy-colleges-dont-meet-pci-guidelines-one-month-inspection</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
+          <t>17.01.2025 : Governor presides 61st Annual Convocation of Shivaji University</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/gallery/17-01-2025-governor-presides-61st-annual-convocation-of-shivaji-university/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Maharashtra State CET Cell launches CET-ATAL module for mock tests</t>
+          <t>MHT CET 2025 CAP counselling expanded to four rounds under new rule; what's changed?</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
+          <t>https://news.careers360.com/mht-cet-2025-cap-counselling-expanded-four-rounds-new-rule-round-1-btech-mbbs-pharmacy-admissions-whats-changed</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BJP leader's statement on Raj Thackeray, 'Like one who predicts...'?</t>
+          <t>Maharashtra State CET Cell launches CET-ATAL module for mock tests</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
+          <t>https://news.careers360.com/maharashtra-state-cet-cell-launches-cet-atal-module-for-mock-tests</t>
         </is>
       </c>
     </row>
@@ -1607,24 +1607,24 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
+          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
+          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces Approval For Teacher Recruitment Process, Introduces New</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-chandrakant-patil-announces-approval-for-teacher-recruitment-process-introduces-new-merit-based-selection-method</t>
         </is>
       </c>
     </row>
@@ -1643,60 +1643,60 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
+          <t>Pune: Major Announcement for Girls’ Education, Minister Chandrakant Patil to Inspect 100 Colleges, Review Fee Waiver Implementation</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
+          <t>https://www.mypunepulse.com/pune-major-announcement-for-girls-education-minister-chandrakant-patil-to-inspect-100-colleges-review-fee-waiver-implementation/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Pushes for AI-Based Challan System</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
+          <t>https://www.mypunepulse.com/traffic-congestion-free-kothrud-minister-chandrakant-patil-pushes-for-ai-based-challan-system/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ensure Safety Measures For Pune Hills: Higher And Technical Education Minister Chandrakant Patil’s Directives</t>
+          <t>Maharashtra News: Recruitment Of 4,435 Assistant Professors To Begin Soon, Says Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-recruitment-of-4435-assistant-professors-to-begin-soon-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Warns PMC, Shut Down Sus Waste Project Or Face Protest</t>
+          <t>Ensure Safety Measures For Pune Hills: Higher And Technical Education Minister Chandrakant Patil’s Directives</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
+          <t>https://www.mypunepulse.com/ensure-safety-measures-for-pune-hills-higher-and-technical-education-minister-chandrakant-patils-directives/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pune: Jitendra Awhad Taunts Chandrakant Patil: Dont Ask Who Is Dhangekar As Former Congress MLA Ravindra</t>
+          <t>Pune: Chandrakant Patil Warns PMC, Shut Down Sus Waste Project Or Face Protest</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-jitendra-awhad-tells-chandrakant-patil-dont-ask-who-is-dhangekar-as-former-congress-mla-ravindra-dhangekar-ready-to-join-shinde-faction</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-warns-pmc-shut-down-sus-waste-project-or-face-protest/</t>
         </is>
       </c>
     </row>
@@ -1715,5448 +1715,5460 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
+          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
+          <t>No Ajit Pawar vs Chandrakant Patil In Pune: PMC Polls Likely To Be Held Under Leadership Of Muralidhar Mohol</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
+          <t>https://www.freepressjournal.in/pune/no-ajit-pawar-vs-chandrakant-patil-in-pune-pmc-polls-likely-to-be-held-under-leadership-of-muralidhar-mohol</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
+          <t>Global Ganesh Festival 2025: Eknath Shinde to Lead, Chandrakant Patil as Chief Receptionist</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
+          <t>https://www.punekarnews.in/global-ganesh-festival-2025-eknath-shinde-to-lead-chandrakant-patil-as-chief-receptionist/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
+          <t>Traffic Congestion-Free Kothrud: Minister Chandrakant Patil Directs Introduction Of AI-Based Challan System</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
+          <t>https://www.freepressjournal.in/pune/traffic-congestion-free-kothrud-minister-chandrakant-patil-directs-introduction-of-ai-based-challan-system</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
+          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
+          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
+          <t>Maharashtra Minister Chandrakant Patil Announces 6-Month NAAC Extension, Lifts Admission Freeze On 229 Mumbai</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-announces-6-month-naac-extension-lifts-admission-freeze-on-229-mumbai-university-colleges</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
+          <t>Mumbai: Minister Chandrakant Patil Directs Formation Of Committee To Expedite AI University Establishment</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-chandrakant-patil-directs-formation-of-committee-to-expedite-ai-university-establishment</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
+          <t>Minister Chandrakant Patil Orders Comprehensive Report on Challenges Faced by Educational Institutions in Maharashtra</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
+          <t>https://www.punekarnews.in/minister-chandrakant-patil-orders-comprehensive-report-on-challenges-faced-by-educational-institutions-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
+          <t>Pune: Chandrakant Patil Orders Immediate Measures To Resolve Baner-Balewadi Traffic Woes</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
+          <t>https://www.mypunepulse.com/pune-chandrakant-patil-orders-immediate-measures-to-resolve-baner-balewadi-traffic-woes/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
+          <t>'To Prevent Malpractices': Maharashtra Minister Says CET Exam Not To Be Held Outside State</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
+          <t>https://www.thedailyjagran.com/maharashtra/to-prevent-malpractices-maharashtra-minister-says-cet-exam-not-to-be-held-outside-state-10243139</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
+          <t>Maharashtra: Judo Excellence Centre To Be Established In Sangli, Announces Minister Chandrakant Patil</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-judo-excellence-centre-to-be-established-in-sangli-announces-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
+          <t>Pune: Chandrakant Patil Orders Detailed Report On Traffic, Roads, and Water Woes In Kothrud; Says Such Issues</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
+          <t>https://www.freepressjournal.in/pune/pune-chandrakant-patil-orders-detailed-report-on-traffic-roads-and-water-woes-in-kothrud-says-such-issues-will-not-be-tolerated</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
+          <t>Mumbai: Ensure Timely Payment Of Honorarium For Guest Lecturers In Govt Polytechnic Colleges, Says Minister</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-ensure-timely-payment-of-honorarium-for-guest-lecturers-in-govt-polytechnic-colleges-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
+          <t>Maharashtra: Higher Education Minister Chandrakant Patil Chairs Meeting To Discuss Establishment Of Separate</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-higher-education-minister-chandrakant-patil-chairs-meeting-to-discuss-establishment-of-separate-arts-university</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
+          <t>Pune: Maharashtra Minister Chandrakant Patil Inaugurates Reconstructed Steps To Mhatoba Mandir In Kothrud</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
+          <t>https://www.freepressjournal.in/pune/pune-maharashtra-minister-chandrakant-patil-inaugurates-reconstructed-steps-to-mhatoba-mandir-in-kothrud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
+          <t>Maharashtra Politics: BJP Invites Sangli MP Vishal Patil To Join Party, But He Declines, Calls For Unity In</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-invites-sangli-mp-vishal-patil-to-join-party-but-he-declines-calls-for-unity-in-development</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>'To Prevent Malpractices': Maharashtra Minister Says CET Exam Not To Be Held Outside State</t>
+          <t>Pune: High-Level Meeting Held to Resolve Baner-Balewadi Traffic Woes; Minister Chandrakant Patil Orders Immediate Action</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/to-prevent-malpractices-maharashtra-minister-says-cet-exam-not-to-be-held-outside-state-10243139</t>
+          <t>https://www.punekarnews.in/pune-high-level-meeting-held-to-resolve-baner-balewadi-traffic-woes-minister-chandrakant-patil-orders-immediate-action/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Maharashtra Assembly Monsoon Session: Opposition Raises Alarm Over Poor Living Conditions At Mumbai</t>
+          <t>1,000 New Cops to Join Pune Police Force as City Expands: Chandrakant Patil</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-assembly-monsoon-session-opposition-raises-alarm-over-poor-living-conditions-at-mumbai-universitys-cama-girls-hostel-govt-denies-lapses</t>
+          <t>https://www.punekarnews.in/1000-new-cops-to-join-pune-police-force-as-city-expands-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
+          <t>Maharashtra’s ‘Atal’ Initiative: Over 1 Lakh Students Registered For Entrance Exam Preparation,</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-atal-initiative-over-1-lakh-students-registered-for-entrance-exam-preparation-education-minister-chandrakant-patil-urges-more-to-join</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CET Exams to Be Held Only Within Maharashtra</t>
+          <t>Anna Bansode set to become Maha Assembly’s Deputy Speaker</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
+          <t>https://www.socialnews.xyz/2025/03/25/anna-bansode-set-to-become-maha-assemblys-deputy-speaker/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
+          <t>Maharashtra News: Investigation Ordered Into Financial Irregularities At Govt Pharma College In Karad, Says</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-investigation-ordered-into-financial-irregularities-at-govt-pharma-college-in-karad-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
+          <t>Maharashtra Govt Mulls ₹2,000 Monthly Aid For Female Students Under Earn And Learn Scheme: Minister</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-mulls-2000-monthly-aid-for-female-students-under-earn-and-learn-scheme-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
+          <t>Maharashtra Assembly Monsoon Session: Opposition Raises Alarm Over Poor Living Conditions At Mumbai</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-assembly-monsoon-session-opposition-raises-alarm-over-poor-living-conditions-at-mumbai-universitys-cama-girls-hostel-govt-denies-lapses</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Pune: Union Minister Muralidhar Mohol Supports MLA Hemant Rasanes Hoarding-Free Kasba Initiative</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/pune-union-minister-muralidhar-mohol-supports-mla-hemant-rasanes-hoarding-free-kasba-initiative</t>
+          <t>https://www.newsdrum.in/national/ahead-of-mumbai-protest-maharashtra-minister-asks-jarange-to-hold-talks-with-govt-9725948</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>From Pan Tapri Owner to Maharashtra Assembly Deputy Speaker: Pimpri MLA Anna Bansode Wins Unopposed</t>
+          <t>CET Exams to Be Held Only Within Maharashtra</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/from-pan-tapri-owner-to-maharashtra-assembly-deputy-speaker-pimpri-mla-anna-bansode-wins-unopposed</t>
+          <t>https://www.mypunepulse.com/cet-exams-to-be-held-only-within-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>VIDEO I Attention Punekars! Two Municipal Corporations In Pune Soon With PMC Bifurcation—Read Details Here</t>
+          <t>Maharashtra Government Implements New Transparent Recruitment Process for University Faculty</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/video-i-attention-punekars-two-municipal-corporations-in-pune-soon-with-pmc-bifurcationread-details-here</t>
+          <t>https://www.punekarnews.in/maharashtra-government-implements-new-transparent-recruitment-process-for-university-faculty/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
+          <t>Maharashtra Govt Approves 100% Recruitment In Engineering Colleges, Boosts Higher Education Quality</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-approves-100-recruitment-in-engineering-colleges-boosts-higher-education-quality/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
+          <t>CM Devendra Fadnavis Inaugurates ₹713 Crore Development Projects In Ichalkaranji, Vows Swift Approval For</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
+          <t>https://www.freepressjournal.in/pune/cm-devendra-fadnavis-inaugurates-713-crore-development-projects-in-ichalkaranji-vows-swift-approval-for-future-proposals</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Mr. Sunjjoy Chaudhri Leads Team Veer Santaji at Khasdar Celebrity Cricket League 2025, Celebrating Pune’s Grand Festival with Support from Mr. Murlidhar Mohol and Mr. Chandrakant Patil</t>
+          <t>Pune: Union Minister Muralidhar Mohol Supports MLA Hemant Rasanes Hoarding-Free Kasba Initiative</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
+          <t>https://www.freepressjournal.in/pune/pune-union-minister-muralidhar-mohol-supports-mla-hemant-rasanes-hoarding-free-kasba-initiative</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
+          <t>From Pan Tapri Owner to Maharashtra Assembly Deputy Speaker: Pimpri MLA Anna Bansode Wins Unopposed</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
+          <t>https://www.freepressjournal.in/pune/from-pan-tapri-owner-to-maharashtra-assembly-deputy-speaker-pimpri-mla-anna-bansode-wins-unopposed</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
+          <t>Pune Hosts Grand ‘Warkari Bhaktiyog 2025’ on International Yoga Day</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
+          <t>https://www.punekarnews.in/pune-hosts-grand-warkari-bhaktiyog-2025-on-international-yoga-day/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
+          <t>Union Minister of Jal Shakti CR Patil Reviewed Key Projects of WII under NMCG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
+          <t>https://affairscloud.com/union-minister-of-jal-shakti-cr-patil-reviewed-key-projects-of-wii-under-nmcg/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा</t>
+          <t>Mr. Sunjjoy Chaudhri Leads Team Veer Santaji at Khasdar Celebrity Cricket League 2025, Celebrating Pune’s Grand Festival with Support from Mr. Murlidhar Mohol and Mr. Chandrakant Patil</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
+          <t>https://www.hindustanmetro.com/mr-sunjjoy-chaudhri-leads-team-veer-santaji-at-khasdar-celebrity-cricket-league-2025-celebrating-punes-grand-festival-with-support-from-mr-murlidhar-mohol-and-mr-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
+          <t>Pune: Minister Orders Compulsory Land Acquisition to Open Balewadi–Wakad Mula River Bridge</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
+          <t>https://www.punekarnews.in/pune-minister-orders-compulsory-land-acquisition-to-open-balewadi-wakad-mula-river-bridge/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
+          <t>Maharashtra State CET Cell Launches visionary initiative CET-ATAL - Module for Mock Tests</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
+          <t>https://www.hindustanmetro.com/maharashtra-state-cet-cell-launches-visionary-initiative-cet-atal-module-for-mock-tests/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>सांगलीचे अपक्ष खासदार विशाल पाटील यांना चंद्रकांत पाटील यांच्याकडून खुली ऑफर</t>
+          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Maharashtra Maratha Committee</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/chandrakant-patil-makes-an-open-offer-to-sangli-independent-mp-vishal-patil-to-join-bjp/34589</t>
+          <t>https://saralnama.in/other/5176/radhakrishna-vikhe-patil-appointed-chairman-of-maharashtra-maratha-committee/</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
+          <t>18.06.2025: उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची विभागाच्या वरिष्ठ अधिकाऱ्यांसह राज्यपालांसोबत विविध विषयांवर चर्चा | राजभवन महाराष्ट्र | भारत</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/gallery/18-06-2025-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%BF%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>मुंबईत दीड कोटी अमराठी, त्यांच्याशी‌ बोलताना हिंदी हवी की नको; चंद्रकांत पाटील यांचं विधान</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-minister-chandrakant-patil-said-one-and-half-crore-non-marathi-live-in-mumbai-for-them-should-have-hindi-be-spoken-to-or-not-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
+          <t>अमित शाहांना भेटण्यासाठी लोक माझ्याकडे यायचे, आता मात्र…चंद्रकांत पाटलांच्या विधानाची चर्चा!</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-murlidhar-mohol-now-become-an-after-getting-central-ministerial-post-1444270.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Vishal Patil: मंत्री चंद्रकांत पाटील यांच्याकडून अपक्ष खासदार विशाल पाटील यांना ऑफर</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/171311/</t>
+          <t>https://marathi.abplive.com/news/sangli/minister-chandrakant-patil-offers-to-join-bjp-to-independent-mp-vishal-patil-after-get-offer-vishal-patil-said-if-i-am-getting-an-offer-of-joining-party-i-think-i-am-doing-a-good-job-1349507</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
+          <t>Pune News: राज्यात 5,500 अधिव्याख्याता, 2,900 कर्मचारी भरतीला मंजुरी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-approves-5500-professors-2900-staff-recruitment-sb97</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांना हवंय देवेंद्र फडणवीसांचं पद? थेट म्हणाले, सर्व मंत्रिपदं भूषवली आता फक्त…</t>
+          <t>Sharad Pawar : शरद पवारांच्या गोटात खळबळ ! चंद्रकांत पाटलांनी फोडला जिल्हा उपाध्यक्ष</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-i-am-senior-minister-only-home-minister-department-is-remain-1389806.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/vinod-taral-to-join-shinde-sena-chandrakant-patil-gains-sharad-pawar-eknath-khadse-loses-jalgaon-gs97</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Chandrakant patil: एकनाथ शिंदेकडे 75 नगरसेवक गेलेत, आता मुंबई महापालिकेसाठी राज ठाकरे राजकीय</t>
+          <t>“राज्यात सरकार अस्थिर करण्याचा काहींचा प्रयत्न” – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-urges-farmers-to-focus-on-compensation-not-protest-ocd-94-5309717/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>विशाल पाटील कसे विजयी झाले हे जाहीरपणे सांगू शकत नाही : चंद्रकांत पाटील</t>
+          <t>राज्याला उच्च शिक्षणाचे जागतिक केंद्र बनविणार – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-cannot-reveal-how-vishal-patil-won-dc95</t>
+          <t>https://mahasamvad.in/171311/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>उच्च व तंत्रशिक्षण मंत्र्यांच्या घरातील कपाटांमध्ये…; स्वतः चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>मुलींच्या शिक्षणासाठी मोठी घोषणा: मंत्री चंद्रकांत पाटील 100 महाविद्यालयांना देणार अचानक भेटी, फी माफीची अं...</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/akshardhara-book-gallery-maruti-chitampally-literature-gallery-inaugurated-chandrakant-patil-pune-print-news-ssb-93-5260696/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/minister-chandrakant-patil-will-pay-surprise-visits-to-100-colleges-check-the-implementation-of-fee-waiver-134473291.html</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>केंद्रीय मंत्री रक्षा खडसे यांच्या मुलीची छेड, शिंदे सेनेचे आमदार चंद्रकांत पाटील यांनी मौन सोडले,...</t>
+          <t>चंद्रकांत पाटलांना हवंय देवेंद्र फडणवीसांचं पद? थेट म्हणाले, सर्व मंत्रिपदं भूषवली आता फक्त…</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-said-i-am-senior-minister-only-home-minister-department-is-remain-1389806.html</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>मग युती कधी? उद्धव ठाकरेंसमोर मिलिंद नार्वेकरांची गुगली, मी सुद्धा या सुवर्णक्षणाची</t>
+          <t>Chandrakant patil: एकनाथ शिंदेकडे 75 नगरसेवक गेलेत, आता मुंबई महापालिकेसाठी राज ठाकरे राजकीय</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
+          <t>https://marathi.abplive.com/news/chandrakant-patil-criticizes-on-uddhav-thackeray-said-raj-thackeray-is-political-convenience-for-mumbai-municipal-corporation-maharashtra-politics-marathi-news-1368293</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>आंदोलनाचा प्रत्येकाला अधिकार, मात्र मार्ग सनदशीर नसल्यास कारवाई; चंद्रकांत पाटील यांचा इशारा…</t>
+          <t>शिंदेंच्या शिवसेनेचे आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतले ताब्यात, मुक्ताईनगर बंद</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-warns-against-illegal-protests-ocd-94-5326788/</t>
+          <t>https://www.lokmat.com/jalgaon/shindes-shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-muktai-nagar-closed-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Shiv Sena On Raksha Khadse Daughter | शिवसेना आमदार चंद्रकांत पाटील यांच्या कार्यकर्त्यांकडून छेडछाड? पाटील स्पष्टच बोलले..</t>
+          <t>विशाल पाटील कसे विजयी झाले हे जाहीरपणे सांगू शकत नाही : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-cannot-reveal-how-vishal-patil-won-dc95</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
+          <t>उच्च व तंत्रशिक्षण मंत्र्यांच्या घरातील कपाटांमध्ये…; स्वतः चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
+          <t>https://www.loksatta.com/pune/akshardhara-book-gallery-maruti-chitampally-literature-gallery-inaugurated-chandrakant-patil-pune-print-news-ssb-93-5260696/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>पत्रकारांच्या मुला-मुलींच्या करिअर अन् कुटुंबाच्या आरोग्यासाठी मोठं पाऊल</t>
+          <t>केंद्रीय मंत्री रक्षा खडसे यांच्या मुलीची छेड, शिंदे सेनेचे आमदार चंद्रकांत पाटील यांनी मौन सोडले,...</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
+          <t>https://www.tv9marathi.com/maharashtra/raksha-khadse-daughter-harassed-reaction-of-mla-chandrakant-patil-1359186.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
+          <t>मग युती कधी? उद्धव ठाकरेंसमोर मिलिंद नार्वेकरांची गुगली, मी सुद्धा या सुवर्णक्षणाची</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-milind-narvekar-and-chandrakant-patil-meet-at-parag-alavani-daughter-wedding-and-discussion-on-yuti-impact-on-maharashtra-politics-1341419</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
+          <t>आंदोलनाचा प्रत्येकाला अधिकार, मात्र मार्ग सनदशीर नसल्यास कारवाई; चंद्रकांत पाटील यांचा इशारा…</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-warns-against-illegal-protests-ocd-94-5326788/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
+          <t>Principal Retirement Age in Maharashtra: प्राचार्यांच्या निवृत्ती वयात वाढ; मंत्री चंद्रकांत पाटील यांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/amravati/amravati-40th-principal-association-state-conference-retirement-age-extension-chandrakant-patil-announcement-as80</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
+          <t>Chandrakant Patil Shiv Sena On Raksha Khadse Daughter | शिवसेना आमदार चंद्रकांत पाटील यांच्या कार्यकर्त्यांकडून छेडछाड? पाटील स्पष्टच बोलले..</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
+          <t>https://marathi.abplive.com/videos/news/jalgaon-chandrakant-patil-shiv-sena-on-raksha-khadse-daughter-devendra-fadanvis-marathi-news-abp-majha-1347066</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
+          <t>पत्रकारांच्या मुला-मुलींच्या करिअर अन् कुटुंबाच्या आरोग्यासाठी मोठं पाऊल</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
+          <t>https://marathi.abplive.com/news/minister-chandrakant-patil-suggestion-after-pratibimb-foundation-take-a-big-step-for-the-career-of-journalists-sons-and-daughters-along-with-health-of-their-families-maharashtra-marathi-news-1355102</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>खासदार विशाल पाटलांना भाजपकडून ऑफर, चंद्रकांत पाटील म्हणाले, "एक चांगला माणूस यावा, यासाठी..."</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/chandrakant-patil-has-offered-sangli-congress-mp-vishal-patil-to-join-the-bjp-a-a571/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>शिक्षक गिरीश फोंडे यांचे निलंबन रद्द करणार, मंत्री चंद्रकांत पाटील यांच्याकडून आश्वासन</t>
+          <t>चंद्रकांत पाटील यांची घोषणा ! लवकरच 'या' महाविद्यालयातील विद्यार्थिनींसाठी सुरु होणार एक लाख रुपयांची विशेष शिष्यवृत्ती</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/teacher-girish-fondes-suspension-will-be-revoked-assurance-from-minister-chandrakant-patil-a-a746/</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-announced-special-scholarship-for-female-students-of-sydenham-college-963588.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil : जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही, चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-statement-on-jayant-patil-ncp-sharad-pawar-leader-sangli-politics-marathi-news-1371392</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं</t>
+          <t>खासदार विशाल पाटलांना भाजपकडून ऑफर, चंद्रकांत पाटील म्हणाले, "एक चांगला माणूस यावा, यासाठी..."</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-uday-samant-on-manoj-jarange-patil-over-mumbai-morcha-for-maratha-reservation-marathi-news-1379258</t>
+          <t>https://www.lokmat.com/sangli/chandrakant-patil-has-offered-sangli-congress-mp-vishal-patil-to-join-the-bjp-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
+          <t>शेतीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/artificial-intelligence-technology-useful-for-agriculture-says-chandrakant-patil-ssb-93-5328187/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
+          <t>शिक्षक गिरीश फोंडे यांचे निलंबन रद्द करणार, मंत्री चंद्रकांत पाटील यांच्याकडून आश्वासन</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
+          <t>https://www.lokmat.com/sangli/teacher-girish-fondes-suspension-will-be-revoked-assurance-from-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
+          <t>जयश्री पाटील भाजपमध्ये, बुधवारी प्रवेश, पक्षात मानसन्मान : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
+          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-statement-on-jayashree-patil-to-joining-bjp-zws-70-5163284/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
+          <t>गुहागर येथील खरे-ढेरे महाविद्यालयात प्रमाणपत्राचा गैरव्यवहार, मंत्री चंद्रकांत पाटील यांचे कारवाईचे आदेश</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176328/</t>
+          <t>https://www.lokmat.com/ratnagiri/certificate-fraud-at-khare-dhere-college-in-guhagar-minister-chandrakant-patil-orders-action-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173280/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ चंद्रकांत पाटील</t>
+          <t>BJP Kolhapur: विधानसभा जिंकल्यानंतर भाजपची 'शत-प्रतिशत'ची तयारी महापालिका, जिल्हा परिषद</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-have-137-mlas-black-magic-will-do-nothing-maharashtra-government-will-run-for-5-years-says-chandrakant-patil-at-kolhapur-1344696</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांनी घेतला संभाव्य पूरस्थितीचा आढावा</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
+          <t>https://mahasamvad.in/176328/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil | कृषी उत्पादन वाढीसाठी एआय तंत्रज्ञान उपयुक्त : पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
+          <t>https://pudhari.news/maharashtra/sangali/ai-technology-useful-for-agriculture-growth-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
+          <t>राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार – उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
+          <t>https://mahasamvad.in/173280/</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील सांगलीचे पालकमंत्री</t>
+          <t>सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-guardian-minister-of-sangli</t>
+          <t>https://marathi.abplive.com/news/maharashtra/extension-of-the-deadline-for-admission-registration-conducted-by-cet-cell-information-from-minister-chandrakant-patil-1368834</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>मी राज्यातील सिनिअर मंत्री, ‘गृहमंत्री’पद फक्त राहिलंय - चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176819/</t>
+          <t>https://www.lokmat.com/sangli/i-am-a-senior-minister-in-the-state-the-post-of-home-minister-remains-says-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>उद्धव ठाकरे यांचे पुन्हा भाजपाशी मनोमिलन?, पराग अळवणी यांच्या मुलीच्या लग्नात चंद्रकांत पाटील यांची...</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176831/</t>
+          <t>https://www.tv9marathi.com/maharashtra/uddhav-thackerays-alliance-with-bjp-chandrakant-patil-and-thackeray-meet-at-wedding-ceremony-1341596.html</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
+          <t>पूरबाधितांच्या नुकसानीचे पंचनामे तातडीने करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176833/</t>
+          <t>https://mahasamvad.in/176819/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
+          <t>Chandrakant Patil | मराठ्यांना कुणबीतून सरसकट ओबीसी आरक्षण टिकत नाही : ना. चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-says-maratha-quota-cannot-survive-through-kunbi-obc-route-sk95</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>पूरपश्चात व्यवस्थापन तातडीने करावे – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169332/</t>
+          <t>https://mahasamvad.in/176831/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
+          <t>34 एकर जमिनीची 100 एकर कशी झाली? चंद्रकांत पाटलांचा एकनाथ खडसेंवर खळबळजनक आरोप नाथाभाऊंचा</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
+          <t>https://marathi.abplive.com/news/politics/eknath-khadse-vs-chandrakant-patil-how-did-34-acres-of-land-become-100-acres-eknath-khadse-response-to-chandrakant-patil-allegations-jalgaon-maharashtra-politics-marathi-news-1362993</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
+          <t>“काँग्रेसयुक्त भाजप कधी झाली, हे त्यांनाच कळले नाही”, चंद्रकांत पाटलांच्या ‘त्या’ विधानावर हर्षवर्धन सपकाळांचा टोला</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-made-the-statement-while-on-a-visit-to-pune-pune-print-news-svk-88-phm-00-5295740/</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
+          <t>जिल्ह्याच्या चौफेर विकासासाठी सर्व यंत्रणांनी कामे प्रस्तावित करावीत – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172941/</t>
+          <t>https://mahasamvad.in/169332/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
+          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173478/</t>
+          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>जिल्हा नियोजनची कामे मुदतीत न करणाऱ्या ठेकेदारांवर कारवाई, पालकमंत्री चंद्रकांत पाटील यांचा इशारा</t>
+          <t>Ganeshotsav Budget: गणेशोत्सवासाठी 600 कोटींची तरतूद; उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे मत</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/action-will-be-taken-against-contractors-who-do-not-complete-district-planning-works-within-the-deadline-guardian-minister-chandrakant-patil-warns-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/pune/600-crore-ganeshotsav-budget-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
+          <t>पद्मभूषण डॉ. वसंतदादा पाटील स्मारकाची पालकमंत्री चंद्रकांत पाटील यांनी केली पाहणी</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
+          <t>https://mahasamvad.in/172941/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>जिल्हा नियोजनसाठी ६३२ कोटींचा निधी मंजूर, सांगलीचे पालकमंत्री चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>Sanjay Raut : शिवसेना-भाजपा युतीच्या चर्चांवर संजय राऊतांची रोखठोक भूमिका, चंद्रकांत पाटलांचा उल्लेख करत म्हणाले…</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/fund-of-rs-632-crores-approved-for-district-planning-sangli-guardian-minister-chandrakant-patil-gave-information-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-reaction-on-chandrakant-patil-statement-of-shivsena-bjp-alliance-will-be-golden-moment-sgk-96-4858543/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार?</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174837/</t>
+          <t>https://marathi.abplive.com/news/sangli/will-ajit-pawar-chandrakant-patil-jayant-patil-rohit-pawar-come-on-the-same-platform-in-sangli-for-saroj-patil-function-1377194</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>राज्यात दोन हजार नवीन ग्रंथालये : उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>आता प्राचार्यांची सेवानिवृत्ती ६५ व्या वर्षी हाेणार : ना. चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/two-thousand-new-libraries-in-maharashtra-announces-minister-chandrakant-patil-ap84</t>
+          <t>https://www.lokmat.com/amravati/now-principals-will-retire-at-the-age-of-65-announcement-by-n-chandrakant-patil-a-a782-c1000/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
+          <t>प्राचार्यांचे निवृत्ती वय ६५ करण्यासाठी सकारात्मक - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत दादा पाटील</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
+          <t>https://mahasamvad.in/173478/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
+          <t>जयश्री पाटलांच्या प्रवेशावरून भाजप-विशाल पाटील वाद शिगेला! थेट पलटवार अन् चंद्रकांत पाटलांचा टोला</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163743/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-responds-to-vishal-patils-allegation-on-bjp-breaking-their-political-family-after-jayashree-patils-entry-as11</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
+          <t>क्रांतिसिंह नाना पाटील, क्रांतिअग्रणी डॉ. जी. डी. बापू लाड यांना पालकमंत्री चंद्रकांत पाटील यांनी केले अभिवादन</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
+          <t>https://mahasamvad.in/174837/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>चंद्रकांत पाटलांचा रोख कोणाकडे ?</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175756/</t>
+          <t>https://www.loksatta.com/politics/guardian-minister-chandrakant-patil-invites-sangli-independent-mp-vishal-patil-to-join-bjp-print-politics-news-zws-70-4956371/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
+          <t>ग्रंथालयांच्या अडचणी सोडण्यासाठी शासन प्रयत्नशील – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
+          <t>https://mahasamvad.in/163743/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
+          <t>निवडणुका महायुती म्हणूनच; महापौर भाजपचा – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
+          <t>https://www.loksatta.com/kolhapur/chandrakant-patil-outlines-mahayutis-new-election-formula-in-kolhapur-bjp-meet-vsd-99-5289375/</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
+          <t>जिल्ह्याचा शाश्वत विकास साधण्यासाठी कटिबद्ध – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
+          <t>https://mahasamvad.in/175756/</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>हात जोडतो, नसते वाद काढू नका!वाघ्या कुत्र्याच्या समाधीवरून चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>राज्यात दोन हजार नवीन ग्रंथालये : उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-chandrakant-patil-appeal-over-tomb-of-tiger-dog-controversy-zws-70-4983085/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/two-thousand-new-libraries-in-maharashtra-announces-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
+          <t>Chandrakant Patil Statement : शिंदेंची दादांविरोधात शहांकडे तक्रार? चंद्रकांत पाटील म्हणतात, खळखळ व्यक्त केली नाही तर...</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-on-eknath-shinde-complains-to-amit-shah-against-ajit-pawar-patil-breaks-silence-rm96-sm89</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
+          <t>शासकीय खरेदीतील गैरकारभार खपवून घेणार नाही, पालकमंत्री चंद्रकांत पाटील यांनी अधिकाऱ्यांना सुनावले</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176171/</t>
+          <t>https://www.lokmat.com/sangli/will-not-tolerate-malpractices-in-government-procurement-guardian-minister-chandrakant-patil-tells-officials-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>खानापूरला शिवाजी विद्यापीठाचे उपकेंद्र; चंद्रकांत पाटील यांची घोषणा</t>
+          <t>Mahayuti Guardian Minister : चंद्रकांत पाटलांना सांगलीला आणलं, तर मुश्रीफांना थेट विदर्भात धाडलं; आबिटकरांना शिंदेंचं मोठं गिफ्ट</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/shivaji-university-s-sub-centre-in-khanapur-says-chandrakant-patil-zws-70-4960985/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-sangli-hasan-mushrif-washim-prakash-abitkar-kolhapur-guardian-ministers-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>“उद्धव ठाकरेंच्या शिवसेनेला सत्तेत यायचं आहे पण…”, चंद्रकांत पाटील यांचा दावा काय?</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173059/</t>
+          <t>https://www.loksatta.com/maharashtra/uddhav-thackeray-shivsena-wants-to-join-mahayuti-but-what-chandrkant-patil-said-scj-81-5018355/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
+          <t>इंजिनियरिंगसाठी 28 जूनपासून प्रवेश, डिप्लोमासाठी 30 जूनपर्यंत मुदतवाढ मंत्री</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
+          <t>https://marathi.abplive.com/education/college-admission-for-engineers-from-june-28-extension-for-diploma-till-june-30-minister-chandrakant-patil-decision-1366417</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
+          <t>शासकीय व्यसनमुक्ती व पुनर्वसन केंद्राचे पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते लोकार्पण</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
+          <t>https://mahasamvad.in/176833/</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>जिल्हा नियोजनची कामे मुदतीत न करणाऱ्या ठेकेदारांवर कारवाई, पालकमंत्री चंद्रकांत पाटील यांचा इशारा</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176754/</t>
+          <t>https://www.lokmat.com/sangli/action-will-be-taken-against-contractors-who-do-not-complete-district-planning-works-within-the-deadline-guardian-minister-chandrakant-patil-warns-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
+          <t>जिल्हा नियोजनसाठी ६३२ कोटींचा निधी मंजूर, सांगलीचे पालकमंत्री चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
+          <t>https://www.lokmat.com/sangli/fund-of-rs-632-crores-approved-for-district-planning-sangli-guardian-minister-chandrakant-patil-gave-information-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
+          <t>देशातील कर्तबगार स्त्रियांचा आदर्श विद्यार्थिनींनी घ्यावा – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
+          <t>https://mahasamvad.in/176171/</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>पुणे पोलीस दलात लवकरच एक हजार पोलीस कर्मचारी; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163261/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-says-there-will-soon-be-1000-police-personnel-in-the-pune-police-force-pune-print-news-amy-95-5209449/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
+          <t>भाजपला अजूनसुद्धा दुसऱ्याचीच पोरं का आवडतात? राजू शेट्टींची चंद्रकांत पाटलांवर</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
+          <t>https://marathi.abplive.com/news/politics/why-does-bjp-still-like-other-people-children-raju-shetti-scathing-criticism-of-chandrakant-patil-offer-to-vishal-patil-1349730</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
+          <t>खानापूरला शिवाजी विद्यापीठाचे उपकेंद्र; चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
+          <t>https://www.loksatta.com/maharashtra/shivaji-university-s-sub-centre-in-khanapur-says-chandrakant-patil-zws-70-4960985/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>मंत्री चंद्रकांत पाटील यांची ‘दिलखुलास’ मध्ये २४ ते २६ तर ‘जय महाराष्ट्र’मध्ये २५ मार्चला मुलाखत</t>
+          <t>भावी पिढी वाचण्यासाठी बालवयातच नशामुक्तीचा संस्कार आवश्यक – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160007/</t>
+          <t>https://mahasamvad.in/176754/</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सांगली जिल्ह्याचा विकासदर वाढवण्याचे उद्दिष्ट – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/169326/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-district-developmet-plan-announced-by-guardian-minister-chandrakant-patil-rds-00-5309586/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
+          <t>Chandrakant Patil: चंद्रकांत पाटील ॲक्शन मोडमध्ये; 'या' कार्यालयात दिली अचानक भेट, प्रकरणे निकाली काढण्याचे निर्देश</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
+          <t>https://www.navarashtra.com/latest-news/chandrakant-patil-instructions-to-no-case-should-remain-pending-higher-and-technical-education-department-marathi-news-775394.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
+          <t>Pune News: 'सगळ्यांचा रेकॉर्ड माहितेय, उद्याच यादी जाहीर.., 'हिंदी'वादावरुन चंद्रकांत पाटलांचा थेट इशारा</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
+          <t>https://marathi.ndtv.com/maharashtra/pune-news-chandrakant-patil-slams-raj-thackeray-uddhav-thackeray-on-hindi-language-controvery-8785417</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>क्वांटम संगणन उपक्रमाच्या माध्यमातून प्राध्यापकांना प्रशिक्षण – मंत्री चंद्रकांत पाटील</t>
+          <t>Shaktipeeth Expressway |'शक्तिपीठ' महामार्गाविरोधात शेतकरी आक्रमक, चंद्रकांत पाटील यांचा ताफा अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/169422/</t>
+          <t>https://pudhari.news/maharashtra/sangali/shaktipeeth-expressway-farmer-protest-chandrakant-patil-convoy-blocked-ss88</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
+          <t>मंत्री चंद्रकांत पाटील यांची ‘दिलखुलास’ मध्ये २४ ते २६ तर ‘जय महाराष्ट्र’मध्ये २५ मार्चला मुलाखत</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
+          <t>https://mahasamvad.in/160007/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
+          <t>उच्च व तंत्र शिक्षण विभागाच्या ‘डॅशबोर्ड’चे मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175217/</t>
+          <t>https://mahasamvad.in/163261/</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>अमली पदार्थ तस्करांवर कायद्याचा धाक यापुढेही कायम ठेवा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161166/</t>
+          <t>https://mahasamvad.in/169326/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
+          <t>Sangli Guardian Minister : सांगली जिल्ह्याचे पुन्‍हा चंद्रकांत पाटील पालक</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/sangli-district-welcomes-reappointment-of-chandrakant-patil-as-guardian-minister-sdj87</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
+          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यासाठी शासन सकारात्मक – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
+          <t>https://mahasamvad.in/175217/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील म्हणतात, भारतीय जनता पार्टीच्या नेत्यांनी धंगेकरांना घेण्याचा निर्णय केला असता तर…</t>
+          <t>सर्वसामान्य नागरिकांसाठी दर्जेदार आरोग्य सुविधा देण्यासाठी शासन कटिबद्ध - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-after-ravindra-dhangekar-entry-into-shinde-group-svk-88-amy-95-4945089/</t>
+          <t>https://mahasamvad.in/173059/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
+          <t>Chandrakant Patil| 'मागच्या नेत्यांनी फक्त आपल्या तालुक्यापुरताच विकास केला'</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-criticizes-former-congress-ncp-leaders-in-khanapur-dc95</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
+          <t>Chandrakant Patil : चंद्रकांत पाटील संतापले; म्हणाले, 'हे खपवून घेणार नाही, राजकीय दबावाला बळी पडू नका'</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-angry-political-pressure-statement-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>पुण्यात वारकऱ्यांसाठी ‘फिरता दवाखाना’; मंत्री चंद्रकांत पाटील यांच्या हस्ते उद्घाटन</t>
+          <t>जयंत पाटलांच्या डोक्यातील त्यांच्या चेहऱ्यावरही दिसणार नाही; चंद्रकांत पाटील यांची कोटी</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/in-pune-chandrakant-patil-inaugurated-free-medical-aid-through-mobile-clinic-for-warkaris-pune-print-news-tss-19-asj-82-5169425/</t>
+          <t>https://www.loksatta.com/maharashtra/guardian-minister-chandrakant-patil-reacted-to-jayant-patil-while-interacting-with-the-media-phm-00-5244552/</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
+          <t>विद्यार्थ्यांना रोजगाराभिमुख शिक्षण आणि प्रशिक्षणाच्या संधी उपलब्ध - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
+          <t>https://mahasamvad.in/161166/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>राज्यातील विद्यार्थ्यांसाठी असलेल्या महाविद्यालयीन योजनांची जबाबदारी प्राध्यापकांवर - मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174729/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/minister-chandrakant-patil-new-responsibility-of-professors-for-students-instructions-for-effective-implementation-of-college-schemes/articleshow/121717827.cms</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
+          <t>Chandrakant Patil Dhananjay Mahadik : भाजपमधील संघर्षाचा वणवा स्थानिकला पेटणार? वर्चस्व ठेवण्यासाठी मंत्री पाटील-महाडिकांच्यात ईर्षा</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/silent-clash-between-chandrakant-patil-and-dhananjay-mahadik-ahead-of-local-body-elections-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
+          <t>संजय राऊतांना प्रत्येक गोष्टीत पिवळे दिसते, लवकरच औषध मिळेल, मंत्री चंद्रकांत पाटील यांचा मिश्कील टोला</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
+          <t>https://www.lokmat.com/maharashtra/sanjay-raut-sees-yellow-in-everything-will-get-medicine-soon-minister-chandrakant-patil-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
+          <t>Jalgaon Politics | शेतकऱ्यांचे आंदोलन चिघळले : आमदार चंद्रकांत पाटील पोलिसांच्या ताब्यात !</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/jalgaon/jalgaon-politics-farmers-protest-escalates-mla-chandrakant-patil-in-police-custody-ar84</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil: पुणे पोलिस दलात लवकरच एक हजार जणांना घेणार; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
+          <t>https://www.esakal.com/pune/1000-new-recruits-to-join-pune-police-soon-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Vaibhav Patil joins BJP | वैभव पाटील यांच्या प्रवेशामुळे भाजप आणखी बळकट : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160626/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ncp-leader-vaibhav-patil-joins-bjp-chandrakant-patil-says-party-strengthened-as80</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
+          <t>EPS Employees Pension | ईपीएस कर्मचाऱ्यांना निवृत्तीवेतन मिळण्यासाठी पाठपुरावा करू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/chandrakant-patil-pledges-pursuit-for-eps-employees-pension-rights-as80</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>राष्ट्रवादीचे अस्तित्व केवळ पवार कुटुंबापुरतेच मर्यादित, मंत्री चंद्रकांत पाटील यांचे टीकास्त्र</t>
+          <t>Art Diploma Admission: कला पदविका अभ्यासक्रमाला प्रवेश घेण्याची संधी: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/ncp-existence-is-limited-to-the-pawar-family-only-minister-chandrakant-patils-criticism-a-a746/</t>
+          <t>https://pudhari.news/maharashtra/pune/chandrakant-patil-on-art-diploma-admission-sb97</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
+          <t>राष्ट्रवादीचे अस्तित्व केवळ पवार कुटुंबापुरतेच मर्यादित, मंत्री चंद्रकांत पाटील यांचे टीकास्त्र</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
+          <t>https://www.lokmat.com/sangli/ncp-existence-is-limited-to-the-pawar-family-only-minister-chandrakant-patils-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
+          <t>अहिल्यादेवी होळकरांचे कार्य प्रेरणादायी – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
+          <t>https://www.loksatta.com/maharashtra/ahilyadevi-holkar-jayanti-2025-bjp-chandrakant-patil-in-solapur-css-98-5126268/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
+          <t>Dhananjay Munde Resignation: ...तर देवेंद्र फडणवीस धनंजय मुंडेंना राजीनामा द्यायला लावतील चंद्रकांत</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-chandrkant-patil-on-dhananjay-munde-resignation-and-walmik-karad-connection-on-beed-massajog-santosh-deshmukh-case-1340832</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
+          <t>Chandrakant Patil : भाजपचं महायुतीत मोठा भाऊ ? शासकीय कमिट्यांवर 50 टक्के नियुक्त्या; चंद्रकांत पाटलांचे कार्यकर्यांना आदेश</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/guardian-minister-chandrakant-patil-announces-opportunities-for-party-workers-in-district-and-taluka-committees-in-sangli-district-as11</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
+          <t>Chandrakant Patil: लवकरच प्राचार्यांच्या निवृत्तीचे वय बदलणार; चंद्रकांतदादांचा महत्त्वपूर्ण निर्णय</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-principals-retirement-age-65-for-college-principals-chandrakant-patil-announcement-mm76</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
+          <t>Chandrakant Patil : व्हिजन ठेवल्यास समाजाचा सर्वांगीण विकास, मंत्री चंद्रकांत पाटील यांचा सल्ला; ‘सकाळ प्लस स्टडीरूम’च्या ई-पेपरचे प्रकाशन</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-sakal-plus-study-room-e-paper-launched-with-focus-on-student-guidance-amp17</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>Chandrakant Patil : ‘मी सिनिअर मंत्री आता फक्त…’, चंद्रकांत पाटलांचं लक्ष...</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173128/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-leader-minister-chandrakant-patil-big-statement-regarding-ministerial-post-at-sangli-1390006.html</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, पालकमंत्र्यांची गाडी अडवण्याचा प्रयत्न</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/minister-chandrakant-patil-and-farmers-dispute-broke-out-between-in-sangli/articleshow/120792863.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>छत्रपती संभाजी महाराज स्मृतीस्थळ विकासाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>मुक्ताईनगरमध्ये आंदोलन तीव्र; शिंदे गटाचे आमदार चंद्रकांत पाटील, शेतकरी पोलिसांच्या ताब्यात</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173013/</t>
+          <t>https://www.lokmat.com/jalgaon/protests-intensify-in-muktainagar-shinde-group-mla-chandrakant-patil-and-farmers-in-police-custody-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
+          <t>डीपीसीतील पायाभूत सुविधांच्या कामांसाठी यापुढे ऑनलाईन युनिक आयडी क्रमांक - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
+          <t>https://mahasamvad.in/174729/</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
+          <t>‘राजकारण्यांसमोर वाकू नका…’ चंद्रकांत पाटील यांनी कोणाला दिला सल्ला?</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
+          <t>https://www.loksatta.com/pune/do-not-bow-to-politicians-says-education-minister-urges-teachers-to-uphold-dignity-of-profession-pune-print-news-ccp-14-ocd-94-5253062/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
+          <t>माजी विधानपरिषद सभापती दिवंगत शिवाजीराव देशमुख यांच्या स्मारकाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
+          <t>https://mahasamvad.in/173128/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Free education: मुलींना मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा, मंत्र्यांनी दिले थेट आदेश</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/172372/</t>
+          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
+          <t>छत्रपती संभाजी महाराज स्मृतीस्थळ विकासाचा पालकमंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/164366/</t>
+          <t>https://mahasamvad.in/173013/</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
+          <t>जिल्हा क्रीडा संकुलात अद्ययावत सुविधांसाठी आराखडा तयार करा – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
+          <t>https://mahasamvad.in/160626/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
+          <t>Pune News : समाजाचा आत्‍मविश्‍वास वाढविण्याची गरज, चंद्रकांत पाटील यांचे आवाहन; गुरुपौर्णिमेनिमित्त विविध क्षेत्रांतील नामवंतांचा सत्कार</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
+          <t>https://www.esakal.com/pune/indias-ancient-brilliance-first-surgery-dictionary-stadium-were-ours-chandrakant-patil-amp17</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
+          <t>कोल्हापूर महापालिका निवडणुकीसाठी चंद्रकांत पाटील यांच्या गाठीभेटी</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/170382/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-holds-key-meetings-ahead-of-kolhapur-municipal-corporation-elections-ocd-94-5188525/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटलांकडून अपक्ष खासदाराला खुली ऑफर: म्हणाले - विशाल पाटील सोबत आल्यास सांगलीच्या विकासाला गती मि...</t>
+          <t>Sangli News: अजित पवार-चंद्रकांत पाटील-जयंत पाटील-रोहित पवार एकाच व्यासपीठावर येणार? शरद पवारांच्या भगिनी माई कारण ठरणार!</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-134651805.html</t>
+          <t>https://www.msn.com/mr-in/news/other/sangli-news-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%9C%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%B0-%E0%A4%B9-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%8F%E0%A4%95-%E0%A4%9A-%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%AA-%E0%A4%A0-%E0%A4%B5%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A3-%E0%A4%B0-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%97-%E0%A4%A8-%E0%A4%AE-%E0%A4%88-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0/ar-AA1KyMam</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
+          <t>Chandrakant Patil : राज्याला पुढे नेणारे निर्णय; उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
+          <t>https://www.esakal.com/pune/chandrakant-patil-monsoon-session-highlights-major-reforms-but-security-concerns-raised-amp17</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
+          <t>पालकमंत्री चंद्रकांत पाटील यांच्या हस्ते मुख्यमंत्री सहाय्यता निधी कक्षाचे उद्घाटन</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
+          <t>https://mahasamvad.in/164366/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
+          <t>Jayashree Patil : जयश्रीताईंचा निर्णय झाला, चंद्रकांत पाटलांनी सूत्रं हलवली अन् फडणवीसांनी शब्दही दिला; आता बुधवारी भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ex-cm-of-maharashtra-vasantdada-patils-granddaughter-in-law-jayshree-patil-to-join-bjp-in-presence-of-devendra-fadnavis-as11</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>अमली पदार्थ विरोधी टास्क फोर्सने कायद्याचा धाक निर्माण करावा – चंद्रकांत पाटील</t>
+          <t>रोहिणी खडसेंनी दोन ठिकाणी मतदान केलं, त्या फत्त ट्विटरवरच टिव टिव करतात, चंद्रकांत</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-says-anti-drug-task-force-should-create-fear-of-law-mrj-95-4882600/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-on-rohini-khadse-jalgaon-news-mla-chandrakant-patil-criticizes-rohini-khadse-1379392</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
+          <t>चंद्रकांत पाटील यांच्याकडून त्रुटींची कबुली… विषयतज्ज्ञांना कारणे दाखवा नोटिस</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-admits-errorsin-mht-cet-math-paper-takes-disciplinary-action-pune-print-news-ccp-14-rds-00-5198879/</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>चंद्रकांत पाटलांकडून अपक्ष खासदाराला खुली ऑफर: म्हणाले - विशाल पाटील सोबत आल्यास सांगलीच्या विकासाला गती मि...</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-134651805.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Sangli Politics : पालकमंत्री चंद्रकांत पाटील यांनी सांगली जिल्हा नियोजन समितीची यादी केली फायनल, कोणाची लागणारवर्णी?</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176760/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-has-finalized-list-of-sangli-district-planning-committee-members-whose-name-will-be-required-srs92</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>मुंबईकडे कूच नको, कागद-पेन घ्या अन् चर्चेला या: शांततेने मागण्या मांडल्या तर सरकार ऐकेल, चंद्रकांत पाटलांचा...</t>
+          <t>हिंदी सक्तीवरून चंद्रकांत पाटलांचा राज ठाकरेंना सल्ला, म्हणाले, मुख्यमंत्र्यांसोबत…</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/manoj-jarange-protest-warning-chandrakant-patil-135741950.html</t>
+          <t>https://www.tv9marathi.com/politics/chandrakant-patil-suggest-raj-thackeray-that-seat-with-devendra-fadnavis-to-understand-hindi-language-education-policy-1429296.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
+          <t>अमली पदार्थ विरोधी टास्क फोर्सने कायद्याचा धाक निर्माण करावा – चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-says-anti-drug-task-force-should-create-fear-of-law-mrj-95-4882600/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
+          <t>Jayshree Patil | जयश्री पाटील भाजपच्या वाटेवर?; चंद्रकांत पाटील आज भेटणार</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
+          <t>https://pudhari.news/maharashtra/sangali/is-jayshree-patil-joining-bjp-chandrakant-patil-to-meet-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>आम्ही काही सोन्याचा चमचा घेऊन जन्माला आलोय असं नाही… अजित पवार यांचा चंद्रकांतदादांना टोला</t>
+          <t>मुंबईकडे कूच नको, कागद-पेन घ्या अन् चर्चेला या: शांततेने मागण्या मांडल्या तर सरकार ऐकेल, चंद्रकांत पाटलांचा...</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ajit-pawars-attack-on-chandrakant-patil-in-islampur-1471041.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/manoj-jarange-protest-warning-chandrakant-patil-135741950.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
+          <t>विद्यार्थी सहाय्य जनजागृती अभियानातून युवकांच्या जीवनाला सकारात्मक दिशा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
+          <t>https://mahasamvad.in/172372/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jayshree Patil : जयश्री पाटलांना भाजपचे रिटर्न गिफ्ट! प्रवेशाच्या आधीच चंद्रकांत पाटलांची मोठी घोषणा</t>
+          <t>सर जे. जे. स्कूल ऑफ आर्ट महाविद्यालयाला उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची भेट</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jayshree-patil-joins-bjp-and-appointed-to-sangli-district-planning-committee-by-chandrakant-patil-as11</t>
+          <t>https://mahasamvad.in/170382/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
+          <t>Teacher Recruitment : अध्यापकांच्या भरती प्रकियेस मान्यता; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
+          <t>https://www.navarashtra.com/politics/minister-chandrakant-patil-informs-that-recruitment-for-teaching-posts-will-be-done-799732.html</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
+          <t>शेती उत्पादनात वाढ व शेतमाल निर्यातीसाठी कृत्रिम बुद्धिमत्ता तंत्रज्ञान उपयुक्त - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
+          <t>https://mahasamvad.in/176760/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
+          <t>Pune Car Accident : सदाशिव पेठेतील दुर्घटनेतील जखमींची चंद्रकांत पाटील यांनी केली विचारपूस</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
+          <t>https://www.lokmat.com/pune/pune-car-accident-chandrakant-patil-questioned-the-injured-in-the-sadashiv-peth-accident-a-a955-c1008/</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
+          <t>Chandrakant Patil : ‘माणगंगा’प्रश्नी लवकरच सकारात्मक निर्णय</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
+          <t>https://pudhari.news/maharashtra/sangali/manganga-river-issue-chandrakant-patil-statement-dc95</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
+          <t>“मुक्ताईनगर छेडछाड प्रकरणातील संशयित शिंदे गटाचे”, आमदार चंद्रकांत पाटील यांचीही पुष्टी</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
+          <t>https://www.loksatta.com/nashik/muktainagar-eknath-shinde-shivsena-mla-chandrakant-patil-confirms-suspected-belongs-to-shivsena-raksha-khadse-daughter-molestation-case-css-98-4926740/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
+          <t>तासिकातत्वावर प्राध्यापकांचे मानधन वेळेवर देण्यासाठी पोर्टल विकसित करा - उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
+          <t>https://mahasamvad.in/168333/</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Jayshree Patil : जयश्री पाटलांना भाजपचे रिटर्न गिफ्ट! प्रवेशाच्या आधीच चंद्रकांत पाटलांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162964/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jayshree-patil-joins-bjp-and-appointed-to-sangli-district-planning-committee-by-chandrakant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>BJP News: काँग्रेस खासदाराला भाजप मंत्र्यांची खुली ऑफर, खासदाराने एका वाक्यात विषय संपवला</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/161614/</t>
+          <t>https://marathi.ndtv.com/politics/minister-and-bjp-leader-chandrakant-patil-offered-sangli-mp-vishal-patil-to-join-bjp-7935097</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
+          <t>“राज ठाकरे यांना जवळ करणे राजकीय सोय, ठाकरे गटाचे ७५ नगरसेवक शिंदेंकडे गेले”: चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-chandrakant-patil-said-this-is-political-convenience-that-raj-thackeray-and-uddhav-thackeray-closer-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>नवनियुक्त आयुक्तांची भेट घेत चंद्रकांत पाटलांनी वाचला पुण्यातील अडचणींचा पाढा</t>
+          <t>Chandrakant Patil : ‘शक्तिपीठ’विरोधातील शक्ती तपासावी लागेल</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-chandrakant-patil-while-meeting-the-newly-appointed-commissioners-read-out-the-problems-in-pune-a-a1014-c1008/</t>
+          <t>https://pudhari.news/maharashtra/sangali/guardian-minister-chandrakant-patil-warns-on-shaktipith-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
+          <t>आम्ही काही सोन्याचा चमचा घेऊन जन्माला आलोय असं नाही… अजित पवार यांचा चंद्रकांतदादांना टोला</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
+          <t>https://www.tv9marathi.com/maharashtra/ajit-pawars-attack-on-chandrakant-patil-in-islampur-1471041.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
+          <t>अशी दादागिरी चालणार नाही, चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये जोरदार खडाजंगी, बाधित म्हणाले तुम्हाला टाहो फोडून</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-and-farmers-came-face-to-face-over-shaktipith-highway/903727</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>कोल्हापुरातील शिवाजी विद्यापीठाचे उपकेंद्र खानापुरात, मंत्री चंद्रकांत पाटील यांची घोषणा</t>
+          <t>पाणी व्यवस्थापनाद्वारे दीर्घकालीन शाश्वत उपाययोजनांची अंमलबजावणी करावी- पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/shivaji-university-sub-centre-to-be-set-up-in-khanapur-announced-by-minister-chandrakant-patil-a-a746/</t>
+          <t>https://mahasamvad.in/162964/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
+          <t>Carry On Yojana: कॅरी ऑन योजना दुर्दैवी..' चंद्रकांत पाटलांच्या निर्णयाला ABVP चा विरोध</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
+          <t>Chandrakant Patil : शक्तिपीठ महामार्गावरून मंत्री चंद्रकांत पाटील आणि शेतकऱ्यांमध्ये खडाजंगी</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
+          <t>https://agrowon.esakal.com/agro-special/tensions-rise-between-minister-chandrakant-patil-and-farmers-patil-loses-cool</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
+          <t>अभियांत्रिकीच्या प्रवेशाच्या होणार चार प्रवेश फेऱ्या; व्यवस्थापन कोट्यातील जागांसाठीचे नियमही बदलणार</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158873/</t>
+          <t>https://www.loksatta.com/mumbai/engineering-admission-process-revision-four-cap-rounds-says-chandrakant-patil-mumbai-print-news-zws-70-5137735/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Kolhapur : समरजीत घाटगेंची भाजप प्रवेशाची तयारी पूर्ण, चंद्रकांत पाटील लवकरच काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/173469/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/samarjeet-ghatage-set-to-join-bjp-major-blow-to-mva-in-kolhapur-ssy93</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : जन्मभूमीतच दादांचा करिष्मा ओसरला, भाजपचे पदाधिकारी शोधण्याची वेळ</t>
+          <t>नवनियुक्त आयुक्तांची भेट घेत चंद्रकांत पाटलांनी वाचला पुण्यातील अडचणींचा पाढा</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/no-bjp-celebration-for-minister-chandrakant-patil-birthday-this-year-as11-rg93</t>
+          <t>https://www.lokmat.com/pune/pune-news-chandrakant-patil-while-meeting-the-newly-appointed-commissioners-read-out-the-problems-in-pune-a-a1014-c1008/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
+          <t>कोल्हापुरातील शिवाजी विद्यापीठाचे उपकेंद्र खानापुरात, मंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
+          <t>https://www.lokmat.com/sangli/shivaji-university-sub-centre-to-be-set-up-in-khanapur-announced-by-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
+          <t>Chandrakant Patil : तुमच्यासारखा सोन्याचा चमचा घेऊन जन्माला आलो नाही… चंद्रकांतदादांनी रोहित...</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/chandrakant-patil-criticized-rohit-pawar-i-was-not-born-with-a-golden-spoon-like-you-chandrakant-dada-told-rohit-pawar-right-there-1470964.html</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
+          <t>Vishal Patil : विशाल पाटलांचा चंद्रकांतदादांवर पलटवार; ‘आमचं काही व्हायचं ते होऊ दे, आमची तुरुंगात जायचीही तयारी; पण आम्ही काँग्रेस सोडणार नाही’</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-rejects-chandrakant-patils-bjp-entry-offer-vd83</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
+          <t>रोहित पवारांचा खोचक टोला, चंद्रकांतदादांचाही पलटवार; अजित पवारांचं जोरदार प्रत्युत्तर! म्हणाले, 'आम्ही काही...'</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-hits-back-at-rohit-pawar-with-golden-spoon-remark-ajit-pawar-responds-strongly-as11</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>विदर्भ ज्ञान संस्थेला स्वायत्त विद्यापीठ दर्जासाठी सहकार्य करणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://mahasamvad.in/173469/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
+          <t>Chandrakant Patil : सांगलीचा उडता पंजाब? पालकमंत्रीही खवळले ; ठाण मांडून निष्क्रिय बसलेल्या अधिकाऱ्यांना घेतले रडारवर</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-appointed-task-force-in-sangli-district-to-dismantle-drug-factories-as11</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>Pune Police: पुण्याला मिळणार एक हजार नवीन पोलिस; चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-to-get-1000-new-police-sb97</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : झेडपी अध्यक्ष अन् महापालिकेत महापौर भाजपचाच; स्थानिकच्या निवडणुकांसाठी चंद्रकांत पाटलांनी सांगितली व्यूहरचना</t>
+          <t>‘अजितदादा, शरद पवार, सुप्रिया सुळे एवढाच त्यांचा पक्ष…’ , राष्ट्रवादीच्या...</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-local-elections-bjp-mahayuti-strategy-chandrakant-patil-jap93-rg93</t>
+          <t>https://www.tv9marathi.com/maharashtra/ajit-pawar-sharad-pawar-will-come-together-chandrakant-patil-first-reaction-1404550.html</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
+          <t>Chandrakant Patil : जन्मभूमीतच दादांचा करिष्मा ओसरला, भाजपचे पदाधिकारी शोधण्याची वेळ</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/no-bjp-celebration-for-minister-chandrakant-patil-birthday-this-year-as11-rg93</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
+          <t>Modi Solapur Tour : मोदींना सोलापुरात आणण्याची जबाबदारी जयकुमार गोरेंनी सोपवली चंद्रकांत पाटलांवर....</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/jaykumar-gore-entrusted-responsibility-of-bringing-narendra-modi-in-solapur-to-chandrakant-patil-vd83</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
+          <t>Chandrakant Patil Politics: सत्ताधारी आमदारालाच अटक, मुक्ताईनगर कडकडीत बंद, काय आहे कारण?</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/chandrakant-patil-farmers-angry-over-compensation-for-acquired-lands-for-highway-sd67</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
+          <t>Vishal Patil : जयश्रीताईंच्या निर्णयावर विशाल पाटलांची तिखट टीका; चंद्रकांत पाटलांचेही मानले आभार</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-slams-bjp-over-jayshree-patil-bjp-entry-and-says-thanks-to-chandrakant-patil-about-offer-as11</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
+          <t>शिंदे गटाच्या जळगावच्या आमदाराला अटक: इंदूर - हैदराबाद महामार्गाच्या भूसंपादनाला करत होते विरोध; शेतकरी संत...</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/jalgaon/news/jalgaon-chandrakant-patil-arrest-land-acquisition-protest-indore-hyderabad-highway-135504175.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मुंबई तोडण्याची ताकद कोणात नाही, चंद्रकांत पाटलांचा ठाकरेंवर निशाणा</t>
+          <t>शिराळ्यातील संभाजी महाराजांचे स्मृतीस्थळ दर्जेदारपणे करावे – चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
+          <t>https://www.loksatta.com/maharashtra/sambhaji-memorial-project-in-shirala-gets-rs-13-crore-boost-to-be-completed-on-time-says-chandrakant-patil-vsd-99-5250481/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>शेंडा पार्क नव्या रुग्णालयाच्या आवारात दिग्विजय खानविलकरांचा पुतळा उभारू : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157924/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/%E0%A4%B6%E0%A5%87%E0%A4%82%E0%A4%A1%E0%A4%BE-%E0%A4%AA%E0%A4%BE%E0%A4%B0%E0%A5%8D%E0%A4%95-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%B0%E0%A5%81%E0%A4%97%E0%A5%8D%E0%A4%A3%E0%A4%BE%E0%A4%B2%E0%A4%AF%E0%A4%BE%E0%A4%9A%E0%A5%8D%E0%A4%AF%E0%A4%BE-%E0%A4%86%E0%A4%B5%E0%A4%BE%E0%A4%B0%E0%A4%BE%E0%A4%A4-%E0%A4%A6%E0%A4%BF%E0%A4%97%E0%A5%8D%E0%A4%B5%E0%A4%BF%E0%A4%9C%E0%A4%AF-%E0%A4%96%E0%A4%BE%E0%A4%A8%E0%A4%B5%E0%A4%BF%E0%A4%B2%E0%A4%95%E0%A4%B0%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A4%BE-%E0%A4%AA%E0%A5%81%E0%A4%A4%E0%A4%B3%E0%A4%BE-%E0%A4%89%E0%A4%AD%E0%A4%BE%E0%A4%B0%E0%A5%82-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A5%80%E0%A4%B2</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ranjitsinh Mohite Patil : पालकमंत्र्यांची एन्ट्री होताच रणजितसिंह मोहिते पाटलांनी विद्यापीठाच्या कार्यक्रमातून काढता पाय घेतला!</t>
+          <t>जिल्ह्याची ओळख निर्माण करणारे ब्रँड उत्पादन ‘उमेद’ अंतर्गत तयार करा - पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/as-soon-as-guardian-minister-jaykumar-gore-entered-ranjitsinh-mohite-patil-walked-out-of-the-program-vd83</t>
+          <t>https://mahasamvad.in/161614/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यास शासन सकारात्मक; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांचे आश्वासन</t>
+          <t>मराठा आरक्षण : मनोज जरांगे-पाटील यांना सरकारचे चर्चेचे आवाहन</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-library-grant-increase-40-percent-chandrakant-patil-assurance</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-jarange-government-talks</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Agriculture Crisis: कृषी पदवीधरांनी शेतीकडे पाठ फिरविणे चिंतेचे : चंद्रकांत पाटील</t>
+          <t>‘कमवा शिका’ योजनेंतर्गत विद्यार्थिनींना दरमहा २ हजारांचा प्रस्ताव विचाराधीन – मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/concern-over-agriculture-graduates-turning-their-backs-on-farming-chandrakant-patil-rat16</t>
+          <t>https://mahasamvad.in/158873/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
+          <t>Chandrakant Patil : झेडपी अध्यक्ष अन् महापालिकेत महापौर भाजपचाच; स्थानिकच्या निवडणुकांसाठी चंद्रकांत पाटलांनी सांगितली व्यूहरचना</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-local-elections-bjp-mahayuti-strategy-chandrakant-patil-jap93-rg93</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: 'अमित शहांना भेटण्यासाठी आधी लोक माझ्याकडे पाहायचे, पण आता मलाही...'; चंद्रकांतदादांचं मोठं विधान</t>
+          <t>पॉलिटेक्निकच्या प्रवेशाची तारीख जाहीर, ऑनलाईन प्रक्रियेसाठी संकेतस्थळाला</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-says-he-now-needs-to-coordinate-with-murlidhar-mohol-to-reach-amit-shah-dk88-sm89</t>
+          <t>https://marathi.abplive.com/education/polytechnic-admission-start-from-20-may-and-visit-the-website-for-online-process-chandrakant-patil-appeals-1359951</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>सहायक प्राध्यापकांच्या ४४३५ पदांची लवकरच भरती - उच्च आणि तंत्रशिक्षण मंत्री चंद्रकांत पाटील यांची माहिती</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174461/</t>
+          <t>https://deshdoot.com/recruitment-of-4435-posts-of-assistant-professors-soon-information-from-higher-and-technical-education-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>उद्या शंभर एकर जागा देतो, कोल्हापुरातील आयटी पार्क प्रश्नावर मंत्री चंद्रकांत पाटलांचे मोठं वक्तव्य</t>
+          <t>Chandrakant Patil : 'सत्तेचा गैरफायदा घेतला, पण आता आमची सत्ता, न्याय...'; ‘सर्वोदय’वरून दादांनी जयंत पाटलांवर तोफ डागली</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/tomorrow-i-will-give-100-acres-of-land-minister-chandrakant-patil-big-statement-on-the-it-park-issue-in-kolhapur-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-leader-chandrakant-patil-challenges-ncp-sp-jayant-patil-over-sarvodaya-sugar-factory-as11</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>गोगावलेंची पूजा जनतेच्या कल्याणासाठी, अघोरी पूजेच्या आरोपांच्या वादात चंद्रकांत पाटलांची उडी</t>
+          <t>वसंतदादा पाटील यांच्या नातसूनेची भाजपवर मोहोर; एका 'अटी'साठी भाजपची निवड!</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-supports-bharat-gogawale-after-allegations-of-aghori-puja/916805</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/jayashri-patil-joins-bjp-sangli</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
+          <t>Ranjitsinh Mohite Patil : पालकमंत्र्यांची एन्ट्री होताच रणजितसिंह मोहिते पाटलांनी विद्यापीठाच्या कार्यक्रमातून काढता पाय घेतला!</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/as-soon-as-guardian-minister-jaykumar-gore-entered-ranjitsinh-mohite-patil-walked-out-of-the-program-vd83</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
+          <t>Chandrakant Patil : मुंबई तोडण्याची ताकद कोणात नाही, चंद्रकांत पाटलांचा ठाकरेंवर निशाणा</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
+          <t>https://www.tv9marathi.com/videos/chandrakant-patil-slams-uddhav-thackeray-1439709.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
+          <t>अमली पदार्थ विरोधी जनप्रबोधनासाठी गीत स्पर्धा, ५१ हजाराचे बक्षीस – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
+          <t>https://mahasamvad.in/157924/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
+          <t>ग्रंथालयांच्या अनुदानात ४० टक्के वाढ करण्यास शासन सकारात्मक; उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-library-grant-increase-40-percent-chandrakant-patil-assurance</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
+          <t>Agriculture Crisis: कृषी पदवीधरांनी शेतीकडे पाठ फिरविणे चिंतेचे : चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
+          <t>https://agrowon.esakal.com/agro-special/concern-over-agriculture-graduates-turning-their-backs-on-farming-chandrakant-patil-rat16</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
+          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil: 'अमित शहांना भेटण्यासाठी आधी लोक माझ्याकडे पाहायचे, पण आता मलाही...'; चंद्रकांतदादांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175300/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-says-he-now-needs-to-coordinate-with-murlidhar-mohol-to-reach-amit-shah-dk88-sm89</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
+          <t>शरद पवारांना मोठा धक्का? जयंत पाटलांना भाजपात घेण्याचा निर्णय..., बड्या नेत्याचं सूचक विधान</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-says-cm-devendra-fadnavis-will-decide-on-giving-chance-to-jayant-patil-in-bjp-supriya-sule-reacts/918835</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
+          <t>Shaktipeeth Expressway : राज्यात अराजकता निर्माण करण्यासाठी काही शक्तींचे काम सुरू शक्तिपीठ</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
+          <t>https://marathi.abplive.com/news/sangli/chandrakant-patil-on-shaktipeeth-expressway-nagpur-goa-highway-claim-some-forces-working-to-disturb-maharashtra-marathi-1377295</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
+          <t>उद्या शंभर एकर जागा देतो, कोल्हापुरातील आयटी पार्क प्रश्नावर मंत्री चंद्रकांत पाटलांचे मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
+          <t>https://www.lokmat.com/kolhapur/tomorrow-i-will-give-100-acres-of-land-minister-chandrakant-patil-big-statement-on-the-it-park-issue-in-kolhapur-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राज ठाकरे चांगले नेते पण जरा समजून घेतलं पाहिजे आणि… हिंदी सक्तीवरून...</t>
+          <t>Kolhapur Election: शिवसेनेत 'इन्कमिंग' सुसाट, भाजप 'अलर्ट'; कोल्हापूरचा 'चार्ज' महाडिकांऐवजी अनुभवी चंद्रकांतदादांच्या हाती...</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shiv-sena-gaining-ground-bjp-alert-chandrakant-patil-to-lead-kolhapur-civic-politics-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
+          <t>गोगावलेंची पूजा जनतेच्या कल्याणासाठी, अघोरी पूजेच्या आरोपांच्या वादात चंद्रकांत पाटलांची उडी</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/chandrakant-patil-supports-bharat-gogawale-after-allegations-of-aghori-puja/916805</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
+          <t>Rohit Pawar : अजितदादा यॉर्कर टाकतात, जयंतराव गुगली, तर चंद्रकांतदादा सोनं, पण या बेन्टेक्सचं काय...</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
+          <t>https://www.tv9marathi.com/maharashtra/rohit-pawar-praised-chandrakant-patil-and-taunts-gopichand-padalkar-know-what-he-said-1470906.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
+          <t>सांगलीत पूर ओसरला; आता स्थलांतरितांची परतण्याची लगबग, पूरग्रस्त रस्ते, घाट स्वच्छता मोहीम…</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-flood-recedes-chandrakant-patil-leads-inspection-ocd-94-5326644/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
+          <t>Vishal Patil BJP Offer : चंद्रकांतदादांच्या भाजप प्रवेशाच्या गुगलीवर विशाल पाटलांचा सिक्सर; म्हणाले, "मी आता कायद्यानेच..."</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-open-offer-to-independent-mp-vishal-patil-to-join-bjp-sangli-political-news-jap93</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>छत्रपती शिवाजी महाराज यांच्या पुण्यतिथी कार्यक्रम तयारीचा उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
+          <t>Pune News: वाहतूक कोंडी, पाण्याची समस्या ते महिला सुरक्षा.. पुण्यातील नेत्यांचं विचारमंथन; कोण काय म्हणाले?</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160732/</t>
+          <t>https://marathi.ndtv.com/maharashtra/ndtv-marathi-emerging-business-conclave-chandrakant-patil-rupali-chakankar-on-pune-traffic-rain-issue-8786115</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
+          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>डॉ. बाबासाहेब आंबेडकर तंत्रशास्त्र विद्यापीठाच्या उपकेंद्रांच्या धोरणाबाबत सुधारित आराखडा तयार करावा - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/162538/</t>
+          <t>https://mahasamvad.in/174461/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
+          <t>Dhananjay Mahadik : मंत्री चंद्रकांत दादा आणि मुन्ना महाडिक गटात सुप्त संघर्ष, जिल्हाध्यक्ष पदावरून टोकाची ईर्षा</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/latent-conflict-between-minister-chandrakant-patil-and-mp-dhananjay-mahadik-groups-in-bjp-over-election-of-district-president-srs92</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
+          <t>विद्यार्थ्यांना शिष्यवृत्ती मिळणार सोपे, राज्य सरकारचा मोठा निर्णय</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
+          <t>https://marathi.ndtv.com/maharashtra/chandrakant-patil-instructions-to-professors-on-scholarship-implementation-in-colleges-8612913</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
+          <t>अनुदानित महाविद्यालयांमध्ये प्राध्यापक भरती होणार की नाही?; चंद्रकांत पाटील यांनी दिले उत्तर…</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
+          <t>https://www.loksatta.com/pune/will-there-be-recruitment-of-professors-in-aided-colleges-or-not-chandrakant-patil-gave-the-answer-pune-print-news-ccp-14-ssb-93-4945869/</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
+          <t>Chandrakant Patil : राज ठाकरे चांगले नेते पण जरा समजून घेतलं पाहिजे आणि… हिंदी सक्तीवरून...</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
+          <t>https://www.tv9marathi.com/videos/bjp-chandrakant-patil-suggestion-to-mns-raj-thackeray-over-hindi-compulsory-in-maharashtra-school-1429353.html</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Sanjay Raut : “सत्तेसाठी अमित शाह यांचे पाय चाटणार नाही, उद्धव ठाकरे…”, संजय राऊत यांचं चंद्रकांत पाटील यांना उत्तर</t>
+          <t>राज्यातील अध्यापकांच्या भरती प्रकियेस मान्यता, निवड प्रक्रियेसाठी नवीन कार्यपद्धती जाहीर- मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sanjay-raut-strong-answer-to-chandrkant-patil-over-his-statement-over-uddhav-thackeray-also-criticized-amit-shah-scj-81-5018633/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-bharti-new-procedure-announced-for-selection-process-minister-chandrakant-patil/articleshow/118607489.cms</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
+          <t>ग्रंथालय कर्मचाऱ्यांना राज्य कामगार विमा योजनेचा लाभ देण्यासाठी सकारात्मक निर्णय घेणार - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
+          <t>https://mahasamvad.in/175300/</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
+          <t>भाजपमध्ये प्रवेश करण्यापूर्वीच पृथ्वीराज पाटलांच्या पाच मागण्या : फडणवीसांनी चंद्रकांतदादांकडे दिली जबाबदारी</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/congress-city-district-president-prithviraj-patil-joins-bjp-in-presence-of-ravindra-chavan-chandrakant-patil-and-bjp-leaders-as11</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>मराठा आरक्षण उपसमितीच्या अध्यक्षपदी राधाकृष्ण विखे-पाटील</t>
+          <t>राज्यातील विद्यार्थिनींसाठी खुशखबर! 'कमवा आणि शिका' योजनेला होणार शुभारंभ; निधीसाठी पाठपुरावा सुरू</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/radhakrishna-vikhe-patil-appointed-maratha-reservation-subcommittee-chairman</t>
+          <t>https://www.navarashtra.com/career/chandrakant-patil-said-girls-students-of-maharashtra-will-get-benefitted-by-the-scheme-earn-and-learn-964786.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
+          <t>छत्रपती शिवाजी महाराज यांच्या पुण्यतिथी कार्यक्रम तयारीचा उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील यांनी घेतला आढावा</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
+          <t>https://mahasamvad.in/160732/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
+          <t>सावित्रीबाई फुले पुणे विद्यापीठात पुलंच्या नावाने अध्यासन, उच्च आणि तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांची घोषणा</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
+          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-announces-teaching-course-on-p-l-deshpande-at-pune-university-pune-print-news-ocd-94-5146646/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>तिघे वेगवेगळ्या पार्श्वभूमीतील, खडखड होणारच; चंद्रकांत पाटलांनी नाराजीचा चेंडू भिरकावला</t>
+          <t>Vishal Patil: भाजपमध्ये या! चंद्रकांत पाटलांची ऑफर, खासदार विशाल पाटील पॉझिटिव्ह? एका कृतीनं मिळाले संकेत|VIDEO</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/three-from-different-backgrounds-there-will-be-a-clash-chandrakant-patil-spoke-about-the-displeasure-of-the-mahayuti-a-a727/</t>
+          <t>https://saamtv.esakal.com/video/chandrakant-patil-invites-mp-vishal-patil-to-join-bjp-after-jayashreetai-switches-parties-sangli-politics-congress-loss-om0906</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
+          <t>देशातील पहिले डिजिटल शिक्षण पोर्टल महाराष्ट्रात सुरु -उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
+          <t>https://mahasamvad.in/162538/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
+          <t>Chandrakant Patil : ऑपरेशन सिंदूरवरून टीका करणाऱ्या राहुल गांधी, संजय राऊतांना भाजप नेत्याने झाप झापलं; म्हणाले, 'काही जणांना...'</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/chandrakant-patil-slams-congress-leader-rahul-gandhi-and-shivsena-ubt-mp-sanjay-raut-over-operation-sindoor-as11</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
+          <t>Chandrakant Patil | राज्य सरकार अलमट्टीची उंची वाढवू देणार नाही : पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/state-government-will-not-allow-alamatti-height-increase-says-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Pune in Assembly : प्रशासनापुढे मंत्र्यांसह आमदारांनीही हात टेकले; पाटील, मिसाळ, जगताप, रासनेंसह सगळ्यांचाच सुरात सूर</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
+          <t>https://sarkarnama.esakal.com/pune/maharashtra-assembly-pune-mla-chandrakant-patil-madhuri-misal-shankar-jagtap-mla-meeting-post-session-unity-administration-rm82</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>Ajit Pawar : गडकरी, फडणवीसांसमोरच अजितदादांनी चंद्रकांत पाटलांना डिवचलं; दोन दादांवरून निघालेला विषय पोहचला पालकमंत्रिपदापर्यंत...</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
+          <t>https://sarkarnama.esakal.com/pune/ajit-pawar-targets-chandrakant-patil-in-front-of-nitin-gadkari-devendra-fadnavis-guardian-minister-post-maharashtra-politics-rm82</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
+          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>जयश्री पाटलांच्या भाजप प्रवेशावर शिक्कामोर्तब; फडणवीसांच्या उपस्थितीत हाती घेणार कमळ</t>
+          <t>Sanjay Raut : “सत्तेसाठी अमित शाह यांचे पाय चाटणार नाही, उद्धव ठाकरे…”, संजय राऊत यांचं चंद्रकांत पाटील यांना उत्तर</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
+          <t>https://www.loksatta.com/maharashtra/sanjay-raut-strong-answer-to-chandrkant-patil-over-his-statement-over-uddhav-thackeray-also-criticized-amit-shah-scj-81-5018633/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>राज्यातील प्राचार्यांसाठी आनंदाची बातमी ! निवृत्तीचे वय 62 वरून लवकरच होणार 65 वर; उच्च शिक्षणमंत्र्यांचे महत्त्वपूर्ण संकेत</t>
+          <t>भाजपच्या गळाला सांगलीतील बडा नेता? चंद्रकांत पाटलांचे सूचक वक्तव्य, म्हणाले, मोठी रांग लागणार...</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/retirement-age-of-principals-may-be-raised-from-62-to-65-says-minister-chandrakant-patil-941276.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/sangali-news-chandrkant-patil-big-statement-over-operation-lotus-some-big-political-leader-from-sangali-likely-to-join-bjp/931360</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Vishal Patil : ‘आमचं काय व्हायचं ते होऊ दे, तुरुंगात जायचीही तयारी; पण...’; भाजप प्रवेशाबाबत विशाल पाटलांचं मोठं विधान</t>
+          <t>मराठा आरक्षण उपसमितीच्या अध्यक्षपदी राधाकृष्ण विखे-पाटील</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mp-vishal-patil-big-staatment-on-bjp-joining-chandrakant-patilo-offer-911751.html</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/radhakrishna-vikhe-patil-appointed-maratha-reservation-subcommittee-chairman</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BJP Pune Meeting : मेधा कुलकर्णी उठून गेल्या, चंद्रकांतदादा-मोहळांकडून महिला आघाडीच्या आंदोलनाचं समर्थन; भाजप बैठकीत नेमकं काय घडलं?</t>
+          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
+          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
+          <t>BJP-Shivsena Alliance : "...तर मुंबईत उद्धव ठाकरेंना उमेदवार मिळणार नाहीत; चंद्रकांत पाटलांनी दिले युतीचे संकेत?</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt?page=2</t>
+          <t>https://www.navarashtra.com/politics/chandrakant-patlis-suggestive-statement-on-bjp-and-uddhav-thackeray-shiv-sena-alliance-political-news-842296.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CET Exam | एकसमान अभ्यासक्रमांसाठी एकच सीईटी</t>
+          <t>Jayshree Patil |जयश्री पाटील यांचा मुख्यमंत्र्यांच्या उपस्थितीत मुंबईत उद्या भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/single-cet-for-uniform-curriculum-sk95</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-to-join-bjp-in-mumbai-tomorrow-in-presence-of-chief-minister-dc95</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
+          <t>'जयश्री पाटलांचा प्रचार नडला? भाजपने विशाल पाटलांवर हल्लाच चढवला; काँग्रेस प्रेमावरूनही घेरलं</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/mp-vishal-patil-congress-stance-bjp-leader-questions-his-loyalty-over-support-for-jayashree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>पुण्यातील टेकड्यांबाबत मोठा निर्णय, आता 17 टेकड्यांवर अशी होणार उपाययोजना</t>
+          <t>मराठा समाज मंत्रिमंडळ उपसमितीच्या अध्यक्षपदी विखे-पाटील</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/pune/mhatoba-tekdi-pune-chandrakant-patil-will-install-cctv-1333776.html</t>
+          <t>https://www.loksatta.com/mumbai/vikhe-patil-new-head-for-maharashtra-cabinet-sub-committee-on-maratha-quota-zws-70-5324688/</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>सांगली जिल्ह्याच्या विकासासाठी ५४५ कोटींचा आराखडा - पालकमंत्री पाटील</t>
+          <t>तिघे वेगवेगळ्या पार्श्वभूमीतील, खडखड होणारच; चंद्रकांत पाटलांनी नाराजीचा चेंडू भिरकावला</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/rs-545-crore-plan-for-the-development-of-sangli-district-says-guardian-minister-chandrakant-patil-a-a746/</t>
+          <t>https://www.lokmat.com/pune/three-from-different-backgrounds-there-will-be-a-clash-chandrakant-patil-spoke-about-the-displeasure-of-the-mahayuti-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Shaktipeeth Highway: शक्तिपीठ महामार्गाला विरोध, शेतकऱ्यांनी ताकद दाखवली, मंत्री चंद्रकांत पाटलांना घेरलं</t>
+          <t>महाराष्ट्रात महाविद्यालयातील अध्यापकांची ४ हजार ४३५ पदे भरली जाणार- उच्च व तंत्रशिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/clash-between-minister-chandrakant-patil-and-protesters-over-shaktipith-highway-sangli-latest-news-bdk97</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-assistant-professor-recruitment-2025-college-teachers-bharti-education-minister-chandrakant-patil/articleshow/118924405.cms</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
+          <t>Jayashree Patil Joins BJP: बंडखोर नेत्या जयश्री पाटील यांचा भाजप प्रवेश; चंद्रकांतदादांचा काँग्रेससह अजित पवारांना धक्का</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-rebel-congress-leader-jayshree-patil-joins-bjp-in-presence-of-chandrakant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
+          <t>सासऱ्याच्या राजकारणामुळे सुनेला वेदना, नाथाभाऊंचे कुणी टोचले कान?; जळगावाचं राजकारण तापलं</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mla-chandrakant-patil-has-criticized-minister-raksha-khadse-1468718.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
+          <t>Maharashtra Budget 2025 : प्रगती अन विकासाचा ध्यास पाटील : शिक्षणमंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-budget-2025-significant-allocation-for-national-education-policy-implementation-amp17</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
+          <t>BJP Politics : पृथ्वीराज पाटील एकटेच गेले नाहीत... उरलसी सुरली काँग्रेसच मोकळी केली, दिग्गज नेत्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/congress-leader-prithviraj-patil-joins-bjp-along-with-sangli-leaders-and-hundreds-of-congress-workers-as11</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>पुण्यात सामाजिक कार्याचा गौरव, पत्रकारांच्या पाल्ल्यांसाठी 'प्रतिबिंब प्रतिष्ठान'</t>
+          <t>मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
+          <t>https://mahasamvad.in/169668/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
+          <t>जयश्री पाटलांच्या भाजप प्रवेशावर शिक्कामोर्तब; फडणवीसांच्या उपस्थितीत हाती घेणार कमळ</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/jayshree-patil-to-join-bjp-presence-chief-minister-devendra-fadnavis/articleshow/121881414.cms</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
+          <t>राज्यातील प्राचार्यांसाठी आनंदाची बातमी ! निवृत्तीचे वय 62 वरून लवकरच होणार 65 वर; उच्च शिक्षणमंत्र्यांचे महत्त्वपूर्ण संकेत</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
+          <t>https://www.navarashtra.com/maharashtra/retirement-age-of-principals-may-be-raised-from-62-to-65-says-minister-chandrakant-patil-941276.html</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>BJP Pune Meeting : मेधा कुलकर्णी उठून गेल्या, चंद्रकांतदादा-मोहळांकडून महिला आघाडीच्या आंदोलनाचं समर्थन; भाजप बैठकीत नेमकं काय घडलं?</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/153348/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/medha-kulkarni-left-bjp-meeting-midway-as-chandrakant-patil-murlidhar-mohol-backs-deenanath-mangeshkar-case-andolan/articleshow/120120230.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>जयश्री पाटील भाजपसोबत जाणे अनैसर्गिक युती : विशाल पाटील</t>
+          <t>Vishal Patil : ‘आमचं काय व्हायचं ते होऊ दे, तुरुंगात जायचीही तयारी; पण...’; भाजप प्रवेशाबाबत विशाल पाटलांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-joining-bjp-an-unnatural-alliance-says-vishal-patil-dc95</t>
+          <t>https://www.navarashtra.com/maharashtra/mp-vishal-patil-big-staatment-on-bjp-joining-chandrakant-patilo-offer-911751.html</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
+          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt?page=2</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
+          <t>‘बी.फार्म’ आणि ‘डी.फार्म’ अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
+          <t>https://mahasamvad.in/173736/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
+          <t>Manoj Jarange Patil Mumbai Morcha: राज्य सरकारकडून मराठा समाजाच्या उपसमितीचं पुनर्गठन विखे पाटील</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
+          <t>https://marathi.abplive.com/news/politics/manoj-jarange-patil-mumbai-morcha-radhakrishna-vikhe-patil-was-elected-as-the-chairman-of-the-maratha-community-sub-committee-1379179</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
+          <t>CET Exam | एकसमान अभ्यासक्रमांसाठी एकच सीईटी</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
+          <t>https://pudhari.news/maharashtra/solapur/single-cet-for-uniform-curriculum-sk95</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
+          <t>Rohini Khadse : CM फडणवीस म्हणाले ते विशिष्ट पक्षाचे रोहिणी खडसेंनी दिले पुरावे, ते शिंदेंच्या</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
+          <t>https://marathi.abplive.com/news/politics/raksha-khadse-daughter-molestation-case-after-cm-devendra-fadnavis-statement-accused-belonged-to-specific-party-rohini-khadse-claimed-accused-was-supporters-of-shiv-sena-shinde-faction-mla-chandrakant-patil-1347053</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>मोठी बातमी, मराठा आरक्षण उपसमितीचं अध्यक्षपद राधाकृष्ण विखे पाटील यांच्याकडे,</t>
+          <t>पुण्यातील टेकड्यांबाबत मोठा निर्णय, आता 17 टेकड्यांवर अशी होणार उपाययोजना</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
+          <t>https://www.tv9marathi.com/maharashtra/pune/mhatoba-tekdi-pune-chandrakant-patil-will-install-cctv-1333776.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
+          <t>सांगली जिल्ह्याच्या विकासासाठी ५४५ कोटींचा आराखडा - पालकमंत्री पाटील</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
+          <t>https://www.lokmat.com/sangli/rs-545-crore-plan-for-the-development-of-sangli-district-says-guardian-minister-chandrakant-patil-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
+          <t>रणजितसिंह मोहिते पाटलांवर कारवाई होणार का? जयकुमार गोरे म्हणाले, आगे आगे देखिए</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
+          <t>https://marathi.abplive.com/news/solapur/solapur-jayakumar-gore-news-guardian-minister-jayakumar-gore-reaction-to-mla-ranjitsinh-mohite-patil-in-solapur-1361873</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
+          <t>Shaktipeeth Highway: शक्तिपीठ महामार्गाला विरोध, शेतकऱ्यांनी ताकद दाखवली, मंत्री चंद्रकांत पाटलांना घेरलं</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/clash-between-minister-chandrakant-patil-and-protesters-over-shaktipith-highway-sangli-latest-news-bdk97</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
+          <t>व्यावसायिक अभ्यासक्रमाचं शिक्षण विद्यार्थिनींसाठी मोफत</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
+          <t>https://www.newsonair.gov.in/mr/education-free-for-female-students/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
+          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
+          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
+          <t>Jayshree Patil : प्रवेशाआधीच माशी शिंकली! जयश्रीताईंविरोधात भाजपची 'दुसरी' फळी अस्वस्थ?; प्रवेश रखडल्याची चर्चा</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sangli-bjp-leaders-unhappy-ahead-of-congress-rebel-jayshree-patil-joining-bjp-party-as11</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
+          <t>Jayshree Patil | वसंतदादांच्या नातसून जयश्री पाटील यांच्या भाजप प्रवेशामागे बँकाच्या वसुलीचं कारण? सांगलीतील राजकीय समीकरण जाणून घ्या</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-will-joined-bjp-know-the-political-equations-in-sangli-db79</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
+          <t>पुण्यात सामाजिक कार्याचा गौरव, पत्रकारांच्या पाल्ल्यांसाठी 'प्रतिबिंब प्रतिष्ठान'</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-digital-media-social-work-honoured-in-pune-ikshan-pratishthan-for-the-children-of-journalists-ceremony-in-the-presence-of-chandrakant-patil-1360276</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
+          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
+          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
+          <t>जयश्री पाटील भाजपसोबत जाणे अनैसर्गिक युती : विशाल पाटील</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayashree-patil-joining-bjp-an-unnatural-alliance-says-vishal-patil-dc95</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Chandrakant Patil: पालकमंत्र्यांनी साधला पूरग्रस्त कुटुंबांशी संवाद, मदत करण्याचे अश्वासन</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त ‘संविधान गौरव महोत्सव’ - उच्च व तंत्र शिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
+          <t>https://mahasamvad.in/153348/</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
+          <t>kolhapur | आगामी स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती म्हणूनच लढणार</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-to-contest-upcoming-local-body-elections-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
+          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
+          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
+          <t>जे विशाल पाटलांना जमले नाही ते जयश्री पाटलांनी दोनच महिन्यात केलं; भाजप प्रवेशानंतर 25 वर्षांचा प्रश्न निकाली</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-congress-rebel-jayashree-patil-achieves-in-two-months-what-congress-and-vishal-patil-could-not-as11</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
+          <t>वाहतूककोंडीमुक्त कोथरूडसाठी इनस्पेक्शन, ॲक्शन आणि एक्झिक्यूशन त्रिसूत्री</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-orders-cctv-and-ai-challan-boost-to-ease-kothrud-traffic-congestion-in-pune-vsd-99-5254631/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
+          <t>Sangli News: सांगलीत दादा घराण्याला झटका विधानसभेला बंडखोरी केलेल्या जयश्री पाटलांचा</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
+          <t>https://marathi.abplive.com/news/sangli/sangli-district-central-cooperative-bank-vice-president-jayashree-patil-will-join-the-bjp-marathi-news-update-1364524</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Sushma Andhare यांच्यामुळे ठाकरेंच्या शिवसेनेत नाराजी? अंधारे बैठकीला येताच चंद्रकांत मोकाटेंचा काढता पाय</t>
+          <t>जरांगे यांनी कागद-पेन घेऊन चर्चेला यावे!</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/is-sushma-andhare-causing-discontent-in-thackerays-shiv-sena</t>
+          <t>https://pudhari.news/maharashtra/mumbai/jarange-should-come-to-the-discussion-with-paper-and-pen-np88</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
+          <t>पुण्याचे दुसरे दादा जे कधीही दादागिरी करत नाहीत; देवेंद्र फडणवीस यांच्याकडून चंद्रकांतदादांची पाठराखण</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
+          <t>https://www.lokmat.com/pune/another-dada-of-pune-who-never-acts-as-a-bully-chandrakant-dada-gets-support-from-devendra-fadnavis-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
+          <t>मोठी बातमी, मराठा आरक्षण उपसमितीचं अध्यक्षपद राधाकृष्ण विखे पाटील यांच्याकडे,</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-government-made-changes-in-maratha-reservation-sub-committee-rahadhakrishna-vikhe-patil-will-ne-president-1379124</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
+          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
+          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
+          <t>Engineering Admissions: इंजिनियरिंग आणि डिप्लोमाच्या अभ्यासक्रमाच्या प्रवेशासाठी मुदतवाढ; मंत्री चंद्रकांत पाटलांचा निर्णय</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
+          <t>https://saamtv.esakal.com/maharashtra/engineering-and-technology-diploma-admissions-2025-maharashtra-govt-extends-engineering-and-polytechnic-application-deadline-to-june-30-bbj88</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>विधि सीईटीत १०० पर्सेंटाईलचे चार विद्यार्थी चौकशीच्या फेऱ्यात; गैरप्रकाराचा संशय</t>
+          <t>गोपीचंद पडळकर म्हणजे बेन्टेक्सचे सोने: रोहित पवार यांचा नाव न घेता घणाघात; अजित पवार गावकीच्या नादात भावकी ...</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/national/four-students-with-100-percentile-in-law-cet-under-investigation-as-suspicion-of-malpractices-a-a747/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/sangli-rohit-pawar-criticizes-gopichand-padalkar-praises-chandrakant-patil-targets-ajit-pawar-135688604.html</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>भाजपमध्ये आणखी एका नेत्याचा प्रवेश; सांगलीच्या खानापूरमध्ये आता पक्षाची वाढणार ताकद</t>
+          <t>Free education for girl: शुल्कमाफीप्रकरणी चंद्रकांत पाटलांकडून कॉलेजांना भेटी; राज्य सरकारच्या निर्णयानंतरही अडचणी</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/vaibhav-patil-joins-bjp-with-presence-of-chandrakant-patil-895969.html</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girl-free-education-scheme-in-maharashtra-latest-news-chandrakant-patil-mulina-mofat-shikshan-yojana-maharashtra-2024/articleshow/118265312.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
+          <t>Kolhapur Municipal Election | भाजपला हव्यात 33 जागा</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-discussions-with-party-office-bearers-ap84</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
+          <t>Pune Crime Rave Party : नवऱ्यावर इतके गंभीर आरोप झालेत, रोहिणी खडसेंनी राजीनामा द्यायला हवा</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-crime-rave-party-chandrakant-patil-criticizes-rohini-khadse-as-soon-as-her-husband-pranjal-khewalkar-is-arrested-maharashtra-marathi-news-1372935</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Sangli : परदेशी गुंतवणुकीत महाराष्ट्र देशात प्रथम</t>
+          <t>Pune | हल्ल्याची हकिकत ऐकून मन हेलावून गेलं, चंद्रकांत पाटलांकडून गनबोटे-जगदाळे कुटुंबियांचे सांत्वन</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/maharashtra-tops-india-in-foreign-investment-says-chandrakant-patil-dc95</t>
+          <t>https://civicmirror.in/news/pune-or-heartbroken-to-hear-the-truth-about-the-attack-chandrakant-patil-consoles-ganbote-jagdale-families/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
+          <t>Chandrakant Patil: पालकमंत्र्यांनी साधला पूरग्रस्त कुटुंबांशी संवाद, मदत करण्याचे अश्वासन</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
+          <t>https://www.tarunbharat.com/chandrakant-atial-discussion-with-flood-situated-people-sangli-walwa-marathi-news/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Gopichand Padalkar Politics : जिल्हा नियोजन बैठकीत पडळकर-आयुक्त गांधी यांच्यात खडाजंगी? नेमकं कारणं काय?</t>
+          <t>विधि सीईटीत १०० पर्सेंटाईलचे चार विद्यार्थी चौकशीच्या फेऱ्यात; गैरप्रकाराचा संशय</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-mla-gopichand-padalkar-vs-sangli-commissioner-gandhi-over-action-on-street-vendors-in-planning-meeting-as11</t>
+          <t>https://www.lokmat.com/national/four-students-with-100-percentile-in-law-cet-under-investigation-as-suspicion-of-malpractices-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
+          <t>'जिल्हा बँक मुश्रीफांकडे आहे म्हणून का?, मंत्री चंद्रकांत पाटलांच्या टिप्पणीची कोल्हापूर जिल्हयात रंगली 'चर...</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
+          <t>https://www.lokmat.com/kolhapur/discussion-in-the-district-over-minister-chandrakant-patil-comments-on-kolhapur-district-bank-deposits-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
+          <t>Polytechnic Admissions 2025 | पॉलिटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ, उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील यांचे निर्देश...</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
+          <t>https://civicmirror.in/news/polytechnic-admissions-2025-or-extension-of-deadline-for-submission-of-applications-for-polytechnic-courses-instructions/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
+          <t>Chandrakant Patil: “तुम्हालाही चक्कर येईल…”; चंद्रकांत पाटलांची संजय राऊतांवर टीका</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5018629/chandrakant-patil-criticized-sanjay-raut-over-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
+          <t>तुम्ही अजून देखील पुणेकरांना पुण्याचे वाटत नाही, त्यांना कोल्हापूरचेच वाटता; अजितदादांचा पाटलांना चिमटा</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
+          <t>https://www.lokmat.com/pune/pune-citizens-still-dont-think-you-belong-to-pune-they-think-you-belong-to-kolhapur-ajit-pawar-taunt-to-chandrakant-patil-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
+          <t>Maharashtra Politics: भाजपला नको 'काका'; संजयकाका पाटलांसाठी भाजपचे दरवाजे बंद</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-minister-chandrakant-patil-end-talks-of-former-sangli-mp-sanjay-kaka-patil-joining-bjp-bbj88</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>पदविका प्रवेशाला १ लाखांहून अधिक विद्यार्थ्यांचा प्रवेश; प्रवेशाला १४ ऑगस्टवरून ४ सप्टेंबरपर्यंत मुदतवाढ</t>
+          <t>Vita Political News | विट्याचे माजी नगराध्यक्ष वैभव पाटील यांचा मंगळवारी भाजपमध्ये प्रवेश, राष्ट्रवादीला सोडचिठ्ठी</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-diploma-admission-see-surge-chandrakant-patil-announce-deadline-extension-mumbai-print-news-rds-00-5299696/</t>
+          <t>https://pudhari.news/maharashtra/sangali/former-vita-corporator-vaibhav-patil-joins-bjp-quits-ncp-as80</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>कोरोना काळात बंद झालेला पुलोत्सव पुन्हा सुरू होणार; चंद्रकांत पाटलांची माहिती</t>
+          <t>Sangli Politics : भाजपला मोठं यश; जयश्री पाटील यांचा BJPमध्ये प्रवेश, सांगलीत मोठा राजकीय गेम</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/bridge-festival-which-was-closed-during-corona-period-will-resume-information-from-chandrakant-patil-a-a727/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/sangli/major-victory-for-bjp-in-sangli-jayashree-patil-joins-bjp-from-congress/articleshow/121933601.cms</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
+          <t>Sangli Flood: पूरग्रस्तांच्या पुनर्वसनाचा पर्याय, मात्र नागरिकांचा विरोध</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-flood-rehabilitation-plan-faces-public-opposition-sk95</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>विहित नमुन्यात EWS प्रमाणपत्र सादर न करणाऱ्यांचा अर्ज एक वर्षासाठी ग्राह्य धरणार,</t>
+          <t>kolhapur | महायुतीवर शिक्कामोर्तब; आता नाराजी दूरकरण्याचे आव्हान</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/education/chandrakant-patil-announced-ews-certificate-accepted-for-one-year-economically-weaker-section-student-maharashtra-education-marathi-news-1340514</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/mahayuti-alliance-finalized-now-challenge-to-resolve-discontent-ap84</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>जळगावात महामार्गाचे काम रोखले; शेतकऱ्यांसह शिंदे गटाचे आमदार पोलिसांच्या ताब्यात</t>
+          <t>Sangli News Maharashtra Politics : महायुतीचे 'मिशन सांगली', महाविकास आघाडीचा बालेकिल्ला फुटणार?</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/thackeray-group-mlas-including-farmers-taken-into-police-custody-for-blocking-highway-work-in-jalgaon-amy-95-5246634/</t>
+          <t>https://news18marathi.com/maharashtra/mahayuti-leaders-ajit-pawar-chandrakant-patil-and-shrikant-shinde-on-mission-sangli-for-damage-maha-vikas-aghadi-1386892.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
+          <t>डॉ. प्रतापसिंह जाधव यांनाच सर्किट बेंचचे श्रेय</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/credit-for-circuit-bench-goes-to-dr-pratapsinh-jadhav-says-minister-chandrakant-patil-ap84</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>सांगलीत काँग्रेसला मोठा धक्का; जयश्रीताईंना पालकमंत्री भेटले, भाजप प्रवेशाचे ठरले</t>
+          <t>Ajit Pawar on Jayant Patil : कार्यक्रमाला वाळव्यात बोलवायचं आणि आमचीच बिन पाण्यानं करायची अजितदादा</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/congress-rebel-jayashreetai-patil-from-sangli-will-join-bjp-a-a468-c746/</t>
+          <t>https://marathi.abplive.com/news/politics/ajit-pawar-funny-comment-on-jayant-patil-in-front-of-rohit-pawar-and-chandrakant-patil-sangli-maharashtra-politics-marathi-news-1377436</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
+          <t>Girls stipend scheme : 5 लाख मुलींना दरमहा 2 हजार रुपये मानधन देण्याचे लक्ष्य</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-girls-scheme-2k-monthly-stipend-5-lakh-beneficiaries-ab96</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>सासरच्या लोकांसह धर्मगुरूकडून धर्मांतरणासाठी दबाव, छळाला कंटाळून सात महिन्याच्या गर्भवतीची आत्महत्या</t>
+          <t>Samtrjeet Ghatge : समरजीत घाटगेंना लागले घरवापसीचे वेध; भाजप प्रवेशासाठी चंद्रकांतदादा काढणार मुहूर्त</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/samarjit-ghatge-bjp-entry-kagal-assembly-2025-chandrakant-patil-kolhapur-hn97-rg93</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>रोहित, बघतो तुला घरी गेल्यावर….! काका – पुतणे आणि टोमणे….</t>
+          <t>सांगली जिल्ह्यात अमली पदार्थांविरोधात ३० कारवाया, ५० आरोपींना अटक</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
+          <t>https://www.lokmat.com/sangli/30-operations-against-drugs-in-sangli-district-50-accused-arrested-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>संजय राऊत अन् त्यांचा पक्षच 'पनवती'; राऊतांची 'पनवती' टीका भाजप नेत्याच्या जिव्हारी, प्रत्युत्तर देत म्हणाले...</t>
+          <t>भाजपमध्ये आणखी एका नेत्याचा प्रवेश; सांगलीच्या खानापूरमध्ये आता पक्षाची वाढणार ताकद</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-leader-chandrakant-patil-has-responded-to-sanjay-raut-criticism-of-panvati-latest-marathi-news-pp0731</t>
+          <t>https://www.navarashtra.com/politics/vaibhav-patil-joins-bjp-with-presence-of-chandrakant-patil-895969.html</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
+          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
+          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
+          <t>Ravindra Dhangekar : चंद्रकांतदादा अन् मोहोळांच्या युद्धात गजा मारणेचा बळी? रवींद्र धंगेकरांचे खळबळजनक गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/ravindra-dhangekar-allegation-chandrakant-patil-and-murlidhar-mohol-politics-for-gajanan-marne-arrested/854647/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Farmer Loan Waiver : कर्जमाफीसाठी निवडणुकीची वाट पाहताय?; सतेज पाटलांची सरकारवर टिका</t>
+          <t>पुण्यात भाजपच्या तीन नेत्यांमधील शीतयुद्ध चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/waiting-for-elections-to-waive-farm-loans-satej-patil-slams-maharashtra-govt</t>
+          <t>https://www.loksatta.com/politics/cold-war-between-bjp-leaders-chandrakant-patil-murlidhar-mohol-and-medha-kulkarni-in-pune-on-rise-print-politics-news-mrj-95-5012957/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Sanjay Shirsat PA controversy : सामाजिक न्याय मंत्र्यांचा 'पीए' बांधकाम कामगार? चंद्रकांतदादांचा चौकशीला नकार घंटा का?</t>
+          <t>Gopichand Padalkar Politics : जिल्हा नियोजन बैठकीत पडळकर-आयुक्त गांधी यांच्यात खडाजंगी? नेमकं कारणं काय?</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivsena-minister-sanjay-shirsat-pa-name-household-items-list-sangli-bjp-minister-chandrakant-patil-ignores-inquiry-pp82-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/bjp-mla-gopichand-padalkar-vs-sangli-commissioner-gandhi-over-action-on-street-vendors-in-planning-meeting-as11</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
+          <t>Sangli : परदेशी गुंतवणुकीत महाराष्ट्र देशात प्रथम</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
+          <t>https://pudhari.news/maharashtra/sangali/maharashtra-tops-india-in-foreign-investment-says-chandrakant-patil-dc95</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
+          <t>Jayshree Patil | जयश्री पाटील यांचा आज भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
+          <t>https://pudhari.news/maharashtra/sangali/jayshree-patil-joins-bjp-today-sk95</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Kolhapur Politics : जिंकणाऱ्या पैलवानांवरच खेळणार डाव...'स्थानिक'ची कुस्ती जिंकण्यासाठी 'महायुती'चा प्लॅन ठरला!</t>
+          <t>Ajit Pawar : निवेदिका पुण्याच्याच आहेत का हो? चंद्रकांत पाटलांना 'वगळताच' अजितदादांचा टोला, फडणवीस म्हणाले तुम्हीच त्यांना...</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-local-body-election-bjp-ncp-shiv-sena-chandrakant-patil-hasan-mushrif-hn97-rg93</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/ajit-pawar-devendra-fadnavis-shares-fun-moment-at-pune-lokmanya-tilak-award-ceremony-with-chandrakant-patil-eknath-shinde/articleshow/123054887.cms</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
+          <t>पुण्यात वैष्णवांचा मेळा: संत तुकाराम आणि ज्ञानेश्वर माऊलींची पालखी पुण्यात दाखल, मंत्री चंद्रकांत पाटील विठ...</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashadi-ekadashi-warkari-palakhi-pune-photos-videos-135276858.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
+          <t>पाण्याबाबत शाश्वत उपाययोजनांची अंमलबजावणी करा</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
+          <t>https://pudhari.news/maharashtra/sangali/chandrakant-patil-water-management-sustainable-solutions</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>राज्यात उच्च शिक्षण क्षेत्रात भव्य भरती; प्राध्यापक व कर्मचाऱ्यांसाठी ८४०० पदांवर नियुक्तीची संधी</t>
+          <t>Sangli Politics: मलाही मंत्री व्हायचंय, भविष्यात काँग्रेससोबत राहीन असे नाही; विशाल पाटलांच्या विधानाने खळबळ</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/grand-recruitment-in-higher-education-sector-in-the-state-appointment-notice-for-8400-posts-for-professors-and-employees/07251413</t>
+          <t>https://www.lokmat.com/sangli/i-will-join-some-other-party-in-the-future-mp-vishal-patil-statement-creates-a-stir-a-a468-c746/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
+          <t>Muktainagar APMC : मुक्ताईनगरला होणार स्वतंत्र बाजार समिती</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
+          <t>https://agrowon.esakal.com/agro-special/independent-apmc-for-muktainagar-approved-by-state-govt</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
+          <t>विद्यार्थी हित लक्षात घेऊन नॅक मुल्यांकनासाठी महाविद्यालयांना ६ महिन्यांची मुदतवाढ</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
+          <t>https://mahasamvad.in/166808/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: मी मंत्री कसा झालो, मलाही कळालं नाही, मुरलीधर मोहोळ यांच्या विधानाने राजकीय वर्तुळात चर्चा|VIDEO</t>
+          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/murli-mohol-unexpected-union-minister-appointment-pune-mp-bjp-leaders-reactions-om0906</t>
+          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>सांगलीत काँग्रेसला मोठा धक्का! खासदार विशाल पाटलांच्या कट्टर समर्थकांचा भाजपात प्रवेश</t>
+          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/big-blow-to-congress-vishal-patil-loyalists-in-sangli-former-mayor-joins-bjp-nck90</t>
+          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>बीफार्म आणि डीफार्म अभ्यासक्रमाच्या संस्थांना निकष पूर्ण करण्यासाठी एक महिन्याची अंतिम मुदत</t>
+          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bpharm-dpharm-institutes-must-complete-norms-in-one-month-or-face-admission-ban-ocd-94-5266306/</t>
+          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Maharashtra Polytechnic admissions 2025: पॉलीटेक्निक अभ्यासक्रमासाठी अर्ज सादर करणास मुदतवाढ</t>
+          <t>Baramati Rain : मुसळधार पावसाचं रौद्र रुप; बारामतीत 3 इमारती पावसाने खचल्या, नागरीक भयभीत</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/dte-maharashtra-polytechnic-admissions-2025-deadline-extended-for-applications-until-june-26/articleshow/121889185.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maharashtra-rain-update-three-building-damage-due-to-heavy-rainfall-in-baramati-brk/articleshow/121396291.cms</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
+          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
+          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Focus on goal of providing education rather than looking at deposit of scholarship money: Chandrakant Patil</t>
+          <t>पदविका प्रवेशाला १ लाखांहून अधिक विद्यार्थ्यांचा प्रवेश; प्रवेशाला १४ ऑगस्टवरून ४ सप्टेंबरपर्यंत मुदतवाढ</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/focus-on-goal-of-providing-education-rather-than-looking-at-deposit-of-scholarship-money-chandrakant-patil-9998759/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-diploma-admission-see-surge-chandrakant-patil-announce-deadline-extension-mumbai-print-news-rds-00-5299696/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Maharashtra forms new body to ensure effective implementation of NEP 2020 in higher education</t>
+          <t>कोरोना काळात बंद झालेला पुलोत्सव पुन्हा सुरू होणार; चंद्रकांत पाटलांची माहिती</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-forms-new-body-to-ensure-effective-implementation-of-nep-2020-in-higher-education-9964171/</t>
+          <t>https://www.lokmat.com/pune/bridge-festival-which-was-closed-during-corona-period-will-resume-information-from-chandrakant-patil-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>शिवाजी विद्यापीठाचा आज दीक्षान्त समारंभ</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/shivaji-university-convocation-ceremony-today</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Chandrakant Patil Proposes Safety Measures to Prevent Fires on Pune’s 17 Hills</t>
+          <t>जळगावात महामार्गाचे काम रोखले; शेतकऱ्यांसह शिंदे गटाचे आमदार पोलिसांच्या ताब्यात</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/chandrakant-patil-proposes-safety-measures-to-prevent-fires-on-punes-17-hills/</t>
+          <t>https://www.loksatta.com/nashik/thackeray-group-mlas-including-farmers-taken-into-police-custody-for-blocking-highway-work-in-jalgaon-amy-95-5246634/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Chandrakant Patil Launches ATAL Initiative For Students; Check Details</t>
+          <t>रोहित, बघतो तुला घरी गेल्यावर….! काका – पुतणे आणि टोमणे….</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-minister-chandrakant-patil-launches-atal-initiative-for-students-check-details</t>
+          <t>https://www.tv9marathi.com/videos/maharashtra-politics-ajit-pawar-jayant-patil-rohit-pawar-clash-1471655.html</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>No Ajit Pawar vs Chandrakant Patil In Pune: PMC Polls Likely To Be Held Under Leadership Of Muralidhar Mohol</t>
+          <t>सांगलीच्या पूरपट्ट्यात १० हजारांवर अतिक्रमणे, हटविण्याचे औपचारिक आदेश की खरोखर कारवाई होणार</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/no-ajit-pawar-vs-chandrakant-patil-in-pune-pmc-polls-likely-to-be-held-under-leadership-of-muralidhar-mohol</t>
+          <t>https://www.lokmat.com/sangli/over-10000-encroachments-in-sanglis-floodplain-formal-orders-to-remove-them-or-will-action-really-be-taken-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
+          <t>गोपीचंद पडळकर – सांगली आयुक्तांमध्ये शाब्दिक खडाजंगी</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-minister-patil-confirms-verbal-clash-between-mla-padalkar-and-municipal-commissioner-ocd-94-5164995/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Maharashtra: Over 1,600 EWS Students Granted Special Exemption For Certificate Submission</t>
+          <t>सांगलीत काँग्रेसला मोठा धक्का; जयश्रीताईंना पालकमंत्री भेटले, भाजप प्रवेशाचे ठरले</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-over-1600-ews-students-granted-special-exemption-for-certificate-submission</t>
+          <t>https://www.lokmat.com/sangli/congress-rebel-jayashreetai-patil-from-sangli-will-join-bjp-a-a468-c746/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>kolhapur : हसन मुश्रीफ यांच्या मनपातील कारभार्‍यांच्या हाती ‘कमळ’!</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/former-ncp-corporators-from-ajit-pawar-faction-join-bjp-dc95</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>चंद्रकांत पाटील यांच्याकडून भाजपा प्रवेशाची ऑफर, विशाल पाटील म्हणाले...</t>
+          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/chandrakant-patil-offered-to-join-bjp-vishal-patil-said-a-a301/</t>
+          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Carry On Yojana: कॅरी ऑन योजना दुर्दैवी..' चंद्रकांत पाटलांच्या निर्णयाला ABVP चा विरोध</t>
+          <t>राष्ट्रीय अध्यापक शिक्षा परिषदेच्या नियमानुसार बी.एड. महाविद्यालयांवर कारवाई – उच्च व तंत्रशिक्षण मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/carry-on-scheme-unfortunate-for-maharashtra-says-abvp-on-chandrakant-patil-decision-7648590</t>
+          <t>https://civicmirror.in/news/action-against-b-ed-colleges-as-per-the-rules-of-the-national-council-for-teacher-education-higher-and-technical/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>मोठी बातमी : उच्च शिक्षण विभागात मोठी पदभरती… उच्च व तंत्रशिक्षणमंत्र्यांनीच दिली माहिती</t>
+          <t>संजय राऊत अन् त्यांचा पक्षच 'पनवती'; राऊतांची 'पनवती' टीका भाजप नेत्याच्या जिव्हारी, प्रत्युत्तर देत म्हणाले...</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/massive-hiring-in-higher-education-minister-chadrakant-patil-confirms-pune-print-news-ccp-14-ocd-94-5253092/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-leader-chandrakant-patil-has-responded-to-sanjay-raut-criticism-of-panvati-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Sangli : हर्षल पाटील आत्महत्या प्रकरणात नवा ट्विस्ट, जलजीवन मिशनच्या मुख्य ठेकेदाराने सांगितली धक्कादायक माहिती</t>
+          <t>सासरच्या लोकांसह धर्मगुरूकडून धर्मांतरणासाठी दबाव, छळाला कंटाळून सात महिन्याच्या गर्भवतीची आत्महत्या</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/sangli-harshal-patil-death-case-major-twist-jal-jeevan-mission-main-contractor-reveals-pending-payment-from-maharashtra-government-latest-marathi-news-yps99</t>
+          <t>https://www.etvbharat.com/mr/!state/sangli-crime-news-seven-month-pregnant-woman-self-killed-after-alleged-being-tortured-by-in-laws-for-religious-conversion-3-arrested-maharashtra-news-mhs25061200648</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Sangli News:विशाल पाटलांना सांगलीत धक्क्यावर धक्के सुरुच चुलत वहिनींनंतर आता खंद्या</t>
+          <t>State may halt admissions to pharmacy colleges flouting norms</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/former-corporator-manoj-sargar-who-played-a-role-in-getting-vishal-patil-elected-is-joining-the-bharatiya-janata-party-on-monday-1375918</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
+          <t>Ahead of Mumbai protest, Maharashtra minister asks Jarange to hold talks with govt</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
+          <t>https://www.ptinews.com/story/national/Ahead-of-Mumbai-protest--Maharashtra-minister-asks-Jarange-to-hold-talks-with-govt/2848338</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Sangli Politics : भाजप प्रदेशाध्यक्षांचं काँग्रेस जिल्हाध्यक्षांच्या घरी स्नेहभोजन : जेवताना पक्षप्रवेशाचा मुहूर्तही काढला</t>
+          <t>BMC to restart withdrawn services by tanker association with police help</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/angli-congress-leader-prithviraj-patil-joins-bjp-cm-devendra-fadnavis-maharashtra-political-switch-hn97</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-to-restart-withdrawn-services-by-tanker-association-with-police-help-101744571005989.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Vishal Patil : 'आमचं घर फोडलं, पण मी काँग्रेसचाच', विशाल पाटलांचा भाजपवर हल्लाबोल</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/vishal-patil-attacks-bjp-over-jayshree-patil-joining-as11</t>
+          <t>https://theprint.in/india/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/2625634/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>BJP Pune Meeting : मेधा कुलकर्णी बैठकीतून उठून गेल्या चंद्रकांतदादा-मोहोळांकडून महिला</t>
+          <t>Police bust chain-snatching gang; two held, minor detained</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/medha-kulkarni-left-the-meeting-chandrakant-patil-murlidhar-mohol-supported-the-deenanath-mangeshkar-case-andolan-tanisha-bhise-death-case-what-exactly-happened-during-the-meeting-1353526</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
+          <t>Abu Azmi writes letter to Maharashtra Speaker Rahul Narwekar to revoke his suspension</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
+          <t>https://www.indiatvnews.com/maharashtra/maharashtra-abu-azmi-writes-letter-to-speaker-rahul-narwekar-to-revoke-his-suspension-over-statement-on-aurangzeb-latest-updates-2025-03-07-979620</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Sangli Politics: मलाही मंत्री व्हायचंय, भविष्यात काँग्रेससोबत राहीन असे नाही; विशाल पाटलांच्या विधानाने खळबळ</t>
+          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/i-will-join-some-other-party-in-the-future-mp-vishal-patil-statement-creates-a-stir-a-a468-c746/</t>
+          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Double Voting Allegations | Rohini Khadse वर Chandrakant Patil यांचा गंभीर आरोप</t>
+          <t>Maharashtra’s new university faculty recruitment rules emphasise academics, research, teaching</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
+          <t>https://news.careers360.com/maharashtra-university-faculty-recruitment-resume-new-evaluation-rules-academics-research-teaching-interview</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>कारण राजकारण : कलमाडी नंतर पुण्याचा चेहरा कोण ? हा प्रश्न आजही कायम</t>
+          <t>Wonder if some forces are working to destabilise Maharashtra: Minister amid Shaktipeeth stir</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/because-politics-who-is-the-face-of-pune-after-kalmadi-the-rise-of-ajit-pawar-the-late-girish-bapat-chandrakant-patil-and-muralidhar-mohol-in-pune-political-transition-a-a955-c1008/</t>
+          <t>https://www.newsdrum.in/national/wonder-if-some-forces-are-working-to-destabilise-maharashtra-minister-amid-shaktipeeth-stir-9664386</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Crop Damage Survey : महापुराचे पाणी शिरलेल्या सर्व शेतीचे पंचनामे करा</t>
+          <t>Maharashtra Govt Unveils New Grading System To Modernise Public Libraries</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/guardian-minister-orders-crop-damage-survey-in-flood-hit-areas-mj18</t>
+          <t>https://www.mypunepulse.com/maharashtra-govt-unveils-new-grading-system-to-modernise-public-libraries/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>सांगलीत 'कमळ' सुसाट, काँग्रेसला गळती? भाजप दुसरा मोठा धक्का देण्याच्या तयारीत, आमदाराच्या वक्तव्याने खळबळ</t>
+          <t>Chandrakant Patil : मनोज जरांगे यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sudhir-gadgils-statement-fuels-bjp-congress-tensions-as-defection-rumors-gain-momentum-over-prithviraj-patils-bjp-entry-in-sangli-as11</t>
+          <t>https://www.msn.com/mr-in/news/other/chandrakant-patil-%E0%A4%AE%E0%A4%A8-%E0%A4%9C-%E0%A4%9C%E0%A4%B0-%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%95-%E0%A4%97%E0%A4%A6-%E0%A4%85%E0%A4%A8%E0%A5%8D-%E0%A4%AA%E0%A5%87%E0%A4%A8-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-%E0%A4%86%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AC-%E0%A4%AC%E0%A4%A4-%E0%A4%9A%E0%A4%B0%E0%A5%8D%E0%A4%9A%E0%A5%87%E0%A4%B2-%E0%A4%AC%E0%A4%B8-%E0%A4%B5%E0%A4%82-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%86%E0%A4%B5-%E0%A4%B9%E0%A4%A8/ar-AA1L414d</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>महायुतीच्या चार नेत्यांची कोल्हापूर जिल्ह्यात लागणार कसोटी; महापालिका, जिल्हा परिषदेत सत्ता मिळवण्याचे उद्द...</t>
+          <t>सीईटीसाठी आता राज्याबाहेर परीक्षा केंद्र नाही; विधी पाच वर्ष परीक्षेच्या निकालानंतर उच्च व तंत्र शिक्षण विभागाचा निर्णय</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/in-the-upcoming-elections-the-responsibility-lies-with-mahayuti-minister-prakash-abitkar-hasan-mushrif-chandrakant-patil-and-mla-vinay-kore-in-kolhapur-district-a-a746/</t>
+          <t>https://www.loksatta.com/mumbai/no-more-mh-cet-exams-outside-maharashtra-chandrakant-patil-mumbai-print-news-zws-70-5137733/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
+          <t>Maharashtra Breaking News LIVE 21 April 2025 : माझ्या शब्दांची ‘ते’ कधीही तोडमोड करतील...</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-mns-raj-thackeray-uddhav-thackeray-alliance-eknath-shinde-politics-news-in-marathi-aajchya-thalak-batmya-monday-21-april-2025-1388817.html</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
+          <t>Chandrakant Patil : राऊतांची नजर कावीळ झाल्यासारखी चंद्रकांत पाटलांचा संजय राऊतांवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
+          <t>https://marathi.abplive.com/videos/news/politics-chandrakant-patil-sanjay-raut-bjp-uddhav-thackeray-narendra-modi-marathi-news-abp-majha-1364424</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
+          <t>Chandrakant Patil : प्राध्यापक भरतीवरील बंदी उठली; नवीन कार्यपद्धतीनुसार होणार भरती</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
+          <t>https://www.esakal.com/maharashtra/ban-on-professor-recruitment-ends-new-recruitment-system-to-be-adopted-chandrakant-patil-pjp78</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
+          <t>महाराष्ट्रातील सीईटी कक्षाकडून घेण्यात येणाऱ्या प्रवेश नोंदणीला मुदतवाढ; विद्यार्थी हितासाठी निर्णय!</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
+          <t>https://www.lokmat.com/education/extension-of-admission-registration-conducted-by-cet-cells-in-maharashtra-decision-taken-in-the-interest-of-students-said-chandrakant-patil-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
+          <t>Double Voting Allegations | Rohini Khadse वर Chandrakant Patil यांचा गंभीर आरोप</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-double-voting-allegations-chandrakant-patil-accuses-rohini-khadse-of-voting-twice-in-kothali-and-muktainagar-sparks-maharashtra-political-row-1379422</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
+          <t>व्यावसायिक अभ्यासक्रमांच्या प्रवेशासाठी राज्यात ‘विद्यार्थी सहाय्यता केंद्र’ स्थापन करणार</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-to-set-up-help-centres-for-technical-course-applicants-mumbai-print-news-ocd-94-5253012/</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>संजयकाकांसाठी भाजपचे दरवाजे बंद; चंद्रकांत पाटील म्हणाले, आम्ही दुसऱ्या पाटलांमागे</t>
+          <t>AI University Maharashtra: देशातील पहिले आर्टीफिशियल इंटेलिजन्स विद्यापीठ महाराष्ट्रात; समिती गठीत करण्याचे आदेश</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/chandrakant-patil-on-sanjaykaka-patil-and-ones-again-offer-to-vishal-patil-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/career/career-news/indias-first-artificial-intelligence-university-in-maharashtra-order-for-constitution-of-committee-chandrakant-patil/articleshow/117637901.cms</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>कला पदविका अभ्यासक्रमांसाठी प्रवेश घेण्याचे मंत्री चंद्रकांत पाटील यांचे आवाहन</t>
+          <t>‘मिरज सिव्हिल’मधील दोषींवर कारवाई होईल</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Minister-Chandrakant-Patil--appeal-to-take-admission-in-Arts-Diploma-courses</t>
+          <t>https://pudhari.news/maharashtra/sangali/action-against-culprits-in-miraj-hospital-baby-theft-case-ab96</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Chandrakant Patil</t>
+          <t>बीबीए, बीसीएची पुन्हा प्रवेश परीक्षा घ्या : मंत्री पाटील</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-chandrakant-patil-calls-for-re-exam-bba-bca-entrance-ap84</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
+          <t>Abu Azami : औरंगजेबाला महान राजा म्हणणाऱ्या अबू आझमींवर अखेर कारवाई</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
+          <t>https://www.tv9marathi.com/maharashtra/samajwadi-party-mla-abu-azami-suspended-from-maharashtra-assembly-for-praise-aurangzeb-minister-chandrakant-patil-inform-house-1360855.html</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
+          <t>'वसंतदादा घराण्यात मुख्यमंत्रिपद, आमदारकी, खासदारकी...', आमच्यावरही असा अन्याय करावा; काँग्रेस नेत्याची जयश्री पाटलांवर उपरोधिक टीका</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prithviraj-patil-slams-jayshree-patil-bjp-entry-congress-reaction-sangli-politics-as11</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
+          <t>Sharad Lad : शरद लाडही भाजपच्या वाटेवर?</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
+          <t>https://pudhari.news/maharashtra/sangali/sharad-lad-on-way-to-join-bjp-sk95</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
+          <t>Sanjay Shirsat PA controversy : सामाजिक न्याय मंत्र्यांचा 'पीए' बांधकाम कामगार? चंद्रकांतदादांचा चौकशीला नकार घंटा का?</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/shivsena-minister-sanjay-shirsat-pa-name-household-items-list-sangli-bjp-minister-chandrakant-patil-ignores-inquiry-pp82-as11</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
+          <t>Girls Free Education Maharashtra: विद्यार्थिनींसाठी महत्त्वाची बातमी! आता 'इतर शुल्का'तूनही मुक्तता, लवकरच लाभ</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
+          <t>https://marathi.indiatimes.com/career/career-news/girls-free-education-in-maharashtra-special-scheme-for-other-fees-assurance-from-chandrakant-patil/articleshow/123376903.cms</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Sangli | गुन्हेगारी घटनांवर नियंत्रणासाठी जिल्ह्यातील शस्त्र परवान्यांचा आढावा घ्या – पालकमंत्री चंद्रकांत पाटील</t>
+          <t>सांगलीत 'कमळ' सुसाट, काँग्रेसला गळती? भाजप दुसरा मोठा धक्का देण्याच्या तयारीत, आमदाराच्या वक्तव्याने खळबळ</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/sangli-or-review-the-arms-licenses-in-the-district-to-control-criminal-incidents-guardian-minister-chandrakant-patil/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sudhir-gadgils-statement-fuels-bjp-congress-tensions-as-defection-rumors-gain-momentum-over-prithviraj-patils-bjp-entry-in-sangli-as11</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
+          <t>शाळेत मुलांना अमली पदार्थ विरोधी शपथ देणार – मंत्री पाटील</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-guardian-minister-chandrakant-patil-oath-against-drugs-school-students-css-98-4912323/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
+          <t>सांगलीतील अंबाबाई तालीम संस्थेच्या ‘एबीजीआय’ शैक्षणिक संकुलाला स्वायत्त दर्जा</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
+          <t>https://www.loksatta.com/maharashtra/chandrakant-patil-backs-abgi-vision-for-deemed-university-status-rds-00-5268767/</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
+          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
+          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Polytechnic | अभियांत्रिकी पदविका प्रवेश अर्ज नोंदणीसाठी आणखी मुदतवाढ, नवीन वेळापत्रक जाहीर - मंत्री चंद्रकांत पाटील</t>
+          <t>मुक्ताईनगरचे आमदार चंद्रकांत पाटलांना पोलिसांनी घेतलं ताब्यात ; नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/polytechnic-or-engineering-diploma-admission-application-registration-deadline-extended-new-schedule-announced-minister/</t>
+          <t>https://jalgaonlive.news/muktainagar-mla-chandrakant-patil-arrested-by-police-120015/</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
+          <t>Jalgaon News: शिवसेना आमदार चंद्रकांत पाटील यांना पोलिसांनी घेतलं ताब्यात, नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
+          <t>https://marathi.timesnownews.com/maharashtra/shiv-sena-mla-chandrakant-patil-taken-into-custody-by-police-article-152324476</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>जयंत पाटलांच्या डोक्यात जे सुरू ते चेहऱ्यावर उमटत नाही : चंद्रकांत पाटील</t>
+          <t>सीईटी परीक्षा पॅटर्नमध्ये मोठा बदल; चंद्रकांत पाटील यांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/68678/</t>
+          <t>https://eduvarta.com/maharashtra-cet-not-to-be-held-outside-state-to-prevent-malpractices-told-minister-chandrakant--patil</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Satara News : आणखी १७ शिक्षकांची दिव्यांग प्रमाणपत्रे अयोग्य; आठ टप्प्यांमध्ये ३७९ जणांची तपासणी</t>
+          <t>BBA, BCA साठी पुन्हा CET घेण्याच्या मंत्री चंद्रकांत पाटील यांच्या सूचना</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/satara-news-disability-certificates-of-17-more-teachers-are-invalid/</t>
+          <t>https://www.eduvarta.com/Minister-Chandrakant-Patils-instructions-to-conduct-CET-again-for-BBA-BCA</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>दख्खन जत्रेतून स्वयंसहाय्यता बचत गटाच्या महिलांना आर्थिकदृष्ट्या स्वावलंबी होण्यास प्रोत्साहन - पालकमंत्री चंद्रकांत पाटील</t>
+          <t>Chandrakant Patil | Sant Puja and distribution of useful materials to Warkari brothers</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.athawadavishesh.com/34215/</t>
+          <t>https://policenama.com/chandrakant-patil-sant-puja-and-distribution-of-useful-materials-to-warkari-brothers-on-the-occasion-of-ashadhi-wari/</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Sangli Politics : काँग्रेसला खिंडार; पृथ्वीराज पाटील शेकडो समर्थकांसह भाजपात!</t>
+          <t>BAMU चा मोठा निर्णय : चंद्रकांत पाटील, सुळे, दानवे, मुंडे यांच्या शिक्षण संस्थांसह 113 महाविद्यालयांचे प्रवेश थांबवले</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/sangli-politics-congress-suffers-setback-pruthviraj-patil-joins-bjp-with-hundreds-of-supporters/</t>
+          <t>https://civicmirror.in/news/bamu-s-big-decision-admissions-to-113-colleges-including-educational-institutions-of-chandrakant-patil-sule-munde/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Police bust chain-snatching gang; two held, minor detained</t>
+          <t>प्राध्यापक भरतीसाठी उच्च शिक्षणमंत्री चंद्रकांत पाटील आग्रही:11 हजार 87 पदे रिक्त</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/police-bust-chain-snatching-gang-two-held-minor-detained-101740078106456.html</t>
+          <t>https://www.eduvarta.com/Higher-Education-Minister-Chandrakant-Patil-insists-on-the-recruitment-of-professors-11-thousand-87-posts-are-vacant-in-the-state</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Pune: Chandrakant Patil Flags PMC Misgovernance Amid Delayed Elections; High-Level Meeting with Ajit Pawar Likely</t>
+          <t>प्राध्यापक भरती प्रक्रिया लवकर पूर्ण करा; मंत्री चंद्रकांत पाटील यांच्या कुलगुरूंना सूचना</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-chandrakant-patil-flags-pmc-misgovernance-amid-delayed-elections-high-level-meeting-with-ajit-pawar-likely/</t>
+          <t>https://eduvarta.com/Complete-the-professor-recruitment-process-quickly</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Delay In Pune's Equal Water Supply Scheme Sparks Public Discontent; MLA Chandrakant Patil Criticizes PMC</t>
+          <t>Chandrakant Patil</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/delay-in-punes-equal-water-supply-scheme-sparks-public-discontent-mla-chandrakant-patil-criticizes-pmc/</t>
+          <t>https://policenama.com/chandrakant-patil-no-matter-how-much-black-magic-someone-does-it-doesnt-matter-bjp-has-as-many-as-137-mlas-who-is-chandrakant-patal-targeting-so-the-indication-of-bawankules-to-fight-the-upco/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>आता प्राचार्यांची सेवानिवृत्ती ६५ व्या वर्षी हाेणार : ना. चंद्रकांत पाटील यांची घोषणा</t>
+          <t>Chandrakant Patil News | Spontaneous response to the grain festival</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/amravati/now-principals-will-retire-at-the-age-of-65-announcement-by-n-chandrakant-patil-a-a782-c1000/</t>
+          <t>https://policenama.com/chandrakant-patil-news-spontaneous-response-to-the-grain-festival-organized-by-minister-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
+          <t>सहाय्यक प्राध्यापक- शिक्षकेतर कर्मचाऱ्यांच्या भरतीबाबत लवकरच प्रक्रिया-मंत्री चंद्रकांत पाटील</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
+          <t>https://maharashtranews1.com/Assistant-Professor---The-process-regarding-the-recruitment-of-non-teaching-staff-will-be-initiated-soon---Minister-Chandrakant-Patil</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूजचा आढावा एका क्लिकवर</t>
+          <t>मोठी बातमी! मनोज जरांगे पाटील यांनी कागद अन् पेन घेऊन सरकार समोर आरक्षणबाबत चर्चेला बसावं; 'या' मंत्र्याने दिले चर्चेचे निमंत्रण</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-monsoon-alert-ajchya-thalak-batmya-on-august-11-political-news-in-marathi-931306</t>
+          <t>https://mangalwedhatimes.in/manoj-jarange-patil-should-take-paper-and-pen-and-sit-front-of-the-government-to-discuss-reservation-minister-chandrakant-patil-invitation-to-discussion/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Maharashtra News Updates: “ती महिला स्वत:हून पुड्या काढून देत होती”, प्रांजल खेवलकरांच्या वकिलाचा दावा; सगळंच संशयास्पद असल्याचा युक्तिवाद</t>
+          <t>Chandrakant Patil | Philosophy of thinking positively about others in Hindu culture</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-july-pune-rave-party-raj-thackeray-uddhav-thackeray-latest-news-mumbai-konkan-marathwada-weather-report-today-rain-updates-kolhapur-pandharpur-pmw-88-5267001/</t>
+          <t>https://policenama.com/chandrakant-patil-philosophy-of-thinking-positively-about-others-in-hindu-culture-chandrakantdada-patils-assertion/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Pharmacy courses: राज्य सरकारने फार्मसी महाविद्यालये का थांबवली? विद्यार्थ्यांचा ओढा कमी होण्याचे कारण काय?</t>
+          <t>Ashadhi Wari 2025: पंढरीच्या वाटेवर वारकऱ्यांसाठी वारकऱ्यांसाठी 'फिरता दवाखाना'</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-state-government-halts-new-pharmacy-colleges-understand-the-reasons-behind-decreased-demand/articleshow/120842410.cms</t>
+          <t>https://marathi.timesnownews.com/maharashtra/firata-davakhana-for-warkari-state-minister-chandrakant-patil-inaugurated-in-pune-article-152110556</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
+          <t>Bajirao Peshwa Memorials on Parvati Hill</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
+          <t>https://policenama.com/bajirao-peshwa-memorials-on-parvati-hill-development-work-of-bajirao-peshwa-memorial-on-parvati-hill-satisfactory-the-first-phase-will-be-inaugurated-by-union-minister-rajnath-singh-chandrakant-p/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
+          <t>Mumbai University : ८७ अनुकंपा नियुक्त कर्मचाऱ्यांना दिलासा; सेवा नियमित करण्याचा मंत्री चंद्रकांत पाटील यांचा निर्णय</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
+          <t>https://www.marathi.hindusthanpost.com/social/mumbai-university-relief-for-87-compassionately-appointed-employees-minister-chandrakant-patils-decision-to-regularize-services/</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>5 New Police Stations: शहरात होणार नवीन पाच पोलिस ठाणी; मुख्यमंत्र्यांकडून घोषणा</t>
+          <t>“ठाकरे गटाला सत्तेत यायचंय, पण घेत नाहीत”; Chandrakant Patil यांचा घणाघात</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/cm-announces-five-new-police-stations-in-the-city-sb97</t>
+          <t>https://maharashtradesha.com/uddhav-thackerays-party-wants-to-join-the-government-chandrakant-patil-said/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Sangli News | कवठेमहांकाळ येथे जिल्हा व अतिरिक्त सत्रन्यायालयास उच्च न्यायालयाची मंजुरी</t>
+          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-news-high-court-approval-for-district-additional-sessions-judge-kavathemahanaghat-sk95</t>
+          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>'वसंतदादा घराण्यात मुख्यमंत्रिपद, आमदारकी, खासदारकी...', आमच्यावरही असा अन्याय करावा; काँग्रेस नेत्याची जयश्री पाटलांवर उपरोधिक टीका</t>
+          <t>Professors Recruitment: उच्च शिक्षण विभागात मोठी पदभरती; 5500 प्राध्यापक आणि 2900 कर्मचाऱ्यांची भरती होणार</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/prithviraj-patil-slams-jayshree-patil-bjp-entry-congress-reaction-sangli-politics-as11</t>
+          <t>https://marathi.timesnownews.com/maharashtra/big-recruitment-in-the-higher-education-department-of-maharashtra-5500-professors-and-2900-employees-will-be-recruited-article-152339600</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Pune Sinhagad Road flyover: सिंहगड रोड उड्डाणपुलावरून आजपासून वाहतूक सुसाट; अजित पवार यांच्या हस्ते उद्घाटन</t>
+          <t>Anna Bansode elected Dy Speaker, Opp asks Speaker to decide on LoP</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-sinhagad-road-flyover-inauguration-by-ajit-pawar-sb97</t>
+          <t>https://indianexpress.com/article/cities/mumbai/anna-bansode-elected-dy-speaker-opp-asks-speaker-to-decide-on-lop-9907657/</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Sangli : ग्रंथालय वाढीव अनुदानात आमचा हिस्सा किती?</t>
+          <t>Polytechnic Admissions 2025 In Maharashtra: Application Deadline Extended To June 26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/40-percent-hike-in-library-grants-in-maharashtra-dc95</t>
+          <t>https://www.mypunepulse.com/polytechnic-admissions-2025-in-maharashtra-application-deadline-extended-to-june-26/</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Yoga Day: भक्ती आणि योगाच्या माध्यमातून आरोग्यदायी समाज निर्मितीसाठी प्रयत्न करूया; देवेंद्र फडणवीस यांचे आवाहन</t>
+          <t>Pune: Defence Minister Rajnath Singh Likely to Inaugurate Peshwa Memorial at Parvati Hill</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/let-us-strive-to-create-a-healthy-society-through-bhakti-and-yoga-devendra-fadnavis-appeal-sb97</t>
+          <t>https://www.mypunepulse.com/pune-defence-minister-rajnath-singh-likely-to-inaugurate-peshwa-memorial-at-parvati-hill/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Malin Village: दुर्घटनेनंतरही माळीविासीयांना घरांसाठी अडीच वर्षांची प्रतीक्षा; गावकर्‍यांनी अडीच वर्षे काढली पत्राशेडमध्ये</t>
+          <t>Maharashtra Live Update: 'केवळ घरात घुसून मारुन उपयोग नाही तर...'; ओवैसींनी मोदी सरकारला ललकारलं</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/malin-survivors-homeless-after-2-years-sb97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-political-marathi-latest-news-from-maharashtra-1-may-2025-devendra-fadnavis-eknath-shinde-ajit-pawar-bjp-mahayuti-government-sharad-pawar-shivsena-ubt-jammu-kashmir-pahalgam-terror-attack-amit-shah-pm-narendra-modi-mumbai-visit-central-government-approves-caste-based-census</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>सार्वजनिक विद्यापीठे, अशासकीय महाविद्यालयांमधील रिक्तपदांच्या भरतीस वेग येणार, अभियांत्रिकी संस्थांमध्ये 100 टक्के पदभरतीस मान्यता</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/public-universities-recruitment-of-vacancies-in-non-colleges-will-be-accelerated-100-percent-recruitment-in-engineering-institutions-maharashtra-news-mhs25070802041</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-ajchya-thalak-batmya-on-march-05-aajchya-tajya-batmya-pune-mumbai-nagpur-political-news-in-marathi-890636</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>सांगली जिल्हा नियोजन समिती बरखास्त, राज्य शासनाचे आदेश; समिती सदस्यांचा झाला हिरमोड</t>
+          <t>Jayashree Patil - जयश्री पाटील यांचा आज भाजपमध्ये प्रवेश!</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/sangli-district-planning-committee-dissolved-state-government-orders-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/jayashree-patil-joins-bjp-maharashtra-politics-political-entry-news-msr87</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>NEET PG Counselling 2024: मेडिकल कौन्सिल कमिटीकडून 'कट ऑफ पर्सेटाइल'मध्ये घट; ५ पसेंटाइल असणारे 'नीट पीजी'साठी पात्र</t>
+          <t>Maharashtra Live News Today: महाराष्ट्रातील ताज्या घडामोडींचे लाईव्ह अपडेट्स</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/neet-pg-counselling-2024-reduction-in-cut-off-percentile-medical-council-committee-5-percentile-student-qualify/articleshow/118624987.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-breaking-news-live-in-marathi-1-may-2025-maharashtra-din-kamgar-divas-pahalgam-attack-update-pm-modi-cm-devendra-fadnavis-mumbai-pune-latest-updates/liveblog/120781856.cms</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Pune | हडपसरला नवीन मेट्रो मार्गिका, मुख्य शहराशी कनेक्टिव्हिटी मिळणार असल्याने प्रवास होणार वेगवान...</t>
+          <t>Pune Sinhagad Road flyover: सिंहगड रोड उड्डाणपुलावरून आजपासून वाहतूक सुसाट; अजित पवार यांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/pune-or-hadapsar-will-get-a-new-metro-line-connectivity-to-the-main-city-will-make-travel-faster/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-sinhagad-road-flyover-inauguration-by-ajit-pawar-sb97</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Thane News: ठाणे महापालिका क्षेत्रातील विद्यार्थ्यांचे भवितव्य संकटात! ६८ अनधिकृत शाळांविरोधात FIR</t>
+          <t>पुण्याला मिळणार ५ नवीन पोलीस स्टेशन अन् १०० अतिरिक्त पोलीस बळ</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/thane-municipal-corporation-fir-against-68-unauthorized-schools-52-crore-fine/articleshow/118617204.cms</t>
+          <t>https://civicmirror.in/city/pune/big-announcement-for-pune-police-will-get-5-new-police-stations-and-1000-additional-police-force/</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
+          <t>Yoga Day: भक्ती आणि योगाच्या माध्यमातून आरोग्यदायी समाज निर्मितीसाठी प्रयत्न करूया; देवेंद्र फडणवीस यांचे आवाहन</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/let-us-strive-to-create-a-healthy-society-through-bhakti-and-yoga-devendra-fadnavis-appeal-sb97</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Laxman Jagtap: लोकनेते लक्ष्मण जगताप हा प्रेरणादायी अध्याय: उच्च व तंत्र शिक्षणमंत्री चंद्रकांत पाटील</t>
+          <t>शिवसेना उबाठाच्या नाशिकमधील शिबिरात शिवसेना प्रमुख बाळासाहेब ठाकरे यांचे न ऐकलेले भाषण ऐकवणार</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/loknete-laxman-jagtap-is-an-inspiring-chapter-higher-and-technical-education-minister-chandrakant-patil/</t>
+          <t>https://www.tv9marathi.com/maharashtra/shiv-sena-chief-balasaheb-thackeray-unheard-speech-to-be-played-at-shiv-sena-camp-in-nashik-1384444.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
+          <t>Devendra Fadnavis : विद्यापीठे, महाविद्यालयांतील रिक्त पदांची भरती होणार, अभियांत्रिकी संस्थांमध्येही पदभरतीस मान्यता, मुख्यमंत्री फडणवीसांचा निर्णय</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
+          <t>https://www.loksatta.com/maharashtra/recruitment-for-vacant-posts-in-public-universities-and-colleges-100-percent-recruitment-in-engineering-institutes-approved-devendra-fadnavis-decision-gkt-96-5213795/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
+          <t>सरकार शब्द फिरवणार नाही, योग्यवेळी कर्जमाफीचा निर्णय घेणार - मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
+          <t>https://www.etvbharat.com/mr/!state/farmer-loan-waiver-will-be-done-we-will-keep-your-word-assured-cm-devendra-fadnavis-in-pune-yoga-day-2025-maharashtra-news-mhs25062101753</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>राज्यातील ग्रंथालयांसाठी फडणवीस सरकारचा ऐतिहासिक निर्णय : अनुदानात ४०% वाढ</t>
+          <t>Jalgaon Accident: भीषण! एसटी बसचा ब्रेक फेल; नवविवाहित तरुणासह आणखी एकाचा चिरडून मृत्यू, CCTV फुटेज समोर</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/65971/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/jalgaon-news/st-bus-brakes-fail-in-chopda-taluka-newlywed-youth-died-in-accident-cctv-footage/articleshow/121291227.cms</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>राज्याबाहेरील एमएचटी-सीईटी परीक्षा केंद्रे बंद; चूका टाळण्यासाठी समिती, उच्च व शिक्षण मंत्र्यांची घोषणा</t>
+          <t>PMPML: पुणेकरांसाठी खुशखबर! पीएमपीएमएलच्या ताफ्यात लवकरच १००० नव्या बसचा होणार समावेश</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mht-cet-examination-will-be-conducted-in-engineering-colleges-in-maharastra-says-minster-chandrkant-patil-zws-70-5222445/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/good-news-for-punekars-pimpri-chimchwad-to-get-1000-new-buses-will-soon-be-added-to-pmpml-dss02</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
+          <t>10th Exam Result 2025: ... तर दहावीचा निकाल ठेवला जाणार राखीव; नाशिक विभागातील ६६८ शाळांचे काम अद्याप बाकी</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-10th-board-exam-result-2025-ssc-hsc-board-nashik-divisional-office-work-of-668-schools-pending/articleshow/118621538.cms</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
+          <t>School Bus Rules: स्कूलबससाठी नवीन नियमावली येणार; १२ ऐवजी १० महिन्यांचे बस शुल्क आकरण्याची मागणी, वाचा सविस्तर</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
+          <t>https://marathi.indiatimes.com/career/career-news/school-bus-rules-and-regulations-for-student-in-marathi-demand-to-charge-bus-fare-for-10-months-instead-of-12/articleshow/118546648.cms</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>चौंडी येथे होणारी मंत्रिमंडळाची बैठक रद्द, मुंबईतच बैठक होणार चंद्रकांत पाटलांची</t>
+          <t>भयंकर शेवट! दिरानेच केला भावजय व तिच्या मित्राचा खून; 'या' कारणांमुळे घडले मंगळवेढ्यातील दुहेरी हत्याकांड</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/ahmednagar/chaundi-ahilyanagar-cabinet-meeting-cancled-31-may-on-ahilyabai-holkar-300th-jayanti-maharashtra-marathi-news-1356056</t>
+          <t>https://mangalwedhatimes.in/seven-people-murder-woman-a-man-over-a-farming-dispute-incident-in-gunjegaon-two-are-undergoing-treatment-in-a-private-hospital-three-are-in-custody/</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत तीन पाटलांच्या एकत्रित फोटोची चर्चा! आजी माजी खासदार अन् पृथ्वीराज</t>
+          <t>सहाय्यक प्राध्यापक संवर्गातील ५ हजार १२ पदांच्या भरतीस मान्यता</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/mp-vishal-patil-sanjay-patil-and-prithviraj-patil-on-the-same-platform-in-sangli-marathi-news-udpate-1377401</t>
+          <t>https://www.eduvarta.com/Approval-for-recruitment-of-5012-posts-in-the-Assistant-Professor-cadre</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Maharashtra CET Admission 2025: विद्यार्थ्यांसाठी दिलासादायक बातमी! BE/BTech आणि MBA प्रवेशासाठी मुदतवाढ जाहीर</t>
+          <t>MKCL - Devendra Fadnavis | MKCL's Silver Jubilee Foundation Day</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-be-btech-mba-mms-admission-2025-deadline-extended-till-july-14-final-chance/articleshow/122391899.cms</t>
+          <t>https://policenama.com/mkcl-devendra-fadnavis-mkcls-silver-jubilee-foundation-day-celebrated-with-excitement-mkcls-success-in-democratizing-the-information-technology-revolution-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Ramabai Ambedkar Punyatithi 2025: रमाबाई आंबेडकर यांच्या</t>
+          <t>भारतीय राज्यघटनेच्या ७५ व्या वर्षपूर्तीनिमित्त राज्यातील ६ हजार महाविद्यालयांत फेब्रुवारीत ‘संविधान गौरव महोत्सव’</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
+          <t>https://newstown.in/samvidhan-gaurav-mahotsav-in-6-thousand-colleges-in-maharashtra-to-be-held-in-feburary-2025/</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>State may halt admissions to pharmacy colleges flouting norms</t>
+          <t>Maharashtra Guardian Minister : मोठी बातमी ! पालकमंत्र्यांची यादी जाहीर</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-may-halt-admissions-to-pharmacy-colleges-flouting-norms-101753902851567.html</t>
+          <t>https://www.dainikprabhat.com/ig-news-list-of-guardian-ministers-announced/</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
+          <t>Chhaava : छत्रपती संभाजी महाराजांचा 'छावा' फ्रीमध्ये एक लाख नागरिकांना दाखवणार</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
+          <t>https://saamtv.esakal.com/entertainment/chhaava-movie-for-free-to-one-lakh-kothrud-residents-bjp-leader-chandrakant-patil-statement-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Maharashtra: एनसीपी गुटों के विलय पर अटकलें तेज, भाजपा नेता बोले- हकीकत नहीं; शरद गुट से भी आई प्रतिक्रिया</t>
+          <t>राष्ट्र महाराष्ट्र : लाडक्या बहिणींना जे पैसे दिले, ते पुन्हा परत घेणं असा कद्रूपणा करणार नाही - शिंदे</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions-news-in-hindi-2025-05-14</t>
+          <t>https://www.bbc.com/marathi/live/c3e4qkvvdkvt</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
+          <t>Ramabai Ambedkar Punyatithi 2025: रमाबाई आंबेडकर यांच्या</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
+          <t>https://marathi.latestly.com/socially/maharashtra/ramabai-ambedkar-punyatithi-2025-ajit-pawar-to-prakash-ambedkar-pays-tribute-to-ramai-on-her-death-anniversary-590799.html</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
+          <t>Maharashtra: एनसीपी गुटों के विलय पर अटकलें तेज, भाजपा नेता बोले- हकीकत नहीं; शरद गुट से भी आई प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
+          <t>https://www.amarujala.com/india-news/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions-news-in-hindi-2025-05-14</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
+          <t>उद्धव ठाकरे IN, एकनाथ शिंदे OUT? फडणवीस की सफाई के बाद भी क्यों महाराष्ट्र में चर्चे</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
+          <t>https://www.livehindustan.com/maharashtra/uddhav-in-shinde-out-bjp-is-cooking-up-a-new-plan-in-maharashtra-chandrakant-patil-met-uddhav-201738301481336.html</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Free education: मुलींना मोफत उच्च शिक्षण योजनेची प्रभावी अंमलबजावणी करा, मंत्र्यांनी दिले थेट आदेश</t>
+          <t>हिरासत में लिए गए विधायक चंद्रकांत पाटिल, किसानों के साथ हाईवे पर कर रहे थे प्रदर्शन</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/effectively-implement-the-free-higher-education-scheme-for-girls-orders-chandrakant-patil-8702210</t>
+          <t>https://www.aajtak.in/india/news/video/mla-chandrakant-patil-in-custody-protest-on-the-highway-with-farmers-ytvd-2293913-2025-07-23</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
+          <t>CM approves long-pending faculty recruitment for state universities, colleges</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/cm-approves-long-pending-faculty-recruitment-for-state-universities-colleges-101751916450665.html</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
+          <t>Maharashtra News Highlights: ‘हिंदी हवी कशाला?’ उद्धव ठाकरेंनी मुख्यमंत्री देवेंद्र फडणवीस यांना भेट दिलं पुस्तक</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-17-july-maharashtra-assembly-monsoon-session-2025-devendra-fadnavis-on-tri-bhasha-sutra-ola-uber-rickshaw-taxis-closed-rak-94-5234478/</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
+          <t>Maharashtra News Highlights: ‘उशिरा का होईना पण शहाणपण आलं’, हिंदी भाषेची सक्ती मागे घेतल्यानंतर राज ठाकरेंची प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-breaking-news-live-updates-marathwada-farmers-death-shirish-valsangkar-suscide-case-raj-thackeray-uddhav-thackeray-alliance-gold-price-today-22-april-2025-asc-95-5037779/</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
+          <t>अखेर सरकार नरमले; हिंदी सक्तीविरोधातील दोन्ही शासन निर्णय रद्द - मुख्यमंत्र्यांची घोषणा</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/hindi-imposition-maharashtra-policy-withdrawn</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>हिंदी सक्तीविरोधात राज ठाकरे-उद्धव ठाकरेंचा एकत्र मोर्चा, मामा चंद्रकांत वैद्य यांची पहिली...</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-imposition-protest-uddhav-thackeray-and-raj-thackeray-unite-massive-rally-against-mama-chandrakant-vaidya-reaction-1432755.html</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
+          <t>Maharashtra Politics Live: सहा तारखेला कोण, कोण येणार, याची मी वाट पाहतोय, सर्वपक्षीय नेत्यांना राज ठाकरेंचे आवाहन</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/breaking-news-maharashtra-politics-26-june-2025-sharad-pawar-cm-devendra-fadnavis-ajit-pawar-eknath-shinde-bjp-mahayuti-mahavikas-aaghadi-local-body-election-mm76</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
+          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
+          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Hindi Controversy | मराठी भाषा व संस्कृती संपवण्यासाठीच हिंदीची सक्ती, भाजपा व आरएसएसचा हा अजेंडा हाणून पाडू - हर्षवर्धन सपकाळ</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/hindi-is-being-forced-to-end-marathi-language-and-culture-we-will-defeat-this-agenda-of-bjp-and-rss-harshvardhan-sapkal/</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
+          <t>Mumbai Dam Water Level: मुंबईकरांना पाणीदिलासा! सातही धरणांत ५० टक्क्यांहून अधिक भर, कोणत्या धरणात किती पाणी?</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/water-storage-in-seven-dams-supplying-water-to-mumbai-reaches-50-percent/articleshow/122265724.cms</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
+          <t>Uday Samant : राज्यात हिंदी सक्ती धोरण उद्धव ठाकरेंनी स्वीकारले मंत्री उदय सामंत यांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
+          <t>https://civicmirror.in/news/uddhav-thackeray-has-accepted-the-hindi-mandatory-policy-in-the-state-reveals-minister-uday-samant/</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
+          <t>Raj Thackeray : "या मोर्चाला कोणताही पक्षीय झेंडा नसेल. फक्त 'मराठी'..," राज ठाकरेंची हिंदी सक्तीविरोधात भव्य मोर्चाची घोषणा</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
+          <t>https://civicmirror.in/news/raj-thackeray-announces-grand-march-against-hindi-compulsion/</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Did BJP Minister Just Confirm Rift Within Mahayuti? Shindes Meeting With Shah...</t>
+          <t>Pune News | पुणे फेस्टिव्हल २९ ऑगस्टला होणार सुरू ; राज्यपालांच्या हस्ते उद्घाटन</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/maharashtra-politics-did-bjp-minister-just-confirm-rift-within-mahayuti-shindes-meeting-with-shah-2886410.html</t>
+          <t>https://www.dainikprabhat.com/pune-news-pune-festival-to-begin-on-august-29-inauguration-by-governor/</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Ahilyadevi Holkar’s legacy must be known to youth: CM</t>
+          <t>Mere speculation: Chandrakant Patil on rumours about likely merger of NCP factions</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/mere-speculation-chandrakant-patil-on-rumours-about-likely-merger-of-ncp-factions/article69575055.ece</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
+          <t>Ahilyadevi Holkar’s legacy must be known to youth: CM</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/ahilyadevi-holkar-s-legacy-must-be-known-to-youth-cm-101748631369699.html</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
+          <t>‘Dead bodies, debris’: Eyewitness recalls hearing ‘massive sound’ during Air India plane crash | Trending - Hindustan Times</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
+          <t>https://www.hindustantimes.com/trending/dead-bodies-debris-eyewitness-recalls-hearing-massive-sound-during-air-india-plane-crash-101749723280168.html</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
+          <t>Pregnant woman’s dad accuses spouse, kin of harassment</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/pregnant-womans-dad-accuses-spouse-kin-of-harassment/articleshow/121809105.cms</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
+          <t>Maharashtra to seek restoration of Savarkar’s barrister degree</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/maharashtra-to-seek-restoration-of-savarkar-s-barrister-degree-101748373138133.html</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>'If anything happens to me...':Abu Azmi responds after suspension over Aurangzeb remarks</t>
+          <t>Days before HSC exam, 70 students get hall tickets with wrong subjects</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://english.mathrubhumi.com/news/india/abu-azmi-suspended-maharashtra-assembly-aurangzeb-42dc0e0b</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/days-before-hsc-exam-70-students-get-hall-tickets-with-wrong-subjects/articleshow/118097108.cms</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
+          <t>Maharashtra launches 'ATAL' portal for entrance prep and career guidance</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
+          <t>https://timesofindia.indiatimes.com/education/news/maharashtra-launches-atal-portal-for-entrance-prep-and-career-guidance/articleshow/117296155.cms</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
+          <t>'If anything happens to me...':Abu Azmi responds after suspension over Aurangzeb remarks</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
+          <t>https://english.mathrubhumi.com/news/india/abu-azmi-suspended-maharashtra-assembly-aurangzeb-42dc0e0b</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Buldhana Shock: Doctor Dies After Setting Himself on Fire, Motive Still a Mystery</t>
+          <t>India Emerging as Global Knowledge Partner: Dharmendra Pradhan</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/buldhana-shock-doctor-dies-after-setting-himself-on-fire-motive-still-a-mystery-a525/</t>
+          <t>https://www.newsonair.gov.in/india-emerging-as-global-knowledge-partner-dharmendra-pradhan/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
+          <t>MHT CET PCM re-test 2025 on May 5 for 27,837 candidates after 21 maths questions go wrong</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163883/</t>
+          <t>https://news.careers360.com/mht-cet-pcm-re-test-2025-may-5-for-27837-english-urdu-marathi-21-maths-questions-go-wrong-paper-setters-blacklisted</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
+          <t>Millennium National School shines at Invitational Taekwondo Inter-School Competition</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
+          <t>https://www.punekarnews.in/millennium-national-school-shines-at-invitational-taekwondo-inter-school-competition/</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
+          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
+          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>RTE News : ‘या’ कारणामुळे खासगी इंग्रजी माध्यम शाळा प्रवेश प्रक्रियेवर बहिष्काराच्या तयारी</t>
+          <t>डॉ. बाबासाहेब आंबेडकर यांच्या जनता वृत्तपत्राच्या तीन खंडाचे मुख्यमंत्री देवेंद्र फडणवीस यांच्या हस्ते प्रकाशन</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/news/rte-news-preparations-to-boycott-private-english-medium-school-admission-process-due-to-this-reason/</t>
+          <t>https://mahasamvad.in/163883/</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Patankar and Patil join BJP as strong rivals of sitting Sena MLAs</t>
+          <t>मोठी बातमी! MHT-CET 2025 पीसीएम गटाची फेर परीक्षा; 'या' दिवशी होणार पेपर, सीईटी सेलची माहिती</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/patankar-and-patil-join-bjp-as-strong-rivals-of-sitting-sena-mlas/articleshow/121762155.cms</t>
+          <t>https://marathi.indiatimes.com/career/career-news/mht-cet-2025-pcm-group-re-exam-on-may-5-exam-canceled-due-to-technical-errors-conducted-on-27-april/articleshow/120769046.cms</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>BJP mantri’s remark sparks buzz of patch-up with Shiv Sena UBT</t>
+          <t>MHT CET Exam 2025 | एमएचटी-सीईटी २०२५ पीसीएम गटाच्या परीक्षेत तांत्रिक त्रुटी; ५ मे रोजी फेर परीक्षा होणार....</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
+          <t>https://civicmirror.in/maharashtra/mht-cet-exam-2025-or-technical-glitch-in-mht-cet-2025-pcm-group-exam-re-exam-on-may-5th/cid1746067306.htm</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Sanjay Raut claims 'some in BJP' want alliance with Uddhav Sena, Fadnavis retorts</t>
+          <t>MHT-CET 2025: एमएचटी-सीईटी 2025 पुन्हा होणार; 21 प्रश्नांमध्ये तांत्रिक त्रुटी, 5 मे रोजी फेर परीक्षा जाहीर</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/sanjay-raut-bjp-shiv-sena-ubt-alliance-maharashtra-mahayuti-mva-devendra-fadnavis-2672702-2025-01-31</t>
+          <t>https://marathi.timesnownews.com/maharashtra/mht-cet-2025-reexam-announces-for-pcm-on-may-5-due-to-errors-in-21-questions-read-details-in-marathi-article-151540811</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>BJP MLC first to record statement in CM’s SIT probe</t>
+          <t>BJP mantri’s remark sparks buzz of patch-up with Shiv Sena UBT</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
+          <t>https://timesofindia.indiatimes.com/india/bjp-mantris-remark-sparks-buzz-of-patch-up-with-shiv-sena-ubt/articleshow/117754765.cms</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>BJP leaders conduct back-to-back separate review meetings at PMC; Oppn questions lack of results</t>
+          <t>BJP MLC first to record statement in CM’s SIT probe</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/bjp-leaders-conduct-back-to-back-separate-review-meetings-at-pmc-oppn-questions-lack-of-results-101751143694920.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-mlc-first-to-record-statement-in-cm-s-sit-probe-101740079847054.html</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
+          <t>BJP district rural unit president elected in Kalaburagi</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
+          <t>https://www.thehindu.com/news/national/karnataka/bjp-district-rural-unit-president-elected-in-kalaburagi/article69155570.ece</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
+          <t>BJP leader's statement on Raj Thackeray, 'Like one who predicts...'?</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
+          <t>https://www.indiaherald.com/Politics/Read/994827843/BJP-leaders-statement-on-Raj-Thackeray-Like-one-who-predicts</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
+          <t>Radhakrishna Vikhe Patil Appointed Chairman Of Cabinet Panel On Maratha Community Issues</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
+          <t>https://www.freepressjournal.in/mumbai/radhakrishna-vikhe-patil-appointed-chairman-of-cabinet-panel-on-maratha-community-issues</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>पृथ्वीराज पाटील यांचा भाजप प्रवेश टाळला</t>
+          <t>Vishal Patil : सांगलीत काँग्रेसला मोठा धक्का; विशाल पाटलांना लागले मंत्रि‍पदाचे वेध; भाजप प्रवेशाबद्दल सूचक विधान</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/independent-sangli-mp-vishal-patil-hints-at-leaving-congress-fueling-speculation-about-joining-bjp-as11</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Jayant Patil Politics : विशाल पाटलांना येणाऱ्या ऑफरवर जयंत पाटलांची गुगली; म्हणाले, 'ते अपक्ष, त्यांनीच...'</t>
+          <t>Jayant Patil : 'भाजप पायघड्या घालतोच, पण लोकांनाही...'; जयश्री पाटलांच्या प्रवेशानंतर जयंत पाटलांची खरमरीत टीका</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-jayant-patil-on-mp-vishal-patil-bjp-offer-says-he-should-decide-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ncp-sp-leader-jayant-patil-criticizes-bjp-over-defection-of-sanglis-congress-rebel-jayshree-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Jayashree Patil - जयश्री पाटील यांचा आज भाजपमध्ये प्रवेश!</t>
+          <t>Vaibhav Patil : आजोबांनी दाखवली निष्ठा, नातवाने दिला धक्का...; वैभव पाटलांचा राष्ट्रवादीच्या वर्धापनदिनीच भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/jayashree-patil-joins-bjp-maharashtra-politics-political-entry-news-msr87</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/former-vita-chief-vaibhav-patil-joins-bjp-setback-for-ncp-sharad-pawar-and-eknath-shinde-shivsena-also-jayant-patil-as11</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>काँग्रेसचे पृथ्वीराज पाटील यांचा भाजप प्रवेश निश्चित</t>
+          <t>NCP-BJP Political War : प्रवेश केलेले तीन आमदार राष्ट्रवादीसाठी बूस्टर, मात्र अजितदादांचा खरा धक्का कोणाला? भाजप की शरद पवारांना</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/congress-prithviraj-patil-to-join-bjp-dc95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/three-former-mlas-joining-ncp-causing-political-setback-for-bjp-and-sharad-pawar-group-in-maharashtra-2025-as11</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>काँग्रेसचे सहयोगी खासदार पाटलांना भाजप प्रवेशाची खुली ऑफर</t>
+          <t>पृथ्वीराज पाटील यांचा भाजप प्रवेश टाळला</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/congress-mp-vishal-patil-entry-to-bjp-offers-sangli-news-amy-95-4953086/</t>
+          <t>https://www.tarunbharat.com/prithviraj-patil-avoided-joining-the-bjp/</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Sangli: वसंतदादा पाटील यांच्या नातसून जयश्रीताई पाटील भाजपमध्ये, अजितदादांना शह</t>
+          <t>Maharashtra Politic's : वर्धापनदिनीच शरद पवारांच्या राष्ट्रवादीला मोठे धक्के; बालेकिल्ल्यातील दोन युवा शिलेदार भाजपने फोडले</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/former-chief-minister-vasantdada-patil-granddaughter-jayashreetai-patil-will-join-bjp-a-a746/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sharad-pawars-ncps-satyajitsinh-patankar-and-vaibhav-patil-join-bjp-vd83</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>काँग्रेसचे पृथ्वीराज पाटील यांचा भाजप प्रवेश निश्चित</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/sangali/congress-prithviraj-patil-to-join-bjp-dc95</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A128"/>
+  <dimension ref="A1:A165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,889 +438,1148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
+          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-directs-universities-to-hire-contractual-professors-after-drop-in-nirf-rankings-101757788998645.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/amp/story/pune/kothrud-free-shuttle-bus-metro-connectivity-launch</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bes24-mh-chandrakant-patil.amp.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-onion-farmers-launch-seven-day-phone-strike-over-crashing-prices/article70043030.ece/amp/</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362-amp.html</t>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026?amp</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/naredco-mahi-launches-pune-chapter-at-pune-growth-conclave-2025/</t>
+          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/cm-dy-cms-to-clarify-bhujbal-doubts-on-ordinance-chandrakant-patil-ocd-94-5366686/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/even-though-mp-vishal-patil-is-growing-close-to-bjp-he-is-not-in-a-position-where-bjp-wants-him-minister-chandrakant-patil-a-a746/</t>
+          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts?amp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178164/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/government-to-release-kunbi-records-white-paper-guardian-minister-chandrakant-patil-sk95</t>
+          <t>https://www.ptinews.com/story/national/india-targets-5-pc-share-in-global-shipbuilding-market-by-2030-minister/2916379</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/chandrakant-patil-highlighted-need-to-create-5-to-6-hour-work-modules-for-women-and-provide-employment-to-more-women-1492175.html</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/pune/minister-chandrakant-patil-has-inspected-and-reviewed-the-swargate-metro-station-989157.html</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-urges-efforts-to-ensure-mahayuti-mayor-sdj87</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7%E0%A4%95-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/vi-AA1MAx0W?ocid=hpmsn</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/ajinkya-dilip-patil-demands-chandrakant-patil-to-be-the-chairman-of-maratha-sub-committee/videoshow/123844027.cms</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/short-videos/trending/chandrakant-patil-new-gr-on-maratha-reservation-shocks-obcs-chandrakant-patil-spoke-directly-n18s-1074225.html</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/provide-funding-for-the-coep-organization-chief-minister-devendra-fadnavis-assured-chandrakant-patil/939239</t>
+          <t>https://mahasamvad.in/179160/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/special-bus-service-from-home-to-metro-station-has-been-started-for-kothrudkars-989714.html</t>
+          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
+          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178123/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-met-vice-chancellors-to-address-criticism-over-states-educational-decline-pune-print-news-sud-02-5367659/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-assures-to-follow-up-at-the-ministerial-level-135978085.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chandrakant-patil-suggests-contract-professors-in-universities-mumbai-print-news-ocd-94-5368741/</t>
+          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maratha-vs-obc-conflict-over-hyderabad-gazette-chandrakant-patil-advises-jarange-to-focus-on-implementation-assures-chhagan-bhujbals-concerns-will-be-addressed-as11</t>
+          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AA%E0%A5%8D%E0%A4%B0-%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A4%95%E0%A4%B9-%E0%A4%95%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9F-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%A4-%E0%A4%A4%E0%A5%8D%E0%A4%AA%E0%A5%81%E0%A4%B0%E0%A4%A4-%E0%A4%89%E0%A4%A4-%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B0%E0%A5%8D%E0%A4%A5%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AD%E0%A4%B5-%E0%A4%B7%E0%A5%8D%E0%A4%AF-%E0%A4%B5%E0%A4%B0-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8%E0%A4%9A-%E0%A4%A8%E0%A5%8D%E0%A4%B9/ar-AA1MsMTN</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-contractual-assistant-professor-bharti-2025-nirf-ranking-higher-education-minister-chandrakant-patil/articleshow/123864684.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A4%AE%E0%A4%B9-%E0%A4%AA-%E0%A4%B2-%E0%A4%95%E0%A5%87%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%89%E0%A4%AE%E0%A5%87%E0%A4%A6%E0%A4%B5-%E0%A4%B0-%E0%A4%B8-%E0%A4%A0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%9C%E0%A4%A8-%E0%A4%85%E0%A4%B8%E0%A4%A3-%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%87%E0%A4%9A%E0%A5%8D%E0%A4%9B%E0%A5%81%E0%A4%95-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AB%E0%A5%87%E0%A4%B1%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%A2%E0%A4%B2%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%B9-%E0%A4%95-%E0%A4%A3/ar-AA1MacYV</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-manoj-jarange-demands-accepted-patil-advice-implementation-135893272.html</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/manoj-jarange-ultimatum-maratha-subcommittee-radhakrishna-vikhe-patil-action-dk88</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/pune-news-%E0%A4%AA%E0%A5%81%E0%A4%A3%E0%A5%87%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%AB%E0%A4%A4-%E0%A4%AC%E0%A4%B8-%E0%A4%B8%E0%A5%87%E0%A4%B5-%E0%A4%95%E0%A5%81%E0%A4%A0%E0%A5%82%E0%A4%A8-%E0%A4%95%E0%A5%81%E0%A4%A0%E0%A5%87-%E0%A4%A7-%E0%A4%B5%E0%A4%A3-%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%9F%E0%A5%87%E0%A4%B6%E0%A4%A8%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A4%B0-%E0%A4%AA%E0%A4%B0%E0%A5%8D%E0%A4%AF%E0%A4%82%E0%A4%A4-%E0%A4%AA%E0%A5%88%E0%A4%B6-%E0%A4%82%E0%A4%B8%E0%A4%B9-%E0%A4%B5%E0%A5%87%E0%A4%B3%E0%A5%87%E0%A4%9A-%E0%A4%B9-%E0%A4%AC%E0%A4%9A%E0%A4%A4-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0/ar-AA1Mv10g</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maratha-reservation-fadnavis-statement-reservation-not-to-anyone-in-general-but-to-marathas-who-have-a-valid-proof-of-kunbi</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjp-minister-jaykumar-gore-targets-sangli-politics-by-offering-bjp-entry-to-jayant-patil-vishal-patil-and-haridas-patil-as11</t>
+          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/when-maratha-people-will-get-kunbi-certificate-minister-radhakrishna-vikhe-patil-give-detail-information-1488592.html</t>
+          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/satara-gazetteer-report-divisional-commissioner-sk95</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/state-government-gets-a-jolt-from-jarange-patil-vikhe-patil-increases-work-activities-985044.html</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/amp/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maratha-reservation-gr-will-not-be-withdrawn-vikhe-patil-rat16</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/pune/latest-marathi-news-punekar-get-free-bus-transportation-from-station-to-home-convenient-and-cost-effective-local18-1479628.html</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/police-seized-rs-15-lakh-marijuana-hidden-in-maize-crop-in-bastawade-tasgaon-sud-02-5371243/</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/pune-free-shuttle-bus-service-to-metro-station-in-kothrud/articleshow/123877790.cms</t>
+          <t>https://www.msn.com/mr-in/lifestyle/topstories/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1x59Ez?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/states-higher-technical-education-rules-for-hourly-paid-chb-professors-not-being-followed-at-university-level-pune-print-news-sud-02-5367753/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/onion-growers-launch-phone-karo-movement-to-demand-price-hike-sai29</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/pune-free-bus-service-from-station-to-home-started-where-to-go-from-and-where-read-in-detail/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/maharashtra/mumbai/maharashtra-karnataka-border-issue-review-every-three-months-ap84</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/shortage-of-professor-posts-in-the-state-candidates-will-be-filled-on-contract-basis-989409.html/amp</t>
+          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/amp/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/premier/naam-foundation-celebrates-its-10th-anniversary-in-presence-of-minitster-nitin-gadkari-entertainment-news-kds07</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://pudhari.news/amp/story/belgaon/pressure-on-karnataka-border-dispute-ma-youth-committee-expert-meeting-demand-sp96</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/big-relief-for-students-submit-income-certificate-once-to-get-full-scholarship-till-all-education-rm96</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/if-water-is-planned-properly-there-will-be-no-time-for-farmers-to-commit-suicide-nitin-gadkari-a-a941/amp/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/camp-organized-at-kochur-on-the-occasion-of-a-chandrakant-patils-birthday/</t>
+          <t>https://www.esakal.com/maharashtra/income-certificate-to-be-issued-once-minister-directs-simplification-of-scholarship-process-mla-chandrakant-patil-pjp78</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/government-will-issue-a-white-paper-on-kunbi-registration-minister-patils-statement/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://policenama.com/swargate-metro-station-swargate-metro-station-will-become-a-multimodal-hub-for-punekars-for-travel-as-well-as-corporate-in-the-future-chandrakantdada-patil-has-confidence/</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/at-muktainagar-a-chandrakantbhau-patil-was-showered-with-good-wishes-a-crowd-of-workers-came-to-wish-him/</t>
+          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-free-bus-service-from-home-to-metro-station-started-in-kothrud-know-the-schedule-and-route/</t>
+          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/jalgaon/news/demand-for-200-crores-for-deepening-drains-and-protective-walls-in-the-affected-areas-inspection-by-guardian-minister-gulabrao-patil-and-minister-savkare-135956811.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://vishwanewsmarathi.com/now-implement-kolhapur-gazetteer-immediately-maratha-community-demands/</t>
+          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Scholarship-distribution-on-auto-system.html</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/pune/minister-chandrakant-patil-has-inspected-and-reviewed-the-swargate-metro-station-989157.html/amp</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/special-bus-service-from-home-to-metro-station-has-been-started-for-kothrudkars-989714.html/amp</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891/amp</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/amp/pune/latest-marathi-news-punekar-get-free-bus-transportation-from-station-to-home-convenient-and-cost-effective-local18-1479628.html</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/medical-colleges-to-be-opened-under-private-universities-after-maharashtra-amend-law-mumbai-print-news-zws-70-5366366/</t>
+          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-cctv-surveillance-on-dark-spots-soon-dc95</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/593-new-colleges-in-maharashtra-major-announcement-by-chief-minister-devendra-fadnavis/articleshow/123815581.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473/amp</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/after-mla-sudhir-mungantiwar-effort-proposal-of-rs-414-74-crores-for-gondwana-university-sub-center-in-chandrapur-zws-70-5370222/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379/amp</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477/amp</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/gang-war-in-kolhapur-youth-kills-23-year-old-mahesh-rakh-shocking-facts-from-cctv-footage/articleshow/123865866.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1L2jvO?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://jalgaonlive.news/driver-killed-on-the-spot-after-tractor-overturns-122846/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/three-men-sitting-in-a-rickshaw-stole-cash-from-a-passengers-pocket/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/silent-treatment-during-ganesh-immersion-sparks-speculation-of-friendly-contest-between-bjp-ncp-in-civic-polls-101757359369693.html</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178464/</t>
+          <t>https://saamtv.esakal.com/amp/story/national-international/uttar-pradesh-gorakhpur-crime-wife-caught-her-husband-red-handed-with-his-girlfriend-in-a-hotel-bdk97</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/actor-nana-patekar-expressed-a-bold-opinion-on-asia-cup-2025-india-vs-pakistan-match-maharashtra-news-mhs25091402934</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/minister-chandrakant-patil-met-vice-chancellors-to-address-criticism-over-states-educational-decline-pune-print-news-sud-02-5367659/lite/</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://news24pune.com/ai-and-quantum-computing-are-big-opportunities-for-india/</t>
+          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/mumbai/news/st-will-recruit-17450-drivers-and-assistants-8000-new-buses-will-come-into-passenger-service-135973498.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/chandrakant-patil-highlighted-need-to-create-5-to-6-hour-work-modules-for-women-and-provide-employment-to-more-women-1492175.html/amp</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/maratha-reservation-%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B2-%E0%A4%95%E0%A5%81%E0%A4%A3%E0%A4%AC-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%A3%E0%A4%AA%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%95%E0%A4%A7-%E0%A4%AA-%E0%A4%B8%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B5-%E0%A4%96%E0%A5%87-%E0%A4%AA-%E0%A4%9F%E0%A4%B2-%E0%A4%82%E0%A4%A8-%E0%A4%B8%E0%A4%97%E0%A4%B3%E0%A4%82-%E0%A4%B8-%E0%A4%82%E0%A4%97-%E0%A4%A4%E0%A4%B2%E0%A4%82-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87/ar-AA1Mc2LQ</t>
+          <t>https://saamtv.esakal.com/amp/story/sports/shahid-afridi-irfan-pathan-2006-pakistan-tour-dog-meat-remark-controversy-cricket-feud-ind-vs-pak-viral-video-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/todays-top-political-news-maratha-reservation-controversy-hyderabad-gazette-manoj-jarange-warn-chhagan-bhujbal-sdp-92-5361359/</t>
+          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/breaking-news-11-september-2025-marathi-news-solapur-govind-barge-case-pune-mumbai-monsoon-2025-maharashtra-latest-updates/liveblog/123820930.cms</t>
+          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-preparation-for-pune-graduate-constituency-election-print-politics-mews-asj-82-5360333/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500/amp</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mahadevi-madhuri-elephant-rehabilitation-important-hearing-held-in-supreme-court/articleshow/123849295.cms</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/lite/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/savitribai-phule-pune-university-vacancy-of-238-professors-sppu-nirf-ranking-2025-down/articleshow/123844742.cms</t>
+          <t>https://sarkarnama.esakal.com/amp/story/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/82-minor-girls-returned-to-their-parents-under-operation-muskan-in-ahilyanagar-ssb-93-5366771/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630/amp</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/amp/maharashtra/marathi-musician-and-actor-srinath-mhatre-worked-as-additional-background-music-composer-in-jolly-llb-3-local18-1478471.html</t>
+          <t>https://sarkarnama.esakal.com/amp/story/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/permission-for-private-universities-to-offer-medical-education-in-maharashtra-invest-seize-the-opportunity/articleshow/123842558.cms</t>
+          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/pune/todays-latest-district-marathi-news-ind25b03579-txt-pd-today-20250909112309</t>
+          <t>https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/entertainment/nana-patekar-and-makrand-anaspure-naam-foundation-decade-long-journey-of-social-service-naam-foundation-celebrated-its-decade-anniversary-svk01</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://news24pune.com/renowned-writer-vishwas-patil-elected-as-the-president-of-the-99th-all-india-marathi-literary-conference/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/fine-collection-megha-engineering-issue-bjp-mla-demand-ssb-93-5366746/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%B5%E0%A4%BF%E0%A4%B0%E0%A5%8B%E0%A4%A7%E0%A4%95%E0%A4%BE%E0%A4%82%E0%A4%A8%E0%A4%BE-%E0%A4%AA%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%BE%E0%A4%A4-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%A4/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/pune/kothrud-free-shuttle-bus-metro-connectivity-launch</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/government-renames-ideal-state-teacher-award-after-renowned-educationist-dr-j-p-naik-101757443983298.html</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-cm-fadnavis-stresses-autonomy-for-higher-education-institutions-at-coep-event/</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/navratri-festival-extra-msrtc-buses-to-saptashrungi-gad-msrtc-to-run-additional-buses-bbj88</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178050/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077/amp</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chandrakant-patil-suggests-contract-professors-in-universities-mumbai-print-news-ocd-94-5368741/lite/</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/kurla/mumbai-sub-discussion-on-important-issue-related-to-border-question-15377439</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i33850-txt-mumbai-20250910034135</t>
+          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/cm-devendra-fadnavis-directs-to-prepare-a-format-for-scholarship-distribution-on-auto-system/</t>
+          <t>https://navbharatlive.com/career/maharashtra-university-college-professor-recruitment-chandrakant-patil-1361015.html/amp</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Professors-in-the-state-will-protest-in-front-of-the-Directorate-of-Higher-Education-from-tomorrow</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/sangli/an-attempt-to-teach-robotics-guardian-minister-of-sangli-chandrakant-patil-expressed-his-opinion-a-a746/</t>
+          <t>https://www.ibc24.in/youth-corner/assistant-professor-recruitment-maharashtra-2026-5500-vacancies-apply-before-march-3261341.html/amp</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i33850-txt-mumbai-20250910034135</t>
+          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html/amp</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/rising-demand-for-foreign-students-in-engineering-colleges-in-maharashtra-special-preference-for-coep/articleshow/123827313.cms</t>
+          <t>https://www.patrika.com/amp/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/new-colleges-in-maharashtra-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A5%AB%E0%A5%AF%E0%A5%A9-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF%E0%A5%87-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A5%82%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1Mjk3m?cvid=cb3b3cbb29134e49acf9060e129ca2a8</t>
+          <t>https://news.careers360.com/karnataka-sslc-puc-2-time-table-2026-out-on-kseab-karnataka-gov-in-submit-objections-october-9-class-10-12-exam/amp</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://chandablast.com/?p=50179</t>
+          <t>https://www.newsdrum.in/national/5500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-10483604</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chief-Minister-Devendra-Fadnavis-big-announcement-on-professor-recruitment</t>
+          <t>https://www.hindustantimes.com/cities/chandigarh-news/inld-and-jjp-both-proxies-of-the-bjp-haryana-ex-cm-hooda-101758134956254.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pune-news-educational-institutions-will-be-autonomous-but-within-the-framework-of-rules-chief-minister-fadnavis/</t>
+          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/advanced-technology-and-agro-industries-key-to-preventing-farmer-suicides-gadkari/</t>
+          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/shortage-of-professor-posts-in-the-state-candidates-will-be-filled-on-contract-basis-989409.html</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/shivendraraje-makarand-patle-discuss-satara-gazetteer-with-pune-commissioner-sk95</t>
+          <t>https://www.lokmat.com/topics/election/page/1537/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/amp/en/!entertainment/nana-patekar-speaks-against-india-pak-asia-cup-clash-enn25091403520</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B8%E0%A4%BE%E0%A4%A4%E0%A4%BE%E0%A4%B0%E0%A4%BE-%E0%A4%97%E0%A5%85%E0%A4%9D%E0%A5%87%E0%A4%9F%E0%A5%8D%E0%A4%B8%E0%A4%B8%E0%A4%BE%E0%A4%A0%E0%A5%80-%E0%A4%B9%E0%A4%BE%E0%A4%B2%E0%A4%9A%E0%A4%BE/116591/</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/cash-crops-boosted-the-economy-article-on-agrowon-rat16</t>
+          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/coep-tech-to-celebrate-engineer-s-day-101757702158316.html</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/former-mp-chandrakant-khaire-reacted-on-raj-thackeray-and-uddhav-thackeray-coming-together-maharashtra-news-mhs25091004180</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/amp_articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/why-is-only-devendra-fadnavis-targeted-among-the-12-maratha-chief-ministers-of-maharashtra-questions-on-the-minds-of-maharashtra-on-the-banner-of-vaijapur-284041/</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/cm-devendra-fadnavis-coep-college-150-year-old-library-relocated-in-new-building-pune-print-news-css-98-5369379/</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/medical-study-in-maharashtra-%E0%A4%B5%E0%A5%88%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%95-%E0%A4%AF%E0%A4%9A-%E0%A4%B5-%E0%A4%9F-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%96-%E0%A4%B8%E0%A4%97-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%AA-%E0%A4%A0-%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%B5%E0%A5%88%E0%A4%A6%E0%A5%8D%E0%A4%AF%E0%A4%95-%E0%A4%AF-%E0%A4%85%E0%A4%AD%E0%A5%8D%E0%A4%AF-%E0%A4%B8%E0%A4%95%E0%A5%8D%E0%A4%B0%E0%A4%AE-%E0%A4%82%E0%A4%9A-%E0%A4%AA%E0%A4%B0%E0%A4%B5-%E0%A4%A8%E0%A4%97/ar-AA1MoE4b</t>
+          <t>https://www.ptinews.com/detail/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l38309-txt-pune-today-20250913015857</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/gunaratna-sadavarte-demands-resignation-of-minister-radhakrishna-vikhe-patil-reason-revealed-dk88</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/maratha-reservation-good-news-for-western-maharashtra-minister-shivendraraje-bhosale-meeting-with-pune-divisional-commissioner/articleshow/123864953.cms</t>
+          <t>https://navbharatlive.com/career/maharashtra-university-college-professor-recruitment-chandrakant-patil-1361015.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://pudhari.news/sampadakiy/almatti-water-dispute-karnataka-obstructs-maharashtra-development-sp96</t>
+          <t>https://jantaserishta.com/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://news24pune.com/fadnavis-challenges-the-opposition-to-an-open-debate/</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/--You-say-Mahayuti-is-in-power-in-Gokul--why-is-there-no-photo-of-any-BJP-leader-from-the-district-in-the-report---Shoumika-Mahadik</t>
+          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://newstown.in/auto-system-will-be-introduced-for-scholarship-distribution-on-the-line-of-salary-distribution-system-for-government-employees/</t>
+          <t>https://www.devdiscourse.com/article/education/3633620-bengaluru-skill-summit-2025-karnatakas-leap-into-skill-development?amp</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/patil-directs-universities-to-hire-contractual-professors-after-drop-in-nirf-rankings-101757788998645-amp.html</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/dte-stays-admissions-to-174-pharmacy-colleges-across-state-101757358773270.html</t>
+          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/state-plans-to-allow-private-varsities-to-grant-medical-degrees-101757531417862.html</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35121-txt-mumbai-20250918041719</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/new-colleges-in-maharashtra-%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%A4-%E0%A5%AB%E0%A5%AF%E0%A5%A9-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A4%B9-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%AF-%E0%A4%B2%E0%A4%AF%E0%A5%87-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%9A-%E0%A4%B9-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A5%82%E0%A4%B8%E0%A5%8D%E0%A4%9F-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE-%E0%A4%A0%E0%A5%8D%E0%A4%AF-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1Mjk3m</t>
+          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-scholarship-process-change-income-proof-once/photoshow-daurs19</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/ten-day-long-ganesh-chaturthi-festival-to-culminate-today-with-immersion-of-lord-ganeshs-idols/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://annews.co.in/16393/</t>
+          <t>https://www.dainikprabhat.com/why-did-the-family-split-and-become-separated-finally-ajit-pawar-revealed-the-true-chapter/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/India/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/ar-AA1MKOoA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/exam-results/sc-allows-prosecutors-to-provisionally-appear-for-chhattisgarh-judicial-services-exam-101758289734023.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://www.businessupturn.com/business/corporates/pm-modi-lays-foundation-stone-for-sjvns-200-mw-khavda-solar-project-in-gujarat/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263-amp.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/govt-plans-to-introduce-skill-based-learning-in-class-11-12-curriculum-pradhan-101758507200271.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%A4-11-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA%E0%A4%A6%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6-%E0%A4%A8/ar-AA1MQWcn</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-18-101758160005114.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-17-101758074170050.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/education/3635306-paving-the-way-for-skill-based-learning-a-new-era-in-education?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/education/3633673-mizoram-chief-ministers-call-to-action-for-mizo-students?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses/amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/in-the-ubatha-meeting-contest-kalmanuri-np-election/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://annews.co.in/16508/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/amp/story/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A165"/>
+  <dimension ref="A1:A139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,42 +438,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html</t>
+          <t>https://www.indiatoday.in/education-today/news/story/5500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-chandrakant-patil-2791243-2025-09-22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/21/bes24-mh-chandrakant-patil.amp.html</t>
+          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
+          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026?amp</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
@@ -487,329 +487,329 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts?amp</t>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/india-targets-5-pc-share-in-global-shipbuilding-market-by-2030-minister/2916379</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
+          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts?amp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%B5-%E0%A4%B0-%E0%A4%A7%E0%A4%95-%E0%A4%82%E0%A4%B5%E0%A4%B0-%E0%A4%9F-%E0%A4%95/vi-AA1MAx0W?ocid=hpmsn</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179160/</t>
+          <t>https://mahasamvad.in/179266/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
+          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DO3HFhNjGpE/</t>
+          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/chandrakant-patil-assures-to-follow-up-at-the-ministerial-level-135978085.html</t>
+          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
+          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
+          <t>https://mahasamvad.in/179160/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://mahasamvad.in/179154/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/amp/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5388917/what-did-chandrakant-patil-say-about-gopichand-padalkars-controversial-statements/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://mahasamvad.in/178654/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/ladki-bahin-yojana-%E0%A4%B2-%E0%A4%A1%E0%A4%95-%E0%A4%AC%E0%A4%B9-%E0%A4%A3-%E0%A4%AF-%E0%A4%9C%E0%A4%A8-%E0%A4%AC%E0%A4%82%E0%A4%A6-%E0%A4%B9-%E0%A4%A3-%E0%A4%B0-%E0%A4%9C-%E0%A4%A3%E0%A5%82%E0%A4%A8-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%95-%E0%A4%AF-%E0%A4%AE%E0%A5%8D%E0%A4%B9%E0%A4%A3-%E0%A4%B2%E0%A5%87-%E0%A4%89%E0%A4%9A%E0%A5%8D%E0%A4%9A-%E0%A4%B5-%E0%A4%A4%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0%E0%A4%B6-%E0%A4%95%E0%A5%8D%E0%A4%B7%E0%A4%A3-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0%E0%A4%95-%E0%A4%82%E0%A4%A4-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2/ar-AA1x59Ez?cvid=E5D2FC4919EC403B89F2CDD45BDCA942&amp;ocid=TIYLnav&amp;apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://saamtv.esakal.com/video/chandrakant-patil-questions-manoj-jarange-ultimatum-on-certificate-distribution-after-gr-gazette-issued-om0906</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/amp/</t>
+          <t>https://mahasamvad.in/178881/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/big-relief-for-students-submit-income-certificate-once-to-get-full-scholarship-till-all-education-rm96</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/income-certificate-to-be-issued-once-minister-directs-simplification-of-scholarship-process-mla-chandrakant-patil-pjp78</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-alliance-chandrakant-patil-predicts-vote-bank-split-congress-exit-no-impact-on-mahayuti-1386136</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/jalgaon/news/demand-for-200-crores-for-deepening-drains-and-protective-walls-in-the-affected-areas-inspection-by-guardian-minister-gulabrao-patil-and-minister-savkare-135956811.html</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
+          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
         </is>
       </c>
     </row>
@@ -823,210 +823,210 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891/amp</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/the-issue-of-loan-waiver-is-under-the-governments-consideration-what-exactly-did-chandrakant-patil-say/133526/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473/amp</t>
+          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477/amp</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A4%B0-%E0%A4%A0-%E0%A4%B8%E0%A4%AE-%E0%A4%9C-%E0%A4%B8-%E0%A4%A0-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%B0%E0%A4%95-%E0%A4%B0%E0%A4%A8%E0%A5%87-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%AE%E0%A4%B9%E0%A4%A4%E0%A5%8D%E0%A4%A4%E0%A5%8D%E0%A4%B5%E0%A4%AA%E0%A5%82%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3%E0%A4%AF/ar-AA1L2jvO?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/national-international/uttar-pradesh-gorakhpur-crime-wife-caught-her-husband-red-handed-with-his-girlfriend-in-a-hotel-bdk97</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
+          <t>https://www.dainikprabhat.com/chandrakant-patil-then-congress-will-leave-the-alliance-minister-chandrakant-patil-predicted/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/amp/local/maharashtra/mumbai/news/st-will-recruit-17450-drivers-and-assistants-8000-new-buses-will-come-into-passenger-service-135973498.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/sports/shahid-afridi-irfan-pathan-2006-pakistan-tour-dog-meat-remark-controversy-cricket-feud-ind-vs-pak-viral-video-latest-marathi-news-yps99</t>
+          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500/amp</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/lite/</t>
+          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
+          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630/amp</t>
+          <t>https://www.navarashtra.com/business/8th-pay-commission-da-hike-diwali-bonus-central-government-employees-998599.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/amp/story/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://www.navarashtra.com/business/government-schemes-old-pension-scheme-return-supreme-court-2026-news-in-marathi-995481.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
+          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/action-will-be-taken-fancy-number-plate-co-operative-fan/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
+          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
         </is>
       </c>
     </row>
@@ -1040,546 +1040,364 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/navratri-festival-extra-msrtc-buses-to-saptashrungi-gad-msrtc-to-run-additional-buses-bbj88</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077/amp</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
+          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/career/maharashtra-university-college-professor-recruitment-chandrakant-patil-1361015.html/amp</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/youth-corner/assistant-professor-recruitment-maharashtra-2026-5500-vacancies-apply-before-march-3261341.html/amp</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html/amp</t>
+          <t>https://navbharatlive.com/maharashtra/pune/minister-chandrakant-patil-on-gopichand-padalkars-statement-1363502.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/amp/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award/amp/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/karnataka-sslc-puc-2-time-table-2026-out-on-kseab-karnataka-gov-in-submit-objections-october-9-class-10-12-exam/amp</t>
+          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/5500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-10483604</t>
+          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/chandigarh-news/inld-and-jjp-both-proxies-of-the-bjp-haryana-ex-cm-hooda-101758134956254.html</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-polls-ex-bjp-leader-harshvardhan-patil-joins-ncp-sp/ar-AA1rOBQP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
+          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/election/page/1537/</t>
+          <t>https://pudhari.news/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
+          <t>https://mahasamvad.in/178877/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/amp_articleshow/123999758.cms</t>
+          <t>https://mahasamvad.in/179132/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts</t>
+          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35121-txt-mumbai-20250918041719</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/career/maharashtra-university-college-professor-recruitment-chandrakant-patil-1361015.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/no-one-will-support-padalkars-language-chandrakant-patil-clearly-stated-4277808</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3633620-bengaluru-skill-summit-2025-karnatakas-leap-into-skill-development?amp</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://www.loksatta.com/pune/why-cm-devendra-fadnavis-visiting-pune-frequently-pmc-local-body-elections-print-politics-news-css-98-5392812/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
+          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35121-txt-mumbai-20250918041719</t>
+          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-scholarship-process-change-income-proof-once/photoshow-daurs19</t>
+          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/why-did-the-family-split-and-become-separated-finally-ajit-pawar-revealed-the-true-chapter/</t>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/ar-AA1MKOoA?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/exam-results/sc-allows-prosecutors-to-provisionally-appear-for-chhattisgarh-judicial-services-exam-101758289734023.html</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.businessupturn.com/business/corporates/pm-modi-lays-foundation-stone-for-sjvns-200-mw-khavda-solar-project-in-gujarat/</t>
+          <t>https://www.newsdrum.in/national/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries-10480148</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
+          <t>https://www.navarashtra.com/career/education-engineers-day-opinion-learn-these-skills-to-secure-engineering-job-in-10-years-990855.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263-amp.html</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/govt-plans-to-introduce-skill-based-learning-in-class-11-12-curriculum-pradhan-101758507200271.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B8-%E0%A4%B2-%E0%A4%AA%E0%A5%82%E0%A4%B0-%E0%A4%A6-%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%82%E0%A4%A4-%E0%A4%B8%E0%A4%AE-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%A4-11-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%AA%E0%A4%A6%E0%A4%B5-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6-%E0%A4%A8/ar-AA1MQWcn</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-18-101758160005114.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-17-101758074170050.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/education/3635306-paving-the-way-for-skill-based-learning-a-new-era-in-education?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/education/3633673-mizoram-chief-ministers-call-to-action-for-mizo-students?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses/amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79158/</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>https://deshonnati.com/in-the-ubatha-meeting-contest-kalmanuri-np-election/</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
           <t>https://annews.co.in/16508/</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/amp/story/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A139"/>
+  <dimension ref="A1:A150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/5500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-chandrakant-patil-2791243-2025-09-22</t>
+          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/not-giving-immediate-nod-for-faculty-hiring-due-to-fund-crunch-maharashtra-higher-education-minister-10249986/</t>
+          <t>https://www.indiatoday.in/education-today/news/story/5500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-chandrakant-patil-2791243-2025-09-22</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
@@ -487,14 +487,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3633532-maharashtras-digital-leap-library-grants-direct-to-accounts?amp</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
@@ -529,175 +529,175 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179266/</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
+          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://mahasamvad.in/179154/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/minister-chandrakant-patil-criticized-the-opposition/939518</t>
+          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179160/</t>
+          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
+          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179154/</t>
+          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
+          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5388917/what-did-chandrakant-patil-say-about-gopichand-padalkars-controversial-statements/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178654/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5388917/what-did-chandrakant-patil-say-about-gopichand-padalkars-controversial-statements/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
+          <t>https://mahasamvad.in/178654/</t>
         </is>
       </c>
     </row>
@@ -711,280 +711,280 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
+          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178881/</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
+          <t>https://mahasamvad.in/178881/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-thackeray-alliance-chandrakant-patil-predicts-vote-bank-split-congress-exit-no-impact-on-mahayuti-1386136</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
+          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://policenama.com/pm-modi-birthday-news-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-amol-balwadkar-foundation-launched-the-mission-nirmal-cleanliness-campaign-by-higher-technical-education-chan/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/the-issue-of-loan-waiver-is-under-the-governments-consideration-what-exactly-did-chandrakant-patil-say/133526/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://policenama.com/chandrakant-patil-children-should-eat-nachni-foods-for-good-vitamins-needed-by-the-body-chandrakantdada-patils-advice-to-students/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/chandrakant-patil-then-congress-will-leave-the-alliance-minister-chandrakant-patil-predicted/</t>
+          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
+          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://telugu.getlokalapp.com/maharashtra-news/solapur/solapur-city-central/solapur-education-fee-waiver-for-girls-as-per-new-education-policy-15435274</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/pune-kothrud-gets-free-metro-shuttle-smooth-travel-from-station-to-home-bdk97</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
+          <t>https://www.lokmat.com/business/news/gst-rates-cheaper-items-marathi-many-items-will-be-cheaper-from-tomorrow-22-september-see-how-much-gst-will-be-charged-on-which-items-in-your-household-a-a607/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/business/8th-pay-commission-da-hike-diwali-bonus-central-government-employees-998599.html</t>
+          <t>https://www.mahasamvad.in/page/37/?m=0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/business/government-schemes-old-pension-scheme-return-supreme-court-2026-news-in-marathi-995481.html</t>
+          <t>https://www.lokmat.com/business/news/gst-reforms-22-sept-horlicks-vicks-zandu-balm-diapers-toothpaste-everything-is-cheaper-hul-emami-p-and-g-giant-companies-have-released-a-new-list-a-a720/</t>
         </is>
       </c>
     </row>
@@ -1005,42 +1005,42 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
+          <t>https://www.msn.com/mr-in/lifestyle/topstories/student-scholarship-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%AF%E0%A4%95/ar-AA1MKOjT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
+          <t>https://www.navarashtra.com/movies/bollywood/nana-patekar-and-makrand-anaspure-naam-foundation-decade-long-journey-of-social-service-naam-foundation-celebrated-its-decade-anniversary-990653.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
+          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
+          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
         </is>
       </c>
     </row>
@@ -1054,84 +1054,84 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79158/</t>
+          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
+          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/minister-chandrakant-patil-on-gopichand-padalkars-statement-1363502.html</t>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award/amp/</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
+          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-polls-ex-bjp-leader-harshvardhan-patil-joins-ncp-sp/ar-AA1rOBQP?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
         </is>
       </c>
     </row>
@@ -1152,250 +1152,327 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%95-%E0%A4%B2%E0%A5%8D%E0%A4%B9-%E0%A4%AA%E0%A5%81%E0%A4%B0-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A4%9F-%E0%A4%B2-%E0%A4%A7%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%B8%E0%A4%82%E0%A4%9C%E0%A4%AF-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%85%E0%A4%82%E0%A4%AC%E0%A4%B0-%E0%A4%B7-%E0%A4%98-%E0%A4%9F%E0%A4%97%E0%A5%87-%E0%A4%AF-%E0%A4%82%E0%A4%9A-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6/ar-AA1CXkyZ?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8-%E0%A4%B5%E0%A4%A1-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%97/ar-AA1MX7cq</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/pune-baner-missing-link-road-work-bjp-ncp-clash-sb97</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
+          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178877/</t>
+          <t>https://maharashtranews1.com/Graduates--assembly-elections-are-also-being-prepared-by-BJP-and-Shiv-Sena-Thackeray-group-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/jealousy-among-mahayuti-ministers-peaks-over-zilla-parishad-ap84</t>
+          <t>https://www.freepressjournal.in/pune/will-shut-your-business-in-pune-gangster-nilesh-ghaywal-threatens-dharashiv-businessman-over-whatsapp-call-video</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179132/</t>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://www.dainikprabhat.com/dhananjay-munde-on-ajit-pawar/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.esakal.com/pimpri-chinchwad/todays-latest-marathi-news-pne25l40929-txt-pc-today-20250920015330</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
+          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l41674-txt-pune-today-20250921045421</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35121-txt-mumbai-20250918041719</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/why-cm-devendra-fadnavis-visiting-pune-frequently-pmc-local-body-elections-print-politics-news-css-98-5392812/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
+          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
+          <t>https://mahasamvad.in/178893/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+          <t>https://sarkarnama.esakal.com/mumbai/mumbai-bmc-election-2025-shinde-fadnavis-uddhav-raj-thackeray-mm76</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
+          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+          <t>https://www.loksatta.com/nashik/guardian-minister-gulabrao-patil-assured-help-in-muktainagar-phm-00-5382384/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
+          <t>https://maharashtramirror.com/mumbai-news-panipat-writer-vishwas-patil-to-be-the-president-of-sahitya-sammelan/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
+          <t>https://mondaytomondaynews.com/dharna-protest-in-muktainagar-for-the-demands-of-the-dhangar-community-statewide-protest-if-no-decision-is-taken-within-15-days/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
+          <t>https://www.businessupturn.com/business/corporates/pm-modi-lays-foundation-stone-for-sjvns-200-mw-khavda-solar-project-in-gujarat/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+          <t>https://thodkyaat.com/laxman-hake-challenges-manoj-jarange-learn-english-spell-reservation-dont-go-to-delhi-go-to-america-or-africa/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries-10480148</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/career/education-engineers-day-opinion-learn-these-skills-to-secure-engineering-job-in-10-years-990855.html</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries-10480148</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>https://annews.co.in/16508/</t>
         </is>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A150"/>
+  <dimension ref="A1:A137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
         </is>
       </c>
     </row>
@@ -494,28 +494,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
         </is>
       </c>
     </row>
@@ -536,182 +536,182 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179154/</t>
+          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://mahasamvad.in/178560/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/state-to-soon-recruit-college-teachers-announces-minister-chandrakant-patil-sk95</t>
+          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
+          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
+          <t>https://mahasamvad.in/178569/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
+          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
+          <t>https://mahasamvad.in/178557/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5388917/what-did-chandrakant-patil-say-about-gopichand-padalkars-controversial-statements/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178654/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/chandrakant-patil-questions-manoj-jarange-ultimatum-on-certificate-distribution-after-gr-gazette-issued-om0906</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
@@ -725,112 +725,112 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-social-fabric-minister-chandrakant-patil-expresses-concern-over-state-s-social-disintegration-citing-caste-issues-and-impact-on-development-1385630</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178881/</t>
+          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
+          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/pune-kothrud-gets-free-metro-shuttle-smooth-travel-from-station-to-home-bdk97</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/malegaon-development-of-urdu-schools-dada-bhuse-np88</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://agrowon.esakal.com/agro-special/emphasis-on-pest-and-disease-control-along-with-strict-irrigation-in-banana-orchards-rat16</t>
         </is>
       </c>
     </row>
@@ -844,28 +844,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://deshonnati.com/nanded-become-an-entrepreneur-who-strengthens-the-backbone-of-society/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://policenama.com/chandrakant-patil-children-should-eat-nachni-foods-for-good-vitamins-needed-by-the-body-chandrakantdada-patils-advice-to-students/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
@@ -886,182 +886,182 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://ebatmidar.com/%E0%A4%85%E0%A4%A4%E0%A4%BF%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%80%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/income-certificate-now-available-only-once-scholarship-will-be-available-till-completion-of-course/117645/</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/big-relief-for-students-now-income-certificate-will-be-required-only-once-scholarship-will-be-available-till-completion-of-course/</t>
+          <t>https://mahasamvad.in/178881/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
+          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
+          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/maharashtra-news/solapur/solapur-city-central/solapur-education-fee-waiver-for-girls-as-per-new-education-policy-15435274</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/pune-kothrud-gets-free-metro-shuttle-smooth-travel-from-station-to-home-bdk97</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/business/news/gst-rates-cheaper-items-marathi-many-items-will-be-cheaper-from-tomorrow-22-september-see-how-much-gst-will-be-charged-on-which-items-in-your-household-a-a607/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/37/?m=0</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/business/news/gst-reforms-22-sept-horlicks-vicks-zandu-balm-diapers-toothpaste-everything-is-cheaper-hul-emami-p-and-g-giant-companies-have-released-a-new-list-a-a720/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/lifestyle/topstories/student-scholarship-%E0%A4%B6-%E0%A4%B7%E0%A5%8D%E0%A4%AF%E0%A4%B5%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%A4-%E0%A4%85%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%AF%E0%A5%87%E0%A4%A4-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC%E0%A4%A6%E0%A4%B2-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B5%E0%A5%87%E0%A4%B6-%E0%A4%B5%E0%A5%87%E0%A4%B3-%E0%A4%A6-%E0%A4%B2%E0%A5%87%E0%A4%B2-%E0%A4%AE-%E0%A4%B9-%E0%A4%A4-%E0%A4%9A-%E0%A4%A0%E0%A4%B0%E0%A4%A3-%E0%A4%B0-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A3-%E0%A4%AF%E0%A4%95/ar-AA1MKOjT</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/spontaneous-response-to-cancer-screening-camp.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/bollywood/nana-patekar-and-makrand-anaspure-naam-foundation-decade-long-journey-of-social-service-naam-foundation-celebrated-its-decade-anniversary-990653.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/supreme-court-orders-to-hold-local-body-elections-before-january-31-2026.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
         </is>
       </c>
     </row>
@@ -1082,49 +1082,49 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79158/</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/buffalo-gives-birth-to-miraculous-two-faced-calf-in-kolhapur-sparking-discussion-on-social-media/articleshow/123928719.cms</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
+          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
+          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award//</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -1152,329 +1152,238 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/national/%E0%A4%A6-%E0%A4%B2%E0%A5%8D%E0%A4%B2-%E0%A4%A4-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%AF-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%A8-%E0%A4%B5%E0%A4%A1-%E0%A4%A8%E0%A4%82-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-%E0%A4%A4-%E0%A4%B0-%E0%A4%9C%E0%A4%95-%E0%A4%AF-%E0%A4%AD%E0%A5%82%E0%A4%95%E0%A4%82%E0%A4%AA-%E0%A4%98%E0%A4%A1-%E0%A4%AE-%E0%A4%A1-%E0%A4%82%E0%A4%A8-%E0%A4%B5%E0%A5%87%E0%A4%97/ar-AA1MX7cq</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AD-%E0%A4%9C%E0%A4%AA-%E0%A4%B8%E0%A4%A6%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%82%E0%A4%A6%E0%A4%A3-%E0%A4%A4-%E0%A4%B6%E0%A4%B9%E0%A4%B0-%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A5%E0%A4%AE/ar-AA1zoITs?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
+          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Graduates--assembly-elections-are-also-being-prepared-by-BJP-and-Shiv-Sena-Thackeray-group-</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/will-shut-your-business-in-pune-gangster-nilesh-ghaywal-threatens-dharashiv-businessman-over-whatsapp-call-video</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/dhananjay-munde-on-ajit-pawar/</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pimpri-chinchwad/todays-latest-marathi-news-pne25l40929-txt-pc-today-20250920015330</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/todays-latest-marathi-news-pne25l41674-txt-pune-today-20250921045421</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
+          <t>https://www.lokmat.com/pune/are-criminals-and-police-afraid-of-the-rulers-pune-is-plagued-by-crime-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
+          <t>https://mahasamvad.in/178777/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/dcm-eknath-shinde-criticizes-to-rahul-gandhi-evm-vote-chori-case-politics-bihar-election-marathi-news-994377.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/autonomy-vital-for-researchers-to-pursue-innovation-says-cm-fadnavis-101757875592362.html</t>
+          <t>https://www.navarashtra.com/world/nepals-interim-cabinet-to-expand-with-three-new-ministers-today-990664.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178893/</t>
+          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/mumbai-bmc-election-2025-shinde-fadnavis-uddhav-raj-thackeray-mm76</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/women-delaying-motherhood-increases-uterine-cancer-risk-experts-warn-pune-print-news-amy-95-5372589/</t>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/guardian-minister-gulabrao-patil-assured-help-in-muktainagar-phm-00-5382384/</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/mumbai-news-panipat-writer-vishwas-patil-to-be-the-president-of-sahitya-sammelan/</t>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://mondaytomondaynews.com/dharna-protest-in-muktainagar-for-the-demands-of-the-dhangar-community-statewide-protest-if-no-decision-is-taken-within-15-days/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/ceo-gajanan-patil-the-contribution-of-gram-panchayat-officers-in-rural-development-is-remarkable-ceo-gajanan-patil/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.businessupturn.com/business/corporates/pm-modi-lays-foundation-stone-for-sjvns-200-mw-khavda-solar-project-in-gujarat/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://thodkyaat.com/laxman-hake-challenges-manoj-jarange-learn-english-spell-reservation-dont-go-to-delhi-go-to-america-or-africa/</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
           <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>https://www.newsdrum.in/national/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries-10480148</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>https://annews.co.in/16508/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A137"/>
+  <dimension ref="A1:A114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,7 +452,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
         </is>
       </c>
     </row>
@@ -466,21 +466,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/5500-assistant-professors-to-be-recruited-in-maharashtra-before-march-2026-chandrakant-patil-article-152869876</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil/2934478</t>
+          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
@@ -494,126 +494,126 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-starts-direct-transfer-of-grants-to-over-10-000-public-libraries/2930525</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://saralnama.in/education/16002/maharashtra-to-hire-5-500-assistant-professors-by-march-2026/</t>
+          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/pune/phd-students-end-protest-after-assurance-from-minister-chandrakant-patil-vsb99</t>
+          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178560/</t>
+          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
+          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
@@ -627,763 +627,602 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178569/</t>
+          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/chandrakant-patil-on-ajit-pawar-statement-says-he-is-right-there-will-be-big-problem-in-getting-investment-maharashtra-politics-marathi-news-1385477</t>
+          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/solapur/use-knowledge-for-nations-interest-higher-education-minister-chandrakant-patil-at-convocation-sdj87</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178557/</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/chandrakant-patil-statement-padalekar-remarks-sw79-sm89</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
+          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
+          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathi-news-political-news-maharashtra-marathi-news-update-21-sept-2025-pm-modi-mallikarjun-kharge-mahayuti-mva-maharashtra-politics-chandrakant-patil-gopichand-padalkar-dhananjay-munde-sunil-tatkare-gunratna-sadavarte-babasaheb-deshmukh-sushma-andhare-anjali-damania-as11</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/</t>
+          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
+          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/pune-kothrud-gets-free-metro-shuttle-smooth-travel-from-station-to-home-bdk97</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/malegaon-development-of-urdu-schools-dada-bhuse-np88</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://lokmat.news18.com/videos/video/nagpur-news-is-it-right-to-check-religion-by-showing-adhar-card-what-do-the-youth-think-listen-n18v-1075647.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/emphasis-on-pest-and-disease-control-along-with-strict-irrigation-in-banana-orchards-rat16</t>
+          <t>https://www.lokmat.com/pune/are-criminals-and-police-afraid-of-the-rulers-pune-is-plagued-by-crime-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/nanded-become-an-entrepreneur-who-strengthens-the-backbone-of-society/</t>
+          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/chandrakant-patil-criticized-of-rahul-gandhi/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://ebatmidar.com/%E0%A4%85%E0%A4%A4%E0%A4%BF%E0%A4%B5%E0%A5%83%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%80%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B6%E0%A5%87%E0%A4%A4%E0%A4%95%E0%A4%B1%E0%A5%8D%E0%A4%AF/</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178881/</t>
+          <t>https://www.tv9marathi.com/entertainment/nana-patekar-hints-at-retiring-from-natak-and-movies-at-naam-foundation-program-here-is-what-he-said-1493419.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/education-jobs/maharashtra-professor-recruitment-2025-6200-teaching-vacancies-eligibility-application-details-mms21</t>
+          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/educational-news-now-students-will-have-to-provide-income-proof-only-once/</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award//</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.nagpurtoday.in/heres-an-english-slug-for-that-news-6200-professors-mega-recruitment-in-state-colleges-soon/09191636</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
+          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-demand-for-subsidy-for-miraj-balgandharva-theatre-ssb-93-5386538/</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/spontaneous-response-to-cancer-screening-camp.html</t>
+          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/sharad-pawar-reaction-on-hyderabad-gazette-and-the-cabinet-sub-committee-formed-on-reservation/articleshow/123964633.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/supreme-court-orders-to-hold-local-body-elections-before-january-31-2026.html</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/jalgaon-floods-damage-crops-ocd-94-5390192/</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
+          <t>https://ndtv.in/maharashtra-news/chandrakant-patil-statement-education-vs-food-priority-9314731</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-electric-vehicles-will-now-run-on-the-kas-plateau-ssb-93-5386502/</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/buffalo-gives-birth-to-miraculous-two-faced-calf-in-kolhapur-sparking-discussion-on-social-media/articleshow/123928719.cms</t>
+          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
+          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award//</t>
+          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
+          <t>https://punemirror.com/city/power-play-over-water/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
+          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/5-500-assistant-professors-to-be-recruited-before-March-2026-says-minister-Chandrakant-Patil/2934478</t>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
+          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/pune/are-criminals-and-police-afraid-of-the-rulers-pune-is-plagued-by-crime-a-a727/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/178777/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/world/nepals-interim-cabinet-to-expand-with-three-new-ministers-today-990664.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79158/</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
+          <t>https://www.dainikprabhat.com/santosh-yadav-gets-krantijyoti-savitribai-phule-state-teacher-award/</t>
         </is>
       </c>
     </row>

--- a/Output/Chandrakant Patil/extracted_links.xlsx
+++ b/Output/Chandrakant Patil/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A114"/>
+  <dimension ref="A1:A95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,168 +459,168 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
+          <t>https://www.moneycontrol.com/education/maharashtra-to-recruit-5500-assistant-professors-by-2026-announces-minister-chandrakant-patil-article-13563810.html</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/cm-devendra-fadnavis-assures-speedy-faculty-recruitment-in-state-universities-links-delay-to-drop-in-nirf-rankings/articleshow/123886591.cms</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-starts-direct-transfer-of-grants-to-over-10000-public-libraries/articleshow/123999758.cms</t>
+          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/education/maharashtra-5500-assistant-professor-posts-to-be-filled-in-senior-colleges-before-march-2026</t>
+          <t>https://www.oneindia.com/india/5500-assistant-professors-recruited-maharashtra-011-7866581.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/no-repeated-paperwork-for-professional-course-scholarships-minister-101758221398673.html</t>
+          <t>https://www.hindustantimes.com/education/news/5500-assistant-professors-to-be-recruited-before-march-2026-in-maharashtra-says-minister-chandrakant-patil-101758440712263.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3635112-maharashtra-to-recruit-5500-assistant-professors-by-march-2026</t>
+          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-residents-to-get-free-shuttle-bus-service-to-kothrud-metro-station-know-more-here/</t>
+          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/education-news/maharashtra-announces-massive-recruitment-5500-assistant-professor-2900-non-teaching-posts-19963995</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-recruit-5500-assistant-professors-for-senior-colleges-by-march-2026-5617</t>
+          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/jalgaon-guardian-minister-gulabrao-patil-visits-flood-hit-areas-assures-support</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/higher-edu-dept-to-host-lecture-series-vikasit-bharat-sanvad-from-sept-17-101757963146391.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chandrakant-patil-nanded-news-education-is-not-our-country-priority-but-two-meals-a-day-is-says-minister-chandrakant-patil-1385473</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/maharashtra-to-recruit-5500-assistant-professors-by-march-2026/ar-AA1MZ5pj</t>
+          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
+          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/nanded-chandrakant-patil-book-reading-abhang-library-student-council-activists-meet-ssb-93-5386464/</t>
+          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/chandrakant-patil-criticized-congress-leader-harshwardhan-sapkal-after-he-taunt-cm-devendra-fadnavis-vvg94</t>
+          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/videos/chandrakant-patil-reviews-lonere-engineering-university-998287.html</t>
+          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pimpri-chinchwad/pune-news-no-one-will-support-padalkars-language-chandrakant-patil-a-a1008/</t>
+          <t>https://marathi.abplive.com/news/nanded/he-took-out-a-bundle-of-five-hundred-rupee-notes-chandrakant-patil-was-happy-with-the-hospitality-of-the-nanded-rest-house-was-given-a-reward-of-five-thousand-rupees-watch-the-video-1385379</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/free-feeder-bus-service-kothrud-metro-chandrakant-patil-sb97</t>
+          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/income-certificate-once-submitted-for-scholarship-is-valid-till-the-end-of-college-relief-for-students-of-higher-and-technical-education-department-maharashtra-news-mhs25091705299</t>
+          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/chandrakant-patil-comment-on-raj-thackeray-uddhav-thackeray-alliance-impact-on-congress-1485726.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/did-you-steal-votes-in-maharashtra-and-up-at-loksabha-election-chandrakant-patil-question-to-rahul-gandhi-vd83</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/chandrakant-patils-reaction-to-gopichand-padalkars-shivral-language/923658/</t>
+          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/at-solapur-university-convocation-chandrakant-patil-tells-graduates-to-apply-learning-for-nations-progress-rds-00-5383005/</t>
+          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
         </is>
       </c>
     </row>
@@ -634,42 +634,42 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/india/chandrakant-patil-criticizes-to-rahul-gandhi-vote-chori-evm-election-comission-political-marathi-news-994302.html</t>
+          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/chandrakant-patil-statement-on-pm-narendra-modis-2047-plans-pune-print-news-sud-02-5390729/</t>
+          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
+          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/physical-disability-is-a-new-opportunity-says-bjp-leader-chandrakant-patil-in-sangli-css-98-5379119/</t>
+          <t>https://sarkarnama.esakal.com/pune/devendra-fadnavis-becomes-prime-minister-time-will-decide-chandrakant-pati-rm89-sm89</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
+          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/devendra-fadnavis-statement-regarding-chandrakant-patil-finance-department-pune-print-news-amy-95-5372587/</t>
+          <t>https://www.esakal.com/maharashtra/big-news-recruitment-of-6200-professors-and-2900-non-teaching-staff-in-one-month-higher-education-minister-informs-that-approval-has-been-received-from-the-finance-department</t>
         </is>
       </c>
     </row>
@@ -683,546 +683,413 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-student-mahadbt-scholarship-simplified-chandrakant-patil-mumbai-print-news-ocd-94-5381828/</t>
+          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ncp-sharad-pawar-leader-offensive-statement-about-jayant-patil-fadnavis-advice-change-padalkars-language-svk-88-sud-02-5388686/</t>
+          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/future-of-maharashtra-politics-depends-on-wise-decisions-urges-nitin-patil-to-formar-mla-prabhakar-gharge-rds-00-5387645/</t>
+          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhpur-news-factionalism-in-bjp-shiv-sena-and-thackeray-sena-is-not-over-what-exactly-is-going-on-in-kolhapur-politics-rg93-aau85</t>
+          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/guardian-minister-chandrakant-patil-sangli-will-lead-in-panchayatraj-abhiyan-sdj87</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-process-of-depositing-grants-of-government-approved-libraries-in-maharashtra-directly-into-bank-accounts-has-begun-a-a747/</t>
+          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/17-september-2025-students-scholarship-minister-of-higher-and-technical-education-chandrakant-patil/</t>
+          <t>https://maharashtratimes.com/career/career-news/maharashtra-scholarship-significant-changes-in-student-scholarship-application-process/articleshow/123950388.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/abp-majha-top-headlines-20-september-2025-maharashtra-rain-agriculture-loss-donald-trump-h1b-visa-rohit-pawar-chandrakant-patil-news-1385500</t>
+          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/pune-launches-free-shuttle-bus-service-from-metro-stations-to-homes-check-routes-stops-and-more-details-here-article-152854891</t>
+          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/pune-kothrud-gets-free-metro-shuttle-smooth-travel-from-station-to-home-bdk97</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/maharashtra-govt-job-5500-teachers-will-be-appointed/</t>
+          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-15-political-news-in-marathi-939285</t>
+          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/Chandrakant-Patil-assures-to-fulfill-demands-Protest-of-PhD-research-students-in-Pune-temporarily-suspended</t>
+          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/devendra-fadnavis-has-qualities-of-prime-minister-says-chandrakant-patil/09221309</t>
+          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/maharashtra-government-to-fill-more-than-5500-professor-posts-125092100019_1.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://policenama.com/kothrud-missing-link-kothrud-constituency-moving-towards-traffic-congestion-relief-missing-link-work-underway-on-the-initiative-of-chandrakantdada-patil/</t>
+          <t>https://ratnagirikhabardar.com/news/79158/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/mega-recruitment-of-5500-assistant-professors-in-the-state/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/vivaan-karulkar-was-felicitated-by-minister-chandrakant-patil/167336/</t>
+          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://theclearnews.com/gram-gaurav-foundation-to-hold-saksha-lakshmi-awareness-campaign-during-navratri/</t>
+          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/nagpur-news-is-it-right-to-check-religion-by-showing-adhar-card-what-do-the-youth-think-listen-n18v-1075647.html</t>
+          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/are-criminals-and-police-afraid-of-the-rulers-pune-is-plagued-by-crime-a-a727/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
+          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
+          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award//</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/marathi-breaking-news-today-live-updates-on-22-september-2025-breaking-marathi-batmya-997787.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/india-news/cm-devendra-fadnavis-likely-to-elected-as-bjp-national-president-due-to-backing-from-rss/articleshow/124014184.cms</t>
+          <t>https://www.nagpurtoday.in/heres-an-english-slug-for-that-news-6200-professors-mega-recruitment-in-state-colleges-soon/09191636</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/crime-developments-in-kothrud-pune-and-challenge-before-murlidhar-mohol-megha-kulkarni-chandrakant-patil-print-politics-news-asj-82-5383787/</t>
+          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/tv9-marathi-live-coverage-latest-live-updates-manoj-jaranage-patil-chhagan-bhujbal-maratha-obc-reservation-rain-updates-thursday-18-september-2025-1494993.html</t>
+          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/pune-news/union-minister-nitin-gadkari-comments-on-agriculture-and-water-problems-in-maharashtra/articleshow/123889927.cms</t>
+          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/kolhapur-bjp-what-exactly-happened-in-secret-meeting-in-ichalkaranji-leaders-soften-after-being-reprimanded-by-seniors-rg93-aau85</t>
+          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/dhananjay-munde-demand-to-sunil-tatkare-for-some-work-ncp-ajit-pawar-maharashtra-politics-marathi-news-1385972</t>
+          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/entertainment/nana-patekar-hints-at-retiring-from-natak-and-movies-at-naam-foundation-program-here-is-what-he-said-1493419.html</t>
+          <t>https://www.loksatta.com/politics/bjp-mla-randhir-savarkar-akola-nilkanth-cooperative-mill-gets-36-4-crore-grant-from-mahayuti-government-sdp-92-5381028/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/education/maharashtra-to-recruit-5500-assistant-professors-in-senior-colleges-by-march-2026-sarkari-naukri-article-152864646</t>
+          <t>https://www.loksatta.com/pune/pune-thieves-broke-lock-of-flat-in-bibwewadi-kondhwa-area-and-stole-valuables-worth-over-rs-5-lakh-pune-print-news-sud-02-5389067/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-begins-direct-transfer-of-grants-to-over-10000-public-libraries-23594857</t>
+          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/jobs/government-jobs/5-500-assistant-professors-to-be-recruited-before-march-2026-says-minister-chandrakant-patil-2025-09-21</t>
+          <t>https://pudhari.news/maharashtra/pune/maharashtra-scholarship-document-verification-simplified-sp96</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.newslaundry.com/2025/09/22/the-fight-for-punes-green-heart-a-citys-soul-vs-6-minutes-of-saved-commute</t>
+          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/nashik-hindi-poet-kumar-ambuj-wins-ycmous-kusumagraj-national-literary-award-2024</t>
+          <t>https://ahmednagarlive24.com/spacial/pune-news-passengers-travelling-on-this-route-will-now-get-free-bus-service-from-the-station-to-their-homes/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/chandrakant-patil-said-5500-assistant-professors-to-be-recruited-before-march-2026-3016077</t>
+          <t>https://policenama.com/pune-navratri-mahotsav-pune-the-31st-pune-navratri-mahotsav-will-be-inaugurated-grandly-by-revenue-minister-chandrashekhar-bawankule-festival-organizer-aba-bagul-gave-this-information-in-a-press-c/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/20/hindi-poet-kumar-ambuj-wins-kusumagraj-national-literary-award//</t>
+          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/open-universitys-kusumagraj-literary-award-announced-for-kumar-ambuj/923878/</t>
+          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/5-500-assistant-professors-to-be-recruited-in-maharashtra-by-march-2026-says-minister/ar-AA1N2uUL?ocid=finance-verthp-feeds</t>
+          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/heres-an-english-slug-for-that-news-6200-professors-mega-recruitment-in-state-colleges-soon/09191636</t>
+          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-gopichand-padalkar-the-sangli-bjp-mla-constantly-making-headlines-for-fiery-speeches-controversial-remarks</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/anti-naxal-public-safety-bill-support-meeting-in-pune-today.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!lifestyle/why-women-in-politics-are-still-excluded-from-indias-posh-act-and-left-vulnerable-to-sexual-harassment-enn25092002732</t>
+          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/maharashtra-revenue-minister-chandrashekhar-bawankule-to-inaugurate-the-31st-pune-navratri-festival-on-september-22</t>
+          <t>https://www.freepressjournal.in/pune/pune-rotten-foodgrain-supplied-to-citizens-for-contractors-benefit-claim-activists</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/devendra-fadnavis-bjp-national-president-maharashtra-political-earthquake-037687.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-sangli-district-rural-executive-committee-of-62-members-declared-5380186/</t>
+          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-plan-zilla-parishad-panchayat-samiti-and-municipal-elections-in-the-tasgaon-print-politics-news-zws-70-5380765/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.bweducation.com/article/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-572650</t>
+          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/relief-for-students-ease-in-the-application-acceptance-process-to-get-scholarships-on-time/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/dhananjay-mahadik-increased-tension-in-mahayuti-said-there-will-be-discussions-on-those-29-seats-vd83-rg93</t>
+          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/solapur/over-11000-degrees-conferred-at-21st-convocation-of-punes-ahilyadevi-holkar-solapur-university-sk95</t>
+          <t>https://www.tv9marathi.com/entertainment/nana-patekar-hints-at-retiring-from-natak-and-movies-at-naam-foundation-program-here-is-what-he-said-1493419.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/maharashtra-to-recruit-5500-assistant-professors-by-march-2026-says-minister-chandrakant-patil</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-government-to-complete-recruitment-of-5500-assistant-professors-in-senior-colleges-of-state-before-march-2026-vru98</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/amol-balwadkar-foundation-pmc-and-adar-poonawalla-to-launch-mission-nirmal-cleanliness-drive-on-pm-modis-75th-birthday/</t>
+          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/chandrakant-patil-statement-education-vs-food-priority-9314731</t>
+          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/amp/maharashtra/mumbai/bjp-maharashtra-president-chandrakant-patil-on-30-year-old-bjp-shiv-sena-alliance-126264710.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/solapur/11000-degrees-awarded-at-convocation-in-solapur-1360498.html</t>
+          <t>https://education.economictimes.indiatimes.com/news/higher-education/5500-assistant-professors-to-be-recruited-before-march-2026-says-maharashtra-higher-education-minister/124055248</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/dada-attacks-devendra-foreign-investment-in-maharashtra-is-difficult/</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>https://www.mypunepulse.com/31st-pune-navratra-mahotsav-to-open-on-sept-22-with-grand-inauguration/</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/interpretation-of-the-interim-order-of-the-waqf-amendment-act.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>https://www.thebridgechronicle.com/news/coep-alumni-celebrate-engineers-day-cm-fadnavis-calls-for-research-autonomy-agn97</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/political-pulse/decode-politics-maharashtra-govt-grant-bjp-mlas-spinning-mill-left-loose-threads-10256680/</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-minister-announces-streamlined-scholarship-process-to-reduce-document-duplication-for-students/articleshow/123951116.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>https://punemirror.com/city/power-play-over-water/</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-university-student-body-demands-rollback-of-triple-fee-policy-for-management-quota-admissions-23594659</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>https://www.heraldgoa.in/top-stories/ed-investigates-bhutani-group-over-%E2%82%B93500-crore-real-estate-fraud/13588/</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/education/news/school-assembly-news-headlines-today-top-national-world-and-other-news-of-september-22-101758505931767.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/naukri-jobs-news/teachers-recruitment-6200-professor-and-2900-non-teaching-staff-vacancies-apply-now-sh04</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>https://agrowon.esakal.com/agro-special/gadkari-water-conservation-key-to-abundant-irrigation-and-farmer-as-energy-contributor-mj18</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79158/</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ruling-party-leaders-focus-on-divisive-politics-instead-of-supporting-students-rohit-pawar/articleshow/124032926.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/pune-navaratra-mahotsav-to-be-inaugurated-on-monday/articleshow/123984318.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/mhalunge-police-arrest-four-for-theft-solve-two-more-robbery-cases/articleshow/124032928.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/india-spends-just-1-of-gdp-on-r-d-says-ex-air-chief-marshal-vivek-chaudhary-101758133458201.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>https://www.cinebuster.in/naam-foundation-celebrates-a-decade-of-dedicated-social-service/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
           <t>https://news.careers360.com/ayush-neet-counselling-2025-bams-bhms-bpt-colleges-deny-fee-waiver-women-ebc-cet-cell-maharashtra-ayurveda-homeopathy-courses</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://www.dainikprabhat.com/santosh-yadav-gets-krantijyoti-savitribai-phule-state-teacher-award/</t>
         </is>
       </c>
     </row>
